--- a/MU/MU user manual infoneo (2).xlsx
+++ b/MU/MU user manual infoneo (2).xlsx
@@ -1,18 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" activeTab="3"/>
+    <workbookView windowWidth="24000" windowHeight="9600" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Flow" sheetId="1" r:id="rId1"/>
     <sheet name="Certificate calcualtions" sheetId="4" r:id="rId2"/>
     <sheet name="BP - CG fee Calculatons" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet2!$A$1:$H$29</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="245">
   <si>
     <t>Category</t>
   </si>
@@ -1655,40 +1658,148 @@
     <t>NO payment Needed</t>
   </si>
   <si>
-    <t>CP</t>
-  </si>
-  <si>
-    <t>Billing Status</t>
-  </si>
-  <si>
-    <t>Payment Status</t>
-  </si>
-  <si>
-    <t>Auto-Transit</t>
-  </si>
-  <si>
-    <t>Resulting Portfolio Status</t>
-  </si>
-  <si>
-    <t>Effective Date</t>
-  </si>
-  <si>
-    <t>Generated</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Not Generated</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>No Billing Needed</t>
-  </si>
-  <si>
-    <t>No Payment Needed</t>
+    <t>custid</t>
+  </si>
+  <si>
+    <t>acctno</t>
+  </si>
+  <si>
+    <t>sancamt</t>
+  </si>
+  <si>
+    <t>Latest Status</t>
+  </si>
+  <si>
+    <t>Base Period Status</t>
+  </si>
+  <si>
+    <t>CP1 Status</t>
+  </si>
+  <si>
+    <t>CP2 Staus</t>
+  </si>
+  <si>
+    <t>CP3 Status</t>
+  </si>
+  <si>
+    <t>CP4 Status</t>
+  </si>
+  <si>
+    <t>CP5 Status</t>
+  </si>
+  <si>
+    <t>CP6 Status</t>
+  </si>
+  <si>
+    <t>2627CR701</t>
+  </si>
+  <si>
+    <t>Stn</t>
+  </si>
+  <si>
+    <t>2627CR702</t>
+  </si>
+  <si>
+    <t>2627CR703</t>
+  </si>
+  <si>
+    <t>NPA</t>
+  </si>
+  <si>
+    <t>Claim 1</t>
+  </si>
+  <si>
+    <t>2627CR704</t>
+  </si>
+  <si>
+    <t>2627CR705</t>
+  </si>
+  <si>
+    <t>2627CR706</t>
+  </si>
+  <si>
+    <t>2627CR707</t>
+  </si>
+  <si>
+    <t>2627CR708</t>
+  </si>
+  <si>
+    <t>2627CR709</t>
+  </si>
+  <si>
+    <t>2627CR710</t>
+  </si>
+  <si>
+    <t>2627CR711</t>
+  </si>
+  <si>
+    <t>2627CR712</t>
+  </si>
+  <si>
+    <t>2627CR713</t>
+  </si>
+  <si>
+    <t>2627CR714</t>
+  </si>
+  <si>
+    <t>2627CR715</t>
+  </si>
+  <si>
+    <t>2627CR716</t>
+  </si>
+  <si>
+    <t>2627CR717</t>
+  </si>
+  <si>
+    <t>2627CR718</t>
+  </si>
+  <si>
+    <t>2627CR719</t>
+  </si>
+  <si>
+    <t>2627CR720</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+  <si>
+    <t>2627CR721</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>2627CR722</t>
+  </si>
+  <si>
+    <t>2627CR723</t>
+  </si>
+  <si>
+    <t>Q2 - Closed</t>
+  </si>
+  <si>
+    <t>2627CR724</t>
+  </si>
+  <si>
+    <t>Q2 - IA</t>
+  </si>
+  <si>
+    <t>InEliCust19</t>
+  </si>
+  <si>
+    <t>SameCutInEli22</t>
+  </si>
+  <si>
+    <t>InEliCust1</t>
+  </si>
+  <si>
+    <t>SameCutInEli23</t>
+  </si>
+  <si>
+    <t>SameCutInEli24</t>
+  </si>
+  <si>
+    <t>SameCutInEli25</t>
   </si>
 </sst>
 </file>
@@ -1705,13 +1816,32 @@
     <numFmt numFmtId="182" formatCode="0.00_ "/>
     <numFmt numFmtId="183" formatCode="mmm/yy"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1928,7 +2058,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1937,13 +2067,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
+        <fgColor theme="3" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2164,7 +2300,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -2175,6 +2311,34 @@
     <border>
       <left style="thin">
         <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
         <color auto="1"/>
@@ -2414,180 +2578,184 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2611,17 +2779,20 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2629,46 +2800,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2680,64 +2851,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3276,947 +3447,947 @@
   <dimension ref="A1:Z71"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7142857142857" style="41" customWidth="1"/>
+    <col min="1" max="1" width="22.7142857142857" style="46" customWidth="1"/>
     <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="49.8571428571429" style="36" customWidth="1"/>
+    <col min="3" max="3" width="49.8571428571429" style="41" customWidth="1"/>
     <col min="4" max="4" width="46.8571428571429" customWidth="1"/>
     <col min="5" max="5" width="57.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:26">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
     </row>
     <row r="2" ht="135" spans="1:26">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="51" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="75" spans="1:26">
-      <c r="A3" s="48"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="53"/>
+      <c r="B3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="17"/>
+      <c r="E3" s="21"/>
     </row>
     <row r="4" ht="75" spans="1:26">
-      <c r="A4" s="48"/>
-      <c r="B4" s="17" t="s">
+      <c r="A4" s="53"/>
+      <c r="B4" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="17"/>
+      <c r="E4" s="21"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="49"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
+      <c r="A5" s="54"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
     </row>
     <row r="6" ht="75" spans="1:26">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="E6" s="51" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:26">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="17"/>
+      <c r="E7" s="21"/>
     </row>
     <row r="8" ht="56" customHeight="1" spans="1:26">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
     </row>
     <row r="9" ht="60" spans="1:26">
-      <c r="A9" s="48"/>
-      <c r="B9" s="17" t="s">
+      <c r="A9" s="53"/>
+      <c r="B9" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
     </row>
     <row r="10" ht="60" spans="1:26">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="52" t="s">
+      <c r="D10" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="17"/>
+      <c r="E10" s="21"/>
     </row>
     <row r="11" customFormat="1" ht="60" spans="1:26">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="17"/>
+      <c r="E11" s="21"/>
     </row>
     <row r="12" customFormat="1" ht="45" spans="1:26">
-      <c r="A12" s="48" t="s">
+      <c r="A12" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
     </row>
     <row r="13" customFormat="1" ht="60" spans="1:26">
-      <c r="A13" s="48"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="53"/>
+      <c r="B13" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
     </row>
     <row r="14" customFormat="1" ht="60" spans="1:26">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="17"/>
+      <c r="E14" s="21"/>
     </row>
     <row r="15" ht="60" spans="1:26">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="46" t="s">
+      <c r="C15" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="47" t="s">
+      <c r="D15" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="17"/>
+      <c r="E15" s="21"/>
     </row>
     <row r="16" ht="45" spans="1:26">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="C16" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
     </row>
     <row r="17" ht="60" spans="1:5">
-      <c r="A17" s="48"/>
-      <c r="B17" s="17" t="s">
+      <c r="A17" s="53"/>
+      <c r="B17" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="C17" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
     </row>
     <row r="18" customFormat="1" ht="60" spans="1:5">
-      <c r="A18" s="48" t="s">
+      <c r="A18" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" ht="60" spans="1:5">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="47" t="s">
+      <c r="D19" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="17"/>
+      <c r="E19" s="21"/>
     </row>
     <row r="20" ht="45" spans="1:5">
-      <c r="A20" s="48" t="s">
+      <c r="A20" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
     </row>
     <row r="21" ht="60" spans="1:5">
-      <c r="A21" s="48"/>
-      <c r="B21" s="17" t="s">
+      <c r="A21" s="53"/>
+      <c r="B21" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
     </row>
     <row r="22" ht="90" spans="1:5">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="47" t="s">
+      <c r="C22" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
     </row>
     <row r="23" ht="65" customHeight="1" spans="1:5">
-      <c r="A23" s="48" t="s">
+      <c r="A23" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="52" t="s">
+      <c r="D23" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="21" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" ht="65" customHeight="1" spans="1:5">
-      <c r="A24" s="48" t="s">
+      <c r="A24" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C24" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="52" t="s">
+      <c r="D24" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="17"/>
-    </row>
-    <row r="25" s="38" customFormat="1" ht="23.25" spans="1:5">
-      <c r="A25" s="53" t="s">
+      <c r="E24" s="21"/>
+    </row>
+    <row r="25" s="43" customFormat="1" ht="23.25" spans="1:5">
+      <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="54"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="55"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="60"/>
     </row>
     <row r="26" ht="90" spans="1:5">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="58" t="s">
+      <c r="C26" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="58" t="s">
+      <c r="D26" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="57"/>
+      <c r="E26" s="62"/>
     </row>
     <row r="27" ht="45" spans="1:5">
-      <c r="A27" s="56"/>
-      <c r="B27" s="17" t="s">
+      <c r="A27" s="61"/>
+      <c r="B27" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
     </row>
     <row r="28" ht="60" spans="1:5">
-      <c r="A28" s="59"/>
-      <c r="B28" s="17" t="s">
+      <c r="A28" s="64"/>
+      <c r="B28" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="47" t="s">
+      <c r="C28" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
     </row>
     <row r="29" ht="75" spans="1:5">
-      <c r="A29" s="48" t="s">
+      <c r="A29" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="47" t="s">
+      <c r="C29" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="60" t="s">
+      <c r="D29" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="17"/>
+      <c r="E29" s="21"/>
     </row>
     <row r="30" ht="45" spans="1:5">
-      <c r="A30" s="48" t="s">
+      <c r="A30" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="46" t="s">
+      <c r="C30" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
     </row>
     <row r="31" ht="55" customHeight="1" spans="1:5">
-      <c r="A31" s="48" t="s">
+      <c r="A31" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
     </row>
     <row r="32" ht="45" spans="1:5">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="46" t="s">
+      <c r="C32" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="47"/>
-      <c r="E32" s="17"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="21"/>
     </row>
     <row r="33" ht="45" spans="1:5">
-      <c r="A33" s="15"/>
-      <c r="B33" s="17" t="s">
+      <c r="A33" s="19"/>
+      <c r="B33" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="46" t="s">
+      <c r="C33" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="47"/>
-      <c r="E33" s="17"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="21"/>
     </row>
     <row r="34" ht="45" spans="1:5">
-      <c r="A34" s="15"/>
-      <c r="B34" s="17" t="s">
+      <c r="A34" s="19"/>
+      <c r="B34" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="47" t="s">
+      <c r="C34" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="47"/>
-      <c r="E34" s="17"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="21"/>
     </row>
     <row r="35" ht="75" spans="1:5">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="47" t="s">
+      <c r="C35" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="47" t="s">
+      <c r="D35" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="E35" s="17"/>
+      <c r="E35" s="21"/>
     </row>
     <row r="36" ht="75" spans="1:5">
-      <c r="A36" s="15"/>
-      <c r="B36" s="17" t="s">
+      <c r="A36" s="19"/>
+      <c r="B36" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="47" t="s">
+      <c r="C36" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
     </row>
     <row r="37" ht="45" spans="1:5">
-      <c r="A37" s="15"/>
-      <c r="B37" s="17" t="s">
+      <c r="A37" s="19"/>
+      <c r="B37" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="47" t="s">
+      <c r="C37" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
     </row>
     <row r="38" ht="60" spans="1:5">
-      <c r="A38" s="61" t="s">
+      <c r="A38" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="47" t="s">
+      <c r="C38" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="47"/>
-      <c r="E38" s="17" t="s">
+      <c r="D38" s="52"/>
+      <c r="E38" s="21" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="39" ht="60" spans="1:5">
-      <c r="A39" s="56"/>
-      <c r="B39" s="17" t="s">
+      <c r="A39" s="61"/>
+      <c r="B39" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="47" t="s">
+      <c r="C39" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="47"/>
-      <c r="E39" s="17"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="21"/>
     </row>
     <row r="40" ht="90" spans="1:5">
-      <c r="A40" s="61" t="s">
+      <c r="A40" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="47" t="s">
+      <c r="C40" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="47" t="s">
+      <c r="D40" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="E40" s="17"/>
+      <c r="E40" s="21"/>
     </row>
     <row r="41" ht="75" spans="1:5">
-      <c r="A41" s="56"/>
-      <c r="B41" s="17" t="s">
+      <c r="A41" s="61"/>
+      <c r="B41" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="47" t="s">
+      <c r="C41" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
     </row>
     <row r="42" ht="45" spans="1:5">
-      <c r="A42" s="59"/>
-      <c r="B42" s="17" t="s">
+      <c r="A42" s="64"/>
+      <c r="B42" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="47" t="s">
+      <c r="C42" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
     </row>
     <row r="43" ht="75" spans="1:5">
-      <c r="A43" s="48" t="s">
+      <c r="A43" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="47" t="s">
+      <c r="C43" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="D43" s="60" t="s">
+      <c r="D43" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="E43" s="17"/>
-    </row>
-    <row r="44" s="39" customFormat="1" ht="45" spans="1:5">
-      <c r="A44" s="45" t="s">
+      <c r="E43" s="21"/>
+    </row>
+    <row r="44" s="44" customFormat="1" ht="45" spans="1:5">
+      <c r="A44" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="62" t="s">
+      <c r="C44" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="E44" s="14"/>
+      <c r="E44" s="18"/>
     </row>
     <row r="45" ht="75" spans="1:5">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="47" t="s">
+      <c r="C45" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="47" t="s">
+      <c r="D45" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="E45" s="17"/>
+      <c r="E45" s="21"/>
     </row>
     <row r="46" ht="75" spans="1:5">
-      <c r="A46" s="15"/>
-      <c r="B46" s="17" t="s">
+      <c r="A46" s="19"/>
+      <c r="B46" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="47" t="s">
+      <c r="C46" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
     </row>
     <row r="47" ht="45" spans="1:5">
-      <c r="A47" s="15"/>
-      <c r="B47" s="17" t="s">
+      <c r="A47" s="19"/>
+      <c r="B47" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="47" t="s">
+      <c r="C47" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
     </row>
     <row r="48" ht="60" spans="1:5">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="47" t="s">
+      <c r="C48" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="D48" s="47"/>
-      <c r="E48" s="17" t="s">
+      <c r="D48" s="52"/>
+      <c r="E48" s="21" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="49" ht="60" spans="1:5">
-      <c r="A49" s="15"/>
-      <c r="B49" s="17" t="s">
+      <c r="A49" s="19"/>
+      <c r="B49" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="47" t="s">
+      <c r="C49" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="D49" s="47"/>
-      <c r="E49" s="17"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="21"/>
     </row>
     <row r="50" ht="90" spans="1:5">
-      <c r="A50" s="61" t="s">
+      <c r="A50" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="B50" s="17" t="s">
+      <c r="B50" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="47" t="s">
+      <c r="C50" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="D50" s="47" t="s">
+      <c r="D50" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="E50" s="17"/>
+      <c r="E50" s="21"/>
     </row>
     <row r="51" ht="75" spans="1:5">
-      <c r="A51" s="56"/>
-      <c r="B51" s="17" t="s">
+      <c r="A51" s="61"/>
+      <c r="B51" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C51" s="47" t="s">
+      <c r="C51" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
     </row>
     <row r="52" ht="45" spans="1:5">
-      <c r="A52" s="59"/>
-      <c r="B52" s="17" t="s">
+      <c r="A52" s="64"/>
+      <c r="B52" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="47" t="s">
+      <c r="C52" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
     </row>
     <row r="53" ht="75" spans="1:5">
-      <c r="A53" s="48" t="s">
+      <c r="A53" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B53" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C53" s="47" t="s">
+      <c r="C53" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="D53" s="60" t="s">
+      <c r="D53" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="E53" s="17"/>
-    </row>
-    <row r="54" s="39" customFormat="1" ht="45" spans="1:5">
-      <c r="A54" s="45" t="s">
+      <c r="E53" s="21"/>
+    </row>
+    <row r="54" s="44" customFormat="1" ht="45" spans="1:5">
+      <c r="A54" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C54" s="62" t="s">
+      <c r="C54" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="E54" s="14"/>
+      <c r="E54" s="18"/>
     </row>
     <row r="56" ht="75" spans="1:5">
-      <c r="A56" s="15" t="s">
+      <c r="A56" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="17" t="s">
+      <c r="B56" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C56" s="47" t="s">
+      <c r="C56" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="D56" s="47" t="s">
+      <c r="D56" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="E56" s="17"/>
+      <c r="E56" s="21"/>
     </row>
     <row r="57" ht="75" spans="1:5">
-      <c r="A57" s="15"/>
-      <c r="B57" s="17" t="s">
+      <c r="A57" s="19"/>
+      <c r="B57" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C57" s="47" t="s">
+      <c r="C57" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
     </row>
     <row r="58" ht="45" spans="1:5">
-      <c r="A58" s="15"/>
-      <c r="B58" s="17" t="s">
+      <c r="A58" s="19"/>
+      <c r="B58" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="47" t="s">
+      <c r="C58" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
     </row>
     <row r="59" ht="60" spans="1:5">
-      <c r="A59" s="15" t="s">
+      <c r="A59" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B59" s="17" t="s">
+      <c r="B59" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="47" t="s">
+      <c r="C59" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="D59" s="47"/>
-      <c r="E59" s="17" t="s">
+      <c r="D59" s="52"/>
+      <c r="E59" s="21" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="60" ht="60" spans="1:5">
-      <c r="A60" s="15"/>
-      <c r="B60" s="17" t="s">
+      <c r="A60" s="19"/>
+      <c r="B60" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="47" t="s">
+      <c r="C60" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="47"/>
-      <c r="E60" s="17"/>
-    </row>
-    <row r="61" s="40" customFormat="1" ht="90" spans="1:5">
-      <c r="A61" s="63" t="s">
+      <c r="D60" s="52"/>
+      <c r="E60" s="21"/>
+    </row>
+    <row r="61" s="45" customFormat="1" ht="90" spans="1:5">
+      <c r="A61" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="B61" s="64" t="s">
+      <c r="B61" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="65" t="s">
+      <c r="C61" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="D61" s="65" t="s">
+      <c r="D61" s="70" t="s">
         <v>92</v>
       </c>
-      <c r="E61" s="64"/>
-    </row>
-    <row r="62" s="40" customFormat="1" ht="75" spans="1:5">
-      <c r="A62" s="66"/>
-      <c r="B62" s="64" t="s">
+      <c r="E61" s="69"/>
+    </row>
+    <row r="62" s="45" customFormat="1" ht="75" spans="1:5">
+      <c r="A62" s="71"/>
+      <c r="B62" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C62" s="65" t="s">
+      <c r="C62" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="D62" s="64"/>
-      <c r="E62" s="64"/>
-    </row>
-    <row r="63" s="40" customFormat="1" ht="45" spans="1:5">
-      <c r="A63" s="67"/>
-      <c r="B63" s="64" t="s">
+      <c r="D62" s="69"/>
+      <c r="E62" s="69"/>
+    </row>
+    <row r="63" s="45" customFormat="1" ht="45" spans="1:5">
+      <c r="A63" s="72"/>
+      <c r="B63" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="65" t="s">
+      <c r="C63" s="70" t="s">
         <v>76</v>
       </c>
-      <c r="D63" s="64"/>
-      <c r="E63" s="64"/>
+      <c r="D63" s="69"/>
+      <c r="E63" s="69"/>
     </row>
     <row r="64" ht="75" spans="1:5">
-      <c r="A64" s="48" t="s">
+      <c r="A64" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="B64" s="17" t="s">
+      <c r="B64" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C64" s="47" t="s">
+      <c r="C64" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="D64" s="60" t="s">
+      <c r="D64" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="E64" s="17"/>
-    </row>
-    <row r="65" s="39" customFormat="1" ht="45" spans="1:5">
-      <c r="A65" s="45" t="s">
+      <c r="E64" s="21"/>
+    </row>
+    <row r="65" s="44" customFormat="1" ht="45" spans="1:5">
+      <c r="A65" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C65" s="62" t="s">
+      <c r="C65" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="D65" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="E65" s="14"/>
-    </row>
-    <row r="66" s="38" customFormat="1" ht="23.25" spans="1:5">
-      <c r="A66" s="68" t="s">
+      <c r="E65" s="18"/>
+    </row>
+    <row r="66" s="43" customFormat="1" ht="23.25" spans="1:5">
+      <c r="A66" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68"/>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
+      <c r="B66" s="73"/>
+      <c r="C66" s="73"/>
+      <c r="D66" s="73"/>
+      <c r="E66" s="73"/>
     </row>
     <row r="67" ht="90" spans="1:5">
-      <c r="A67" s="56" t="s">
+      <c r="A67" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="B67" s="57" t="s">
+      <c r="B67" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="C67" s="58" t="s">
+      <c r="C67" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="D67" s="58" t="s">
+      <c r="D67" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="E67" s="57"/>
+      <c r="E67" s="62"/>
     </row>
     <row r="68" ht="45" spans="1:5">
-      <c r="A68" s="56"/>
-      <c r="B68" s="17" t="s">
+      <c r="A68" s="61"/>
+      <c r="B68" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="47" t="s">
+      <c r="C68" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="D68" s="17"/>
-      <c r="E68" s="17"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
     </row>
     <row r="69" ht="60" spans="1:5">
-      <c r="A69" s="59"/>
-      <c r="B69" s="17" t="s">
+      <c r="A69" s="64"/>
+      <c r="B69" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C69" s="47" t="s">
+      <c r="C69" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="D69" s="17"/>
-      <c r="E69" s="17"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
     </row>
     <row r="70" ht="75" spans="1:5">
-      <c r="A70" s="48" t="s">
+      <c r="A70" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="17" t="s">
+      <c r="B70" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="47" t="s">
+      <c r="C70" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="D70" s="60" t="s">
+      <c r="D70" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="E70" s="17"/>
+      <c r="E70" s="21"/>
     </row>
     <row r="71" ht="45" spans="1:5">
-      <c r="A71" s="48" t="s">
+      <c r="A71" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="17" t="s">
+      <c r="B71" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C71" s="46" t="s">
+      <c r="C71" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="D71" s="17"/>
-      <c r="E71" s="17"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4251,84 +4422,84 @@
   <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="42" style="31" customWidth="1"/>
-    <col min="2" max="2" width="42.8571428571429" style="17" customWidth="1"/>
-    <col min="3" max="4" width="9.14285714285714" style="17"/>
+    <col min="1" max="1" width="42" style="36" customWidth="1"/>
+    <col min="2" max="2" width="42.8571428571429" style="21" customWidth="1"/>
+    <col min="3" max="4" width="9.14285714285714" style="21"/>
     <col min="5" max="5" width="43.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:17">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:17">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="33">
-        <v>1800153</v>
-      </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
+      <c r="B3" s="38">
+        <v>3115502.69</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
       <c r="E3" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:17">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="33">
+      <c r="B4" s="38">
         <v>2</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
       <c r="E4" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="5" ht="33" customHeight="1" spans="1:17">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="33">
-        <v>200000</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
+      <c r="B5" s="38">
+        <v>115000</v>
+      </c>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
       <c r="E5" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:17">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="33">
-        <v>0</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="38">
+        <v>14200</v>
+      </c>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
       <c r="E6" t="s">
         <v>114</v>
       </c>
-      <c r="N6" s="35">
+      <c r="N6" s="40">
         <v>15000</v>
       </c>
       <c r="P6">
@@ -4336,15 +4507,15 @@
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:17">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="38">
         <f>B5-B6</f>
-        <v>200000</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
+        <v>100800</v>
+      </c>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
       <c r="E7" t="s">
         <v>116</v>
       </c>
@@ -4359,19 +4530,19 @@
       </c>
     </row>
     <row r="8" ht="71" customHeight="1" spans="1:17">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="38">
         <f>3%*B7</f>
-        <v>6000</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="36" t="s">
+        <v>3024</v>
+      </c>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="N8" s="35">
+      <c r="N8" s="40">
         <v>20453</v>
       </c>
       <c r="P8">
@@ -4379,15 +4550,15 @@
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:17">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="38">
         <f>B7-B8</f>
-        <v>194000</v>
-      </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
+        <v>97776</v>
+      </c>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
       <c r="E9" t="s">
         <v>120</v>
       </c>
@@ -4399,19 +4570,19 @@
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:17">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="38">
         <f>15%*B3</f>
-        <v>270022.95</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
+        <v>467325.4035</v>
+      </c>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
       <c r="E10" t="s">
         <v>122</v>
       </c>
-      <c r="K10" s="37">
+      <c r="K10" s="42">
         <v>38697.18</v>
       </c>
       <c r="N10">
@@ -4422,19 +4593,19 @@
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:17">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="38">
         <f>75%*B9</f>
-        <v>145500</v>
-      </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
+        <v>73332</v>
+      </c>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
       <c r="E11" t="s">
         <v>124</v>
       </c>
-      <c r="K11" s="37">
+      <c r="K11" s="42">
         <v>47062.7</v>
       </c>
       <c r="N11">
@@ -4445,37 +4616,37 @@
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:17">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="38">
         <f>B11</f>
-        <v>145500</v>
-      </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
+        <v>73332</v>
+      </c>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:17">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
       <c r="E13" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="14" ht="33" customHeight="1" spans="1:17">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="38">
         <f>B12-B13</f>
-        <v>145500</v>
-      </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
+        <v>73332</v>
+      </c>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -4516,199 +4687,199 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-    </row>
-    <row r="2" s="25" customFormat="1" spans="1:14">
-      <c r="A2" s="26" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+    </row>
+    <row r="2" s="30" customFormat="1" spans="1:14">
+      <c r="A2" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="N2" s="25">
+      <c r="N2" s="30">
         <v>832.88</v>
       </c>
     </row>
-    <row r="3" s="25" customFormat="1" spans="1:14">
-      <c r="A3" s="27">
+    <row r="3" s="30" customFormat="1" spans="1:14">
+      <c r="A3" s="32">
         <v>46174</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="32">
         <v>46477</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="33">
         <f>B3-A3+1</f>
         <v>304</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="34">
         <f>1%*E3*C3/365</f>
         <v>832.876712328767</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="33">
         <v>100000</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="33">
         <f>D3*18%</f>
         <v>149.917808219178</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="33">
         <f>D3+F3</f>
         <v>982.794520547945</v>
       </c>
     </row>
-    <row r="4" s="25" customFormat="1"/>
+    <row r="4" s="30" customFormat="1"/>
     <row r="7" spans="1:14">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="31" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="27">
+      <c r="A9" s="32">
         <v>46072</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="32">
         <v>46112</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="33">
         <f>B9-A9+1</f>
         <v>41</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="34">
         <f>0.25%*E9*C9/365</f>
         <v>28.0821917808219</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="33">
         <v>100000</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="33">
         <f>D9*18%</f>
         <v>5.05479452054795</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="33">
         <f>D9+F9</f>
         <v>33.1369863013699</v>
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="H14" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="I14" s="26" t="s">
+      <c r="I14" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="J14" s="26" t="s">
+      <c r="J14" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="K14" s="26" t="s">
+      <c r="K14" s="31" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="33">
         <v>10000</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="32">
         <v>46082</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="32">
         <v>46477</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="33">
         <f>DATEDIF(C15,D15,"d")+1</f>
         <v>396</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="35">
         <v>0.01</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="33">
         <f>IF(K15="Closed",0,B15*F15*(E15/365))</f>
         <v>108.493150684932</v>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="33">
         <f>G15*9%</f>
         <v>9.76438356164384</v>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="33">
         <f>18%*G15</f>
         <v>19.5287671232877</v>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="33">
         <f>G15+H15+I15</f>
         <v>137.786301369863</v>
       </c>
-      <c r="K15" s="28" t="s">
+      <c r="K15" s="33" t="s">
         <v>150</v>
       </c>
     </row>
@@ -4744,559 +4915,559 @@
       </c>
     </row>
     <row r="2" spans="3:10">
-      <c r="C2" s="14"/>
-      <c r="D2" s="14" t="s">
+      <c r="C2" s="18"/>
+      <c r="D2" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="19" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="3" spans="3:10">
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18" t="s">
+      <c r="G3" s="22"/>
+      <c r="H3" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="J3" s="15"/>
+      <c r="J3" s="19"/>
     </row>
     <row r="4" spans="3:10">
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="23">
         <v>46386</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="J4" s="15"/>
+      <c r="J4" s="19"/>
     </row>
     <row r="5" spans="3:10">
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="23">
         <v>46477</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="J5" s="15"/>
+      <c r="J5" s="19"/>
     </row>
     <row r="6" spans="3:10">
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="23">
         <v>46568</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="J6" s="15"/>
+      <c r="J6" s="19"/>
     </row>
     <row r="7" spans="3:10">
-      <c r="C7" s="20"/>
-      <c r="I7" s="20"/>
+      <c r="C7" s="24"/>
+      <c r="I7" s="24"/>
     </row>
     <row r="8" spans="3:10">
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="25">
         <v>46843</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="J8" s="20" t="s">
+      <c r="J8" s="24" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="9" spans="3:10">
-      <c r="C9" s="20"/>
-      <c r="F9" s="22" t="s">
+      <c r="C9" s="24"/>
+      <c r="F9" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="27">
         <v>46843</v>
       </c>
-      <c r="I9" s="24" t="s">
+      <c r="I9" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="J9" s="24" t="s">
+      <c r="J9" s="28" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="10" spans="3:10">
-      <c r="C10" s="20"/>
-      <c r="F10" s="22" t="s">
+      <c r="C10" s="24"/>
+      <c r="F10" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23">
+      <c r="G10" s="27"/>
+      <c r="H10" s="27">
         <v>46844</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="J10" s="28" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="11" spans="3:10">
-      <c r="C11" s="20"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="20"/>
+      <c r="C11" s="24"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="24"/>
     </row>
     <row r="12" spans="3:10">
-      <c r="C12" s="20"/>
-      <c r="I12" s="20"/>
+      <c r="C12" s="24"/>
+      <c r="I12" s="24"/>
     </row>
     <row r="13" spans="3:10">
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="G13" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="25">
         <v>47208</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="J13" s="20" t="s">
+      <c r="J13" s="24" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="14" spans="3:10">
-      <c r="C14" s="20"/>
-      <c r="F14" s="22" t="s">
+      <c r="C14" s="24"/>
+      <c r="F14" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="G14" s="23" t="s">
+      <c r="G14" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="27">
         <v>47208</v>
       </c>
-      <c r="I14" s="24" t="s">
+      <c r="I14" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="J14" s="24" t="s">
+      <c r="J14" s="28" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="15" spans="3:10">
-      <c r="C15" s="20"/>
-      <c r="F15" s="22" t="s">
+      <c r="C15" s="24"/>
+      <c r="F15" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23">
+      <c r="G15" s="27"/>
+      <c r="H15" s="27">
         <v>47209</v>
       </c>
-      <c r="I15" s="24" t="s">
+      <c r="I15" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="J15" s="24" t="s">
+      <c r="J15" s="28" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="16" spans="3:10">
-      <c r="C16" s="20"/>
-      <c r="I16" s="20"/>
+      <c r="C16" s="24"/>
+      <c r="I16" s="24"/>
     </row>
     <row r="17" spans="3:10">
-      <c r="C17" s="20"/>
-      <c r="I17" s="20"/>
+      <c r="C17" s="24"/>
+      <c r="I17" s="24"/>
     </row>
     <row r="18" spans="3:10">
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="G18" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="25">
         <v>47573</v>
       </c>
-      <c r="I18" s="16" t="s">
+      <c r="I18" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="J18" s="20" t="s">
+      <c r="J18" s="24" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="20"/>
-      <c r="F19" s="22" t="s">
+      <c r="C19" s="24"/>
+      <c r="F19" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="G19" s="23" t="s">
+      <c r="G19" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="27">
         <v>47573</v>
       </c>
-      <c r="I19" s="24" t="s">
+      <c r="I19" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="J19" s="24" t="s">
+      <c r="J19" s="28" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="20" spans="3:10">
-      <c r="C20" s="20"/>
-      <c r="F20" s="22" t="s">
+      <c r="C20" s="24"/>
+      <c r="F20" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23">
+      <c r="G20" s="27"/>
+      <c r="H20" s="27">
         <v>47574</v>
       </c>
-      <c r="I20" s="24" t="s">
+      <c r="I20" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="J20" s="24" t="s">
+      <c r="J20" s="28" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="20"/>
-      <c r="I21" s="20"/>
+      <c r="C21" s="24"/>
+      <c r="I21" s="24"/>
     </row>
     <row r="22" spans="3:10">
-      <c r="C22" s="20"/>
-      <c r="I22" s="20"/>
+      <c r="C22" s="24"/>
+      <c r="I22" s="24"/>
     </row>
     <row r="23" spans="3:10">
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="G23" s="21" t="s">
+      <c r="G23" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="H23" s="21">
+      <c r="H23" s="25">
         <v>47938</v>
       </c>
-      <c r="I23" s="16" t="s">
+      <c r="I23" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="J23" s="20" t="s">
+      <c r="J23" s="24" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="24" spans="3:10">
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="G24" s="23" t="s">
+      <c r="G24" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="H24" s="23">
+      <c r="H24" s="27">
         <v>47938</v>
       </c>
-      <c r="I24" s="24" t="s">
+      <c r="I24" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="J24" s="24" t="s">
+      <c r="J24" s="28" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="25" spans="3:10">
-      <c r="F25" s="22" t="s">
+      <c r="F25" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23">
+      <c r="G25" s="27"/>
+      <c r="H25" s="27">
         <v>47939</v>
       </c>
-      <c r="I25" s="24" t="s">
+      <c r="I25" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="J25" s="24" t="s">
+      <c r="J25" s="28" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="26" spans="3:10">
-      <c r="I26" s="20"/>
+      <c r="I26" s="24"/>
     </row>
     <row r="27" spans="3:10">
-      <c r="I27" s="20"/>
+      <c r="I27" s="24"/>
     </row>
     <row r="28" spans="3:10">
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="G28" s="21" t="s">
+      <c r="G28" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H28" s="25">
         <v>48304</v>
       </c>
-      <c r="I28" s="16" t="s">
+      <c r="I28" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="J28" s="20" t="s">
+      <c r="J28" s="24" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="29" spans="3:10">
-      <c r="F29" s="22" t="s">
+      <c r="F29" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="G29" s="23" t="s">
+      <c r="G29" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="H29" s="23">
+      <c r="H29" s="27">
         <v>48304</v>
       </c>
-      <c r="I29" s="24" t="s">
+      <c r="I29" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="J29" s="24" t="s">
+      <c r="J29" s="28" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="30" spans="3:10">
-      <c r="F30" s="22" t="s">
+      <c r="F30" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23">
+      <c r="G30" s="27"/>
+      <c r="H30" s="27">
         <v>48305</v>
       </c>
-      <c r="I30" s="24" t="s">
+      <c r="I30" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="J30" s="24" t="s">
+      <c r="J30" s="28" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="31" spans="3:10">
-      <c r="I31" s="20"/>
+      <c r="I31" s="24"/>
     </row>
     <row r="32" spans="3:10">
-      <c r="I32" s="20"/>
+      <c r="I32" s="24"/>
     </row>
     <row r="33" spans="3:10">
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="G33" s="21" t="s">
+      <c r="G33" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="H33" s="21">
+      <c r="H33" s="25">
         <v>48669</v>
       </c>
-      <c r="I33" s="16" t="s">
+      <c r="I33" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="J33" s="20" t="s">
+      <c r="J33" s="24" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="34" spans="3:10">
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="G34" s="23" t="s">
+      <c r="G34" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="27">
         <v>48669</v>
       </c>
-      <c r="I34" s="24" t="s">
+      <c r="I34" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="J34" s="24" t="s">
+      <c r="J34" s="28" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="35" spans="3:10">
-      <c r="F35" s="22" t="s">
+      <c r="F35" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23">
+      <c r="G35" s="27"/>
+      <c r="H35" s="27">
         <v>48670</v>
       </c>
-      <c r="I35" s="24" t="s">
+      <c r="I35" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="J35" s="24" t="s">
+      <c r="J35" s="28" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="36" spans="3:10">
-      <c r="I36" s="20"/>
+      <c r="I36" s="24"/>
     </row>
     <row r="37" spans="3:10">
-      <c r="I37" s="20"/>
+      <c r="I37" s="24"/>
     </row>
     <row r="38" spans="3:10">
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="G38" s="21" t="s">
+      <c r="G38" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="H38" s="21">
+      <c r="H38" s="25">
         <v>49034</v>
       </c>
-      <c r="I38" s="16" t="s">
+      <c r="I38" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="J38" s="20" t="s">
+      <c r="J38" s="24" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="39" spans="3:10">
-      <c r="F39" s="22"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="24"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5310,418 +5481,749 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.1428571428571" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="24.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="24.8571428571429" customWidth="1"/>
-    <col min="6" max="6" width="26.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="15.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="15.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="14.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="11.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="13.5714285714286" customWidth="1"/>
+    <col min="7" max="7" width="11.8571428571429" customWidth="1"/>
+    <col min="8" max="8" width="13.4285714285714" customWidth="1"/>
+    <col min="9" max="9" width="12.8571428571429" customWidth="1"/>
+    <col min="10" max="10" width="10.7142857142857" customWidth="1"/>
+    <col min="11" max="11" width="13.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" spans="1:6">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="30" spans="1:6">
-      <c r="A2" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>164</v>
+      <c r="H1" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F2" s="6">
-        <v>46844</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="30" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>204</v>
+        <v>209</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F3" s="6">
-        <v>46844</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="45" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>204</v>
+        <v>209</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F4" s="6">
-        <v>46844</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="30" spans="1:6">
-      <c r="A5" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="F5" s="9">
-        <v>47209</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="30" spans="1:6">
-      <c r="A6" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="F6" s="9">
-        <v>47209</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="45" spans="1:6">
-      <c r="A7" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="F7" s="9">
-        <v>47209</v>
-      </c>
-    </row>
-    <row r="8" ht="30" spans="1:6">
-      <c r="A8" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" s="12">
-        <v>47574</v>
-      </c>
-    </row>
-    <row r="9" ht="30" spans="1:6">
-      <c r="A9" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="F9" s="12">
-        <v>47574</v>
-      </c>
-    </row>
-    <row r="10" ht="45" spans="1:6">
-      <c r="A10" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="F10" s="12">
-        <v>47574</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="30" spans="1:6">
-      <c r="A11" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="F11" s="9">
-        <v>47939</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="30" spans="1:6">
-      <c r="A12" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="F12" s="9">
-        <v>47939</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="45" spans="1:6">
-      <c r="A13" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="F13" s="9">
-        <v>47939</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="1:6">
-      <c r="A14" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="15" ht="30" spans="1:6">
-      <c r="A15" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="F15" s="12">
-        <v>48305</v>
-      </c>
-    </row>
-    <row r="16" ht="45" spans="1:6">
-      <c r="A16" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="F16" s="12">
-        <v>48305</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="30" spans="1:6">
-      <c r="A17" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="F17" s="13">
-        <v>49034</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" ht="30" spans="1:6">
-      <c r="A18" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="F18" s="9">
-        <v>48670</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" ht="45" spans="1:6">
-      <c r="A19" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="F19" s="9">
-        <v>48670</v>
-      </c>
-    </row>
-    <row r="20" ht="45" spans="1:6">
-      <c r="A20" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="C20" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="F20" s="12">
-        <v>49034</v>
-      </c>
+      <c r="B7" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C7" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C8" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C11" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C13" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C14" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C15" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C16" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C17" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C18" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C19" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C20" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="C21" s="9">
+        <v>100000</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C22" s="9">
+        <v>100000</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C23" s="9">
+        <v>100000</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C24" s="11">
+        <v>100000</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C25" s="11">
+        <v>100000</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C26" s="13">
+        <v>10000</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C27" s="14">
+        <v>605501.57</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C28" s="13">
+        <v>200000.56</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="C29" s="17">
+        <v>200000.56</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H29" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/MU/MU user manual infoneo (2).xlsx
+++ b/MU/MU user manual infoneo (2).xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="246">
   <si>
     <t>Category</t>
   </si>
@@ -1800,6 +1800,9 @@
   </si>
   <si>
     <t>SameCutInEli25</t>
+  </si>
+  <si>
+    <t>MUDSBBJ20262027C</t>
   </si>
 </sst>
 </file>
@@ -2073,13 +2076,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.8"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="3" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2708,7 +2711,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2722,27 +2725,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2779,20 +2779,20 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -3447,947 +3447,947 @@
   <dimension ref="A1:Z71"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7142857142857" style="46" customWidth="1"/>
+    <col min="1" max="1" width="22.7142857142857" style="45" customWidth="1"/>
     <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="49.8571428571429" style="41" customWidth="1"/>
+    <col min="3" max="3" width="49.8571428571429" style="40" customWidth="1"/>
     <col min="4" max="4" width="46.8571428571429" customWidth="1"/>
     <col min="5" max="5" width="57.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:26">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="48" t="s">
+      <c r="C1" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="48" t="s">
+      <c r="D1" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
     </row>
     <row r="2" ht="135" spans="1:26">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="50" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="75" spans="1:26">
-      <c r="A3" s="53"/>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="52"/>
+      <c r="B3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="21"/>
+      <c r="E3" s="20"/>
     </row>
     <row r="4" ht="75" spans="1:26">
-      <c r="A4" s="53"/>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="52"/>
+      <c r="B4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="21"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="54"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
+      <c r="A5" s="53"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
     </row>
     <row r="6" ht="75" spans="1:26">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="57" t="s">
+      <c r="D6" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="50" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:26">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="21"/>
+      <c r="E7" s="20"/>
     </row>
     <row r="8" ht="56" customHeight="1" spans="1:26">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
     </row>
     <row r="9" ht="60" spans="1:26">
-      <c r="A9" s="53"/>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="52"/>
+      <c r="B9" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
     </row>
     <row r="10" ht="60" spans="1:26">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="57" t="s">
+      <c r="D10" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="20"/>
     </row>
     <row r="11" customFormat="1" ht="60" spans="1:26">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="51" t="s">
+      <c r="D11" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" customFormat="1" ht="45" spans="1:26">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
     </row>
     <row r="13" customFormat="1" ht="60" spans="1:26">
-      <c r="A13" s="53"/>
-      <c r="B13" s="21" t="s">
+      <c r="A13" s="52"/>
+      <c r="B13" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
     </row>
     <row r="14" customFormat="1" ht="60" spans="1:26">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="20"/>
     </row>
     <row r="15" ht="60" spans="1:26">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="21"/>
+      <c r="E15" s="20"/>
     </row>
     <row r="16" ht="45" spans="1:26">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="C16" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
     </row>
     <row r="17" ht="60" spans="1:5">
-      <c r="A17" s="53"/>
-      <c r="B17" s="21" t="s">
+      <c r="A17" s="52"/>
+      <c r="B17" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="52" t="s">
+      <c r="C17" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
     </row>
     <row r="18" customFormat="1" ht="60" spans="1:5">
-      <c r="A18" s="53" t="s">
+      <c r="A18" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="51" t="s">
+      <c r="C18" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
     </row>
     <row r="19" ht="60" spans="1:5">
-      <c r="A19" s="53" t="s">
+      <c r="A19" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="51" t="s">
+      <c r="C19" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="52" t="s">
+      <c r="D19" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="21"/>
+      <c r="E19" s="20"/>
     </row>
     <row r="20" ht="45" spans="1:5">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="52" t="s">
+      <c r="C20" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
     </row>
     <row r="21" ht="60" spans="1:5">
-      <c r="A21" s="53"/>
-      <c r="B21" s="21" t="s">
+      <c r="A21" s="52"/>
+      <c r="B21" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="52" t="s">
+      <c r="C21" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
     </row>
     <row r="22" ht="90" spans="1:5">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="52" t="s">
+      <c r="C22" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
     </row>
     <row r="23" ht="65" customHeight="1" spans="1:5">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="51" t="s">
+      <c r="C23" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="57" t="s">
+      <c r="D23" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="20" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" ht="65" customHeight="1" spans="1:5">
-      <c r="A24" s="53" t="s">
+      <c r="A24" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="57" t="s">
+      <c r="D24" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="21"/>
-    </row>
-    <row r="25" s="43" customFormat="1" ht="23.25" spans="1:5">
-      <c r="A25" s="58" t="s">
+      <c r="E24" s="20"/>
+    </row>
+    <row r="25" s="42" customFormat="1" ht="23.25" spans="1:5">
+      <c r="A25" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="60"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="59"/>
     </row>
     <row r="26" ht="90" spans="1:5">
-      <c r="A26" s="61" t="s">
+      <c r="A26" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="62" t="s">
+      <c r="B26" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="63" t="s">
+      <c r="C26" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="63" t="s">
+      <c r="D26" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="62"/>
+      <c r="E26" s="61"/>
     </row>
     <row r="27" ht="45" spans="1:5">
-      <c r="A27" s="61"/>
-      <c r="B27" s="21" t="s">
+      <c r="A27" s="60"/>
+      <c r="B27" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="52" t="s">
+      <c r="C27" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
     </row>
     <row r="28" ht="60" spans="1:5">
-      <c r="A28" s="64"/>
-      <c r="B28" s="21" t="s">
+      <c r="A28" s="63"/>
+      <c r="B28" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="52" t="s">
+      <c r="C28" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
     </row>
     <row r="29" ht="75" spans="1:5">
-      <c r="A29" s="53" t="s">
+      <c r="A29" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C29" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="65" t="s">
+      <c r="D29" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="21"/>
+      <c r="E29" s="20"/>
     </row>
     <row r="30" ht="45" spans="1:5">
-      <c r="A30" s="53" t="s">
+      <c r="A30" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="51" t="s">
+      <c r="C30" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
     </row>
     <row r="31" ht="55" customHeight="1" spans="1:5">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="51" t="s">
+      <c r="C31" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
     </row>
     <row r="32" ht="45" spans="1:5">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="51" t="s">
+      <c r="C32" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="52"/>
-      <c r="E32" s="21"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="20"/>
     </row>
     <row r="33" ht="45" spans="1:5">
-      <c r="A33" s="19"/>
-      <c r="B33" s="21" t="s">
+      <c r="A33" s="18"/>
+      <c r="B33" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="51" t="s">
+      <c r="C33" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="52"/>
-      <c r="E33" s="21"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="20"/>
     </row>
     <row r="34" ht="45" spans="1:5">
-      <c r="A34" s="19"/>
-      <c r="B34" s="21" t="s">
+      <c r="A34" s="18"/>
+      <c r="B34" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="52" t="s">
+      <c r="C34" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="52"/>
-      <c r="E34" s="21"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="20"/>
     </row>
     <row r="35" ht="75" spans="1:5">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="52" t="s">
+      <c r="C35" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="52" t="s">
+      <c r="D35" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="E35" s="21"/>
+      <c r="E35" s="20"/>
     </row>
     <row r="36" ht="75" spans="1:5">
-      <c r="A36" s="19"/>
-      <c r="B36" s="21" t="s">
+      <c r="A36" s="18"/>
+      <c r="B36" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="52" t="s">
+      <c r="C36" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
     </row>
     <row r="37" ht="45" spans="1:5">
-      <c r="A37" s="19"/>
-      <c r="B37" s="21" t="s">
+      <c r="A37" s="18"/>
+      <c r="B37" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="52" t="s">
+      <c r="C37" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
     </row>
     <row r="38" ht="60" spans="1:5">
-      <c r="A38" s="66" t="s">
+      <c r="A38" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="52" t="s">
+      <c r="C38" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="52"/>
-      <c r="E38" s="21" t="s">
+      <c r="D38" s="51"/>
+      <c r="E38" s="20" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="39" ht="60" spans="1:5">
-      <c r="A39" s="61"/>
-      <c r="B39" s="21" t="s">
+      <c r="A39" s="60"/>
+      <c r="B39" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="52" t="s">
+      <c r="C39" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="52"/>
-      <c r="E39" s="21"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="20"/>
     </row>
     <row r="40" ht="90" spans="1:5">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="52" t="s">
+      <c r="C40" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="52" t="s">
+      <c r="D40" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="E40" s="21"/>
+      <c r="E40" s="20"/>
     </row>
     <row r="41" ht="75" spans="1:5">
-      <c r="A41" s="61"/>
-      <c r="B41" s="21" t="s">
+      <c r="A41" s="60"/>
+      <c r="B41" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="52" t="s">
+      <c r="C41" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
     </row>
     <row r="42" ht="45" spans="1:5">
-      <c r="A42" s="64"/>
-      <c r="B42" s="21" t="s">
+      <c r="A42" s="63"/>
+      <c r="B42" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="52" t="s">
+      <c r="C42" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
     </row>
     <row r="43" ht="75" spans="1:5">
-      <c r="A43" s="53" t="s">
+      <c r="A43" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="52" t="s">
+      <c r="C43" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="D43" s="65" t="s">
+      <c r="D43" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="E43" s="21"/>
-    </row>
-    <row r="44" s="44" customFormat="1" ht="45" spans="1:5">
-      <c r="A44" s="50" t="s">
+      <c r="E43" s="20"/>
+    </row>
+    <row r="44" s="43" customFormat="1" ht="45" spans="1:5">
+      <c r="A44" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="67" t="s">
+      <c r="C44" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="E44" s="18"/>
+      <c r="E44" s="17"/>
     </row>
     <row r="45" ht="75" spans="1:5">
-      <c r="A45" s="19" t="s">
+      <c r="A45" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="52" t="s">
+      <c r="C45" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="52" t="s">
+      <c r="D45" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="E45" s="21"/>
+      <c r="E45" s="20"/>
     </row>
     <row r="46" ht="75" spans="1:5">
-      <c r="A46" s="19"/>
-      <c r="B46" s="21" t="s">
+      <c r="A46" s="18"/>
+      <c r="B46" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="52" t="s">
+      <c r="C46" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
     </row>
     <row r="47" ht="45" spans="1:5">
-      <c r="A47" s="19"/>
-      <c r="B47" s="21" t="s">
+      <c r="A47" s="18"/>
+      <c r="B47" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="52" t="s">
+      <c r="C47" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
     </row>
     <row r="48" ht="60" spans="1:5">
-      <c r="A48" s="19" t="s">
+      <c r="A48" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="21" t="s">
+      <c r="B48" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="52" t="s">
+      <c r="C48" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="D48" s="52"/>
-      <c r="E48" s="21" t="s">
+      <c r="D48" s="51"/>
+      <c r="E48" s="20" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="49" ht="60" spans="1:5">
-      <c r="A49" s="19"/>
-      <c r="B49" s="21" t="s">
+      <c r="A49" s="18"/>
+      <c r="B49" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="52" t="s">
+      <c r="C49" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="D49" s="52"/>
-      <c r="E49" s="21"/>
+      <c r="D49" s="51"/>
+      <c r="E49" s="20"/>
     </row>
     <row r="50" ht="90" spans="1:5">
-      <c r="A50" s="66" t="s">
+      <c r="A50" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="B50" s="21" t="s">
+      <c r="B50" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="52" t="s">
+      <c r="C50" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="D50" s="52" t="s">
+      <c r="D50" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="E50" s="21"/>
+      <c r="E50" s="20"/>
     </row>
     <row r="51" ht="75" spans="1:5">
-      <c r="A51" s="61"/>
-      <c r="B51" s="21" t="s">
+      <c r="A51" s="60"/>
+      <c r="B51" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C51" s="52" t="s">
+      <c r="C51" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
     </row>
     <row r="52" ht="45" spans="1:5">
-      <c r="A52" s="64"/>
-      <c r="B52" s="21" t="s">
+      <c r="A52" s="63"/>
+      <c r="B52" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="52" t="s">
+      <c r="C52" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
     </row>
     <row r="53" ht="75" spans="1:5">
-      <c r="A53" s="53" t="s">
+      <c r="A53" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="B53" s="21" t="s">
+      <c r="B53" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C53" s="52" t="s">
+      <c r="C53" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="D53" s="65" t="s">
+      <c r="D53" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="E53" s="21"/>
-    </row>
-    <row r="54" s="44" customFormat="1" ht="45" spans="1:5">
-      <c r="A54" s="50" t="s">
+      <c r="E53" s="20"/>
+    </row>
+    <row r="54" s="43" customFormat="1" ht="45" spans="1:5">
+      <c r="A54" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C54" s="67" t="s">
+      <c r="C54" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="D54" s="18" t="s">
+      <c r="D54" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="E54" s="18"/>
+      <c r="E54" s="17"/>
     </row>
     <row r="56" ht="75" spans="1:5">
-      <c r="A56" s="19" t="s">
+      <c r="A56" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="21" t="s">
+      <c r="B56" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C56" s="52" t="s">
+      <c r="C56" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="D56" s="52" t="s">
+      <c r="D56" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="E56" s="21"/>
+      <c r="E56" s="20"/>
     </row>
     <row r="57" ht="75" spans="1:5">
-      <c r="A57" s="19"/>
-      <c r="B57" s="21" t="s">
+      <c r="A57" s="18"/>
+      <c r="B57" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C57" s="52" t="s">
+      <c r="C57" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
     </row>
     <row r="58" ht="45" spans="1:5">
-      <c r="A58" s="19"/>
-      <c r="B58" s="21" t="s">
+      <c r="A58" s="18"/>
+      <c r="B58" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="52" t="s">
+      <c r="C58" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
     </row>
     <row r="59" ht="60" spans="1:5">
-      <c r="A59" s="19" t="s">
+      <c r="A59" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="B59" s="21" t="s">
+      <c r="B59" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="52" t="s">
+      <c r="C59" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="D59" s="52"/>
-      <c r="E59" s="21" t="s">
+      <c r="D59" s="51"/>
+      <c r="E59" s="20" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="60" ht="60" spans="1:5">
-      <c r="A60" s="19"/>
-      <c r="B60" s="21" t="s">
+      <c r="A60" s="18"/>
+      <c r="B60" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="52" t="s">
+      <c r="C60" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="52"/>
-      <c r="E60" s="21"/>
-    </row>
-    <row r="61" s="45" customFormat="1" ht="90" spans="1:5">
-      <c r="A61" s="68" t="s">
+      <c r="D60" s="51"/>
+      <c r="E60" s="20"/>
+    </row>
+    <row r="61" s="44" customFormat="1" ht="90" spans="1:5">
+      <c r="A61" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="B61" s="69" t="s">
+      <c r="B61" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="70" t="s">
+      <c r="C61" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="D61" s="70" t="s">
+      <c r="D61" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="E61" s="69"/>
-    </row>
-    <row r="62" s="45" customFormat="1" ht="75" spans="1:5">
-      <c r="A62" s="71"/>
-      <c r="B62" s="69" t="s">
+      <c r="E61" s="68"/>
+    </row>
+    <row r="62" s="44" customFormat="1" ht="75" spans="1:5">
+      <c r="A62" s="70"/>
+      <c r="B62" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="C62" s="70" t="s">
+      <c r="C62" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="D62" s="69"/>
-      <c r="E62" s="69"/>
-    </row>
-    <row r="63" s="45" customFormat="1" ht="45" spans="1:5">
-      <c r="A63" s="72"/>
-      <c r="B63" s="69" t="s">
+      <c r="D62" s="68"/>
+      <c r="E62" s="68"/>
+    </row>
+    <row r="63" s="44" customFormat="1" ht="45" spans="1:5">
+      <c r="A63" s="71"/>
+      <c r="B63" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="70" t="s">
+      <c r="C63" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="D63" s="69"/>
-      <c r="E63" s="69"/>
+      <c r="D63" s="68"/>
+      <c r="E63" s="68"/>
     </row>
     <row r="64" ht="75" spans="1:5">
-      <c r="A64" s="53" t="s">
+      <c r="A64" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="B64" s="21" t="s">
+      <c r="B64" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C64" s="52" t="s">
+      <c r="C64" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="D64" s="65" t="s">
+      <c r="D64" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="E64" s="21"/>
-    </row>
-    <row r="65" s="44" customFormat="1" ht="45" spans="1:5">
-      <c r="A65" s="50" t="s">
+      <c r="E64" s="20"/>
+    </row>
+    <row r="65" s="43" customFormat="1" ht="45" spans="1:5">
+      <c r="A65" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="B65" s="18" t="s">
+      <c r="B65" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C65" s="67" t="s">
+      <c r="C65" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="D65" s="18" t="s">
+      <c r="D65" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="E65" s="18"/>
-    </row>
-    <row r="66" s="43" customFormat="1" ht="23.25" spans="1:5">
-      <c r="A66" s="73" t="s">
+      <c r="E65" s="17"/>
+    </row>
+    <row r="66" s="42" customFormat="1" ht="23.25" spans="1:5">
+      <c r="A66" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="B66" s="73"/>
-      <c r="C66" s="73"/>
-      <c r="D66" s="73"/>
-      <c r="E66" s="73"/>
+      <c r="B66" s="72"/>
+      <c r="C66" s="72"/>
+      <c r="D66" s="72"/>
+      <c r="E66" s="72"/>
     </row>
     <row r="67" ht="90" spans="1:5">
-      <c r="A67" s="61" t="s">
+      <c r="A67" s="60" t="s">
         <v>100</v>
       </c>
-      <c r="B67" s="62" t="s">
+      <c r="B67" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="C67" s="63" t="s">
+      <c r="C67" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="D67" s="63" t="s">
+      <c r="D67" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="E67" s="62"/>
+      <c r="E67" s="61"/>
     </row>
     <row r="68" ht="45" spans="1:5">
-      <c r="A68" s="61"/>
-      <c r="B68" s="21" t="s">
+      <c r="A68" s="60"/>
+      <c r="B68" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="52" t="s">
+      <c r="C68" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20"/>
     </row>
     <row r="69" ht="60" spans="1:5">
-      <c r="A69" s="64"/>
-      <c r="B69" s="21" t="s">
+      <c r="A69" s="63"/>
+      <c r="B69" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C69" s="52" t="s">
+      <c r="C69" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
+      <c r="D69" s="20"/>
+      <c r="E69" s="20"/>
     </row>
     <row r="70" ht="75" spans="1:5">
-      <c r="A70" s="53" t="s">
+      <c r="A70" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="21" t="s">
+      <c r="B70" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="52" t="s">
+      <c r="C70" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="D70" s="65" t="s">
+      <c r="D70" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="E70" s="21"/>
+      <c r="E70" s="20"/>
     </row>
     <row r="71" ht="45" spans="1:5">
-      <c r="A71" s="53" t="s">
+      <c r="A71" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="21" t="s">
+      <c r="B71" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C71" s="51" t="s">
+      <c r="C71" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4422,84 +4422,84 @@
   <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="42" style="36" customWidth="1"/>
-    <col min="2" max="2" width="42.8571428571429" style="21" customWidth="1"/>
-    <col min="3" max="4" width="9.14285714285714" style="21"/>
+    <col min="1" max="1" width="42" style="35" customWidth="1"/>
+    <col min="2" max="2" width="42.8571428571429" style="20" customWidth="1"/>
+    <col min="3" max="4" width="9.14285714285714" style="20"/>
     <col min="5" max="5" width="43.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:17">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:17">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="38">
+      <c r="B3" s="37">
         <v>3115502.69</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
       <c r="E3" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:17">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="38">
+      <c r="B4" s="37">
         <v>2</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
       <c r="E4" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="5" ht="33" customHeight="1" spans="1:17">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="37">
         <v>115000</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
       <c r="E5" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:17">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="37">
         <v>14200</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
       <c r="E6" t="s">
         <v>114</v>
       </c>
-      <c r="N6" s="40">
+      <c r="N6" s="39">
         <v>15000</v>
       </c>
       <c r="P6">
@@ -4507,15 +4507,15 @@
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:17">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="37">
         <f>B5-B6</f>
         <v>100800</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
       <c r="E7" t="s">
         <v>116</v>
       </c>
@@ -4530,19 +4530,19 @@
       </c>
     </row>
     <row r="8" ht="71" customHeight="1" spans="1:17">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="37">
         <f>3%*B7</f>
         <v>3024</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="41" t="s">
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="N8" s="40">
+      <c r="N8" s="39">
         <v>20453</v>
       </c>
       <c r="P8">
@@ -4550,15 +4550,15 @@
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:17">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="37">
         <f>B7-B8</f>
         <v>97776</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
       <c r="E9" t="s">
         <v>120</v>
       </c>
@@ -4570,19 +4570,19 @@
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:17">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="38">
+      <c r="B10" s="37">
         <f>15%*B3</f>
         <v>467325.4035</v>
       </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
       <c r="E10" t="s">
         <v>122</v>
       </c>
-      <c r="K10" s="42">
+      <c r="K10" s="41">
         <v>38697.18</v>
       </c>
       <c r="N10">
@@ -4593,19 +4593,19 @@
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:17">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="38">
+      <c r="B11" s="37">
         <f>75%*B9</f>
         <v>73332</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
       <c r="E11" t="s">
         <v>124</v>
       </c>
-      <c r="K11" s="42">
+      <c r="K11" s="41">
         <v>47062.7</v>
       </c>
       <c r="N11">
@@ -4616,37 +4616,37 @@
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:17">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="37">
         <f>B11</f>
         <v>73332</v>
       </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:17">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
       <c r="E13" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="14" ht="33" customHeight="1" spans="1:17">
-      <c r="A14" s="39" t="s">
+      <c r="A14" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="38">
+      <c r="B14" s="37">
         <f>B12-B13</f>
         <v>73332</v>
       </c>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -4687,199 +4687,199 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-    </row>
-    <row r="2" s="30" customFormat="1" spans="1:14">
-      <c r="A2" s="31" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+    </row>
+    <row r="2" s="29" customFormat="1" spans="1:14">
+      <c r="A2" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="N2" s="30">
+      <c r="N2" s="29">
         <v>832.88</v>
       </c>
     </row>
-    <row r="3" s="30" customFormat="1" spans="1:14">
-      <c r="A3" s="32">
+    <row r="3" s="29" customFormat="1" spans="1:14">
+      <c r="A3" s="31">
         <v>46174</v>
       </c>
-      <c r="B3" s="32">
+      <c r="B3" s="31">
         <v>46477</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C3" s="32">
         <f>B3-A3+1</f>
         <v>304</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="33">
         <f>1%*E3*C3/365</f>
         <v>832.876712328767</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="32">
         <v>100000</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3" s="32">
         <f>D3*18%</f>
         <v>149.917808219178</v>
       </c>
-      <c r="G3" s="33">
+      <c r="G3" s="32">
         <f>D3+F3</f>
         <v>982.794520547945</v>
       </c>
     </row>
-    <row r="4" s="30" customFormat="1"/>
+    <row r="4" s="29" customFormat="1"/>
     <row r="7" spans="1:14">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="30" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="32">
+      <c r="A9" s="31">
         <v>46072</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="31">
         <v>46112</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="32">
         <f>B9-A9+1</f>
         <v>41</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="33">
         <f>0.25%*E9*C9/365</f>
         <v>28.0821917808219</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="32">
         <v>100000</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="32">
         <f>D9*18%</f>
         <v>5.05479452054795</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="32">
         <f>D9+F9</f>
         <v>33.1369863013699</v>
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="F14" s="31" t="s">
+      <c r="F14" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="G14" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="H14" s="31" t="s">
+      <c r="H14" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="I14" s="31" t="s">
+      <c r="I14" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="J14" s="31" t="s">
+      <c r="J14" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="K14" s="31" t="s">
+      <c r="K14" s="30" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="32">
         <v>10000</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="31">
         <v>46082</v>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="31">
         <v>46477</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="32">
         <f>DATEDIF(C15,D15,"d")+1</f>
         <v>396</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="34">
         <v>0.01</v>
       </c>
-      <c r="G15" s="33">
+      <c r="G15" s="32">
         <f>IF(K15="Closed",0,B15*F15*(E15/365))</f>
         <v>108.493150684932</v>
       </c>
-      <c r="H15" s="33">
+      <c r="H15" s="32">
         <f>G15*9%</f>
         <v>9.76438356164384</v>
       </c>
-      <c r="I15" s="33">
+      <c r="I15" s="32">
         <f>18%*G15</f>
         <v>19.5287671232877</v>
       </c>
-      <c r="J15" s="33">
+      <c r="J15" s="32">
         <f>G15+H15+I15</f>
         <v>137.786301369863</v>
       </c>
-      <c r="K15" s="33" t="s">
+      <c r="K15" s="32" t="s">
         <v>150</v>
       </c>
     </row>
@@ -4915,559 +4915,559 @@
       </c>
     </row>
     <row r="2" spans="3:10">
-      <c r="C2" s="18"/>
-      <c r="D2" s="18" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="18" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="3" spans="3:10">
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="J3" s="19"/>
+      <c r="J3" s="18"/>
     </row>
     <row r="4" spans="3:10">
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="22">
         <v>46386</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="I4" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="J4" s="19"/>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" spans="3:10">
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="22">
         <v>46477</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="J5" s="19"/>
+      <c r="J5" s="18"/>
     </row>
     <row r="6" spans="3:10">
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="22">
         <v>46568</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="J6" s="19"/>
+      <c r="J6" s="18"/>
     </row>
     <row r="7" spans="3:10">
-      <c r="C7" s="24"/>
-      <c r="I7" s="24"/>
+      <c r="C7" s="23"/>
+      <c r="I7" s="23"/>
     </row>
     <row r="8" spans="3:10">
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="24">
         <v>46843</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="J8" s="23" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="9" spans="3:10">
-      <c r="C9" s="24"/>
-      <c r="F9" s="26" t="s">
+      <c r="C9" s="23"/>
+      <c r="F9" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="G9" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="26">
         <v>46843</v>
       </c>
-      <c r="I9" s="28" t="s">
+      <c r="I9" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="J9" s="28" t="s">
+      <c r="J9" s="27" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="10" spans="3:10">
-      <c r="C10" s="24"/>
-      <c r="F10" s="26" t="s">
+      <c r="C10" s="23"/>
+      <c r="F10" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27">
+      <c r="G10" s="26"/>
+      <c r="H10" s="26">
         <v>46844</v>
       </c>
-      <c r="I10" s="28" t="s">
+      <c r="I10" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="J10" s="28" t="s">
+      <c r="J10" s="27" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="11" spans="3:10">
-      <c r="C11" s="24"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="24"/>
+      <c r="C11" s="23"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="23"/>
     </row>
     <row r="12" spans="3:10">
-      <c r="C12" s="24"/>
-      <c r="I12" s="24"/>
+      <c r="C12" s="23"/>
+      <c r="I12" s="23"/>
     </row>
     <row r="13" spans="3:10">
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="24">
         <v>47208</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="23" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="14" spans="3:10">
-      <c r="C14" s="24"/>
-      <c r="F14" s="26" t="s">
+      <c r="C14" s="23"/>
+      <c r="F14" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="G14" s="27" t="s">
+      <c r="G14" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="26">
         <v>47208</v>
       </c>
-      <c r="I14" s="28" t="s">
+      <c r="I14" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="J14" s="28" t="s">
+      <c r="J14" s="27" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="15" spans="3:10">
-      <c r="C15" s="24"/>
-      <c r="F15" s="26" t="s">
+      <c r="C15" s="23"/>
+      <c r="F15" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27">
+      <c r="G15" s="26"/>
+      <c r="H15" s="26">
         <v>47209</v>
       </c>
-      <c r="I15" s="28" t="s">
+      <c r="I15" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="J15" s="28" t="s">
+      <c r="J15" s="27" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="16" spans="3:10">
-      <c r="C16" s="24"/>
-      <c r="I16" s="24"/>
+      <c r="C16" s="23"/>
+      <c r="I16" s="23"/>
     </row>
     <row r="17" spans="3:10">
-      <c r="C17" s="24"/>
-      <c r="I17" s="24"/>
+      <c r="C17" s="23"/>
+      <c r="I17" s="23"/>
     </row>
     <row r="18" spans="3:10">
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="F18" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="24">
         <v>47573</v>
       </c>
-      <c r="I18" s="20" t="s">
+      <c r="I18" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="J18" s="24" t="s">
+      <c r="J18" s="23" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="24"/>
-      <c r="F19" s="26" t="s">
+      <c r="C19" s="23"/>
+      <c r="F19" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="G19" s="27" t="s">
+      <c r="G19" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="26">
         <v>47573</v>
       </c>
-      <c r="I19" s="28" t="s">
+      <c r="I19" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="J19" s="28" t="s">
+      <c r="J19" s="27" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="20" spans="3:10">
-      <c r="C20" s="24"/>
-      <c r="F20" s="26" t="s">
+      <c r="C20" s="23"/>
+      <c r="F20" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27">
+      <c r="G20" s="26"/>
+      <c r="H20" s="26">
         <v>47574</v>
       </c>
-      <c r="I20" s="28" t="s">
+      <c r="I20" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="J20" s="28" t="s">
+      <c r="J20" s="27" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="24"/>
-      <c r="I21" s="24"/>
+      <c r="C21" s="23"/>
+      <c r="I21" s="23"/>
     </row>
     <row r="22" spans="3:10">
-      <c r="C22" s="24"/>
-      <c r="I22" s="24"/>
+      <c r="C22" s="23"/>
+      <c r="I22" s="23"/>
     </row>
     <row r="23" spans="3:10">
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="F23" s="21" t="s">
+      <c r="F23" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="H23" s="25">
+      <c r="H23" s="24">
         <v>47938</v>
       </c>
-      <c r="I23" s="20" t="s">
+      <c r="I23" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="J23" s="24" t="s">
+      <c r="J23" s="23" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="24" spans="3:10">
-      <c r="F24" s="26" t="s">
+      <c r="F24" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="G24" s="27" t="s">
+      <c r="G24" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="H24" s="27">
+      <c r="H24" s="26">
         <v>47938</v>
       </c>
-      <c r="I24" s="28" t="s">
+      <c r="I24" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="J24" s="28" t="s">
+      <c r="J24" s="27" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="25" spans="3:10">
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27">
+      <c r="G25" s="26"/>
+      <c r="H25" s="26">
         <v>47939</v>
       </c>
-      <c r="I25" s="28" t="s">
+      <c r="I25" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="J25" s="28" t="s">
+      <c r="J25" s="27" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="26" spans="3:10">
-      <c r="I26" s="24"/>
+      <c r="I26" s="23"/>
     </row>
     <row r="27" spans="3:10">
-      <c r="I27" s="24"/>
+      <c r="I27" s="23"/>
     </row>
     <row r="28" spans="3:10">
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="D28" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="E28" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="F28" s="21" t="s">
+      <c r="F28" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="G28" s="25" t="s">
+      <c r="G28" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="H28" s="25">
+      <c r="H28" s="24">
         <v>48304</v>
       </c>
-      <c r="I28" s="20" t="s">
+      <c r="I28" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="J28" s="24" t="s">
+      <c r="J28" s="23" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="29" spans="3:10">
-      <c r="F29" s="26" t="s">
+      <c r="F29" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="G29" s="27" t="s">
+      <c r="G29" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="H29" s="27">
+      <c r="H29" s="26">
         <v>48304</v>
       </c>
-      <c r="I29" s="28" t="s">
+      <c r="I29" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="J29" s="28" t="s">
+      <c r="J29" s="27" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="30" spans="3:10">
-      <c r="F30" s="26" t="s">
+      <c r="F30" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27">
+      <c r="G30" s="26"/>
+      <c r="H30" s="26">
         <v>48305</v>
       </c>
-      <c r="I30" s="28" t="s">
+      <c r="I30" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="J30" s="28" t="s">
+      <c r="J30" s="27" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="31" spans="3:10">
-      <c r="I31" s="24"/>
+      <c r="I31" s="23"/>
     </row>
     <row r="32" spans="3:10">
-      <c r="I32" s="24"/>
+      <c r="I32" s="23"/>
     </row>
     <row r="33" spans="3:10">
-      <c r="C33" s="20" t="s">
+      <c r="C33" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="F33" s="21" t="s">
+      <c r="F33" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="G33" s="25" t="s">
+      <c r="G33" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="H33" s="25">
+      <c r="H33" s="24">
         <v>48669</v>
       </c>
-      <c r="I33" s="20" t="s">
+      <c r="I33" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="J33" s="24" t="s">
+      <c r="J33" s="23" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="34" spans="3:10">
-      <c r="F34" s="26" t="s">
+      <c r="F34" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="G34" s="27" t="s">
+      <c r="G34" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="H34" s="27">
+      <c r="H34" s="26">
         <v>48669</v>
       </c>
-      <c r="I34" s="28" t="s">
+      <c r="I34" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="J34" s="28" t="s">
+      <c r="J34" s="27" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="35" spans="3:10">
-      <c r="F35" s="26" t="s">
+      <c r="F35" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27">
+      <c r="G35" s="26"/>
+      <c r="H35" s="26">
         <v>48670</v>
       </c>
-      <c r="I35" s="28" t="s">
+      <c r="I35" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="J35" s="28" t="s">
+      <c r="J35" s="27" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="36" spans="3:10">
-      <c r="I36" s="24"/>
+      <c r="I36" s="23"/>
     </row>
     <row r="37" spans="3:10">
-      <c r="I37" s="24"/>
+      <c r="I37" s="23"/>
     </row>
     <row r="38" spans="3:10">
-      <c r="C38" s="20" t="s">
+      <c r="C38" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D38" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="F38" s="21" t="s">
+      <c r="F38" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="G38" s="25" t="s">
+      <c r="G38" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="H38" s="25">
+      <c r="H38" s="24">
         <v>49034</v>
       </c>
-      <c r="I38" s="20" t="s">
+      <c r="I38" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="J38" s="24" t="s">
+      <c r="J38" s="23" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="39" spans="3:10">
-      <c r="F39" s="26"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="29"/>
-      <c r="J39" s="28"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5481,7 +5481,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.4285714285714" customWidth="1"/>
@@ -5542,18 +5542,20 @@
       <c r="C2" s="4">
         <v>100000</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
@@ -5565,447 +5567,479 @@
       <c r="C3" s="4">
         <v>100000</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>100000</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>100000</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>100000</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+      <c r="G6" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>100000</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
+      <c r="G7" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>100000</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
+      <c r="G8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>100000</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
+      <c r="G9" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>100000</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
+      <c r="G10" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>100000</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
+      <c r="G11" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>100000</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
+      <c r="G12" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>100000</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
+      <c r="G13" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <v>100000</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
+      <c r="G14" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="6">
         <v>100000</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
+      <c r="G15" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="6">
         <v>100000</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
+      <c r="G16" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>100000</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
+      <c r="G17" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="6">
         <v>100000</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
+      <c r="G18" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="6">
         <v>100000</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
+      <c r="G19" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="6">
         <v>100000</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
+      <c r="G20" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="8" t="s">
@@ -6017,20 +6051,22 @@
       <c r="C21" s="9">
         <v>100000</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
+      <c r="G21" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="8" t="s">
@@ -6042,20 +6078,20 @@
       <c r="C22" s="9">
         <v>100000</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="8" t="s">
@@ -6067,20 +6103,20 @@
       <c r="C23" s="9">
         <v>100000</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="10" t="s">
@@ -6092,18 +6128,18 @@
       <c r="C24" s="11">
         <v>100000</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="10" t="s">
@@ -6115,18 +6151,18 @@
       <c r="C25" s="11">
         <v>100000</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="12" t="s">
@@ -6135,21 +6171,21 @@
       <c r="B26" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="4">
         <v>10000</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="12" t="s">
@@ -6158,21 +6194,21 @@
       <c r="B27" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13">
         <v>605501.57</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="12" t="s">
@@ -6181,44 +6217,49 @@
       <c r="B28" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="C28" s="13">
+      <c r="C28" s="4">
         <v>200000.56</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="16">
         <v>200000.56</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>245</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H29" etc:filterBottomFollowUsedRange="0">

--- a/MU/MU user manual infoneo (2).xlsx
+++ b/MU/MU user manual infoneo (2).xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="12180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Flow" sheetId="1" r:id="rId1"/>
@@ -5484,7 +5484,7 @@
   <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="15.2857142857143" customWidth="1"/>
     <col min="3" max="3" width="14.2857142857143" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>

--- a/MU/MU user manual infoneo (2).xlsx
+++ b/MU/MU user manual infoneo (2).xlsx
@@ -5484,7 +5484,7 @@
   <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="14.1428571428571" customWidth="1"/>
     <col min="2" max="2" width="15.2857142857143" customWidth="1"/>
     <col min="3" max="3" width="14.2857142857143" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>

--- a/MU/MU user manual infoneo (2).xlsx
+++ b/MU/MU user manual infoneo (2).xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" activeTab="4"/>
+    <workbookView windowWidth="24000" windowHeight="9600" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Flow" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet2!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet2!$A$1:$H$32</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="250">
   <si>
     <t>Category</t>
   </si>
@@ -1703,6 +1703,9 @@
     <t>2627CR703</t>
   </si>
   <si>
+    <t>Claim 2 - IA</t>
+  </si>
+  <si>
     <t>NPA</t>
   </si>
   <si>
@@ -1712,6 +1715,12 @@
     <t>2627CR704</t>
   </si>
   <si>
+    <t>Claim 2</t>
+  </si>
+  <si>
+    <t>Claim 3</t>
+  </si>
+  <si>
     <t>2627CR705</t>
   </si>
   <si>
@@ -1730,6 +1739,9 @@
     <t>2627CR710</t>
   </si>
   <si>
+    <t>stn</t>
+  </si>
+  <si>
     <t>2627CR711</t>
   </si>
   <si>
@@ -1742,6 +1754,9 @@
     <t>2627CR714</t>
   </si>
   <si>
+    <t>IA</t>
+  </si>
+  <si>
     <t>2627CR715</t>
   </si>
   <si>
@@ -1764,9 +1779,6 @@
   </si>
   <si>
     <t>2627CR721</t>
-  </si>
-  <si>
-    <t>IA</t>
   </si>
   <si>
     <t>2627CR722</t>
@@ -4426,6 +4438,7 @@
     <col min="2" max="2" width="42.8571428571429" style="20" customWidth="1"/>
     <col min="3" max="4" width="9.14285714285714" style="20"/>
     <col min="5" max="5" width="43.1428571428571" customWidth="1"/>
+    <col min="7" max="7" width="10.5714285714286"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:17">
@@ -4453,7 +4466,7 @@
         <v>107</v>
       </c>
       <c r="B3" s="37">
-        <v>3115502.69</v>
+        <v>33000000</v>
       </c>
       <c r="C3" s="37"/>
       <c r="D3" s="37"/>
@@ -4479,7 +4492,7 @@
         <v>111</v>
       </c>
       <c r="B5" s="37">
-        <v>115000</v>
+        <v>1200001</v>
       </c>
       <c r="C5" s="37"/>
       <c r="D5" s="37"/>
@@ -4491,9 +4504,7 @@
       <c r="A6" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="37">
-        <v>14200</v>
-      </c>
+      <c r="B6" s="37"/>
       <c r="C6" s="37"/>
       <c r="D6" s="37"/>
       <c r="E6" t="s">
@@ -4512,7 +4523,7 @@
       </c>
       <c r="B7" s="37">
         <f>B5-B6</f>
-        <v>100800</v>
+        <v>1200001</v>
       </c>
       <c r="C7" s="37"/>
       <c r="D7" s="37"/>
@@ -4535,7 +4546,7 @@
       </c>
       <c r="B8" s="37">
         <f>3%*B7</f>
-        <v>3024</v>
+        <v>36000.03</v>
       </c>
       <c r="C8" s="37"/>
       <c r="D8" s="37"/>
@@ -4555,7 +4566,7 @@
       </c>
       <c r="B9" s="37">
         <f>B7-B8</f>
-        <v>97776</v>
+        <v>1164000.97</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -4575,7 +4586,7 @@
       </c>
       <c r="B10" s="37">
         <f>15%*B3</f>
-        <v>467325.4035</v>
+        <v>4950000</v>
       </c>
       <c r="C10" s="37"/>
       <c r="D10" s="37"/>
@@ -4598,7 +4609,7 @@
       </c>
       <c r="B11" s="37">
         <f>75%*B9</f>
-        <v>73332</v>
+        <v>873000.7275</v>
       </c>
       <c r="C11" s="37"/>
       <c r="D11" s="37"/>
@@ -4621,7 +4632,7 @@
       </c>
       <c r="B12" s="37">
         <f>B11</f>
-        <v>73332</v>
+        <v>873000.7275</v>
       </c>
       <c r="C12" s="37"/>
       <c r="D12" s="37"/>
@@ -4643,7 +4654,7 @@
       </c>
       <c r="B14" s="37">
         <f>B12-B13</f>
-        <v>73332</v>
+        <v>873000.7275</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -5480,7 +5491,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
@@ -5490,9 +5501,9 @@
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="11.7142857142857" customWidth="1"/>
     <col min="6" max="6" width="13.5714285714286" customWidth="1"/>
-    <col min="7" max="7" width="11.8571428571429" customWidth="1"/>
-    <col min="8" max="8" width="13.4285714285714" customWidth="1"/>
-    <col min="9" max="9" width="12.8571428571429" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="14.4285714285714" customWidth="1"/>
+    <col min="9" max="9" width="15.8571428571429" customWidth="1"/>
     <col min="10" max="10" width="10.7142857142857" customWidth="1"/>
     <col min="11" max="11" width="13.4285714285714" customWidth="1"/>
   </cols>
@@ -5582,7 +5593,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" hidden="1" spans="1:11">
       <c r="A4" s="5" t="s">
         <v>208</v>
       </c>
@@ -5599,172 +5610,182 @@
         <v>209</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" hidden="1" spans="1:11">
       <c r="A5" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C5" s="6">
         <v>100000</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>217</v>
+      </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" hidden="1" spans="1:11">
       <c r="A6" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C6" s="6">
         <v>100000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>217</v>
+      </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" hidden="1" spans="1:11">
       <c r="A7" s="5" t="s">
         <v>208</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C7" s="6">
         <v>100000</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" hidden="1" spans="1:11">
       <c r="A8" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C8" s="6">
         <v>100000</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" hidden="1" spans="1:11">
       <c r="A9" s="5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C9" s="6">
         <v>100000</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" hidden="1" spans="1:11">
       <c r="A10" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C10" s="6">
         <v>100000</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -5773,319 +5794,325 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C11" s="6">
         <v>100000</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="H11" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>224</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" hidden="1" spans="1:11">
       <c r="A12" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C12" s="6">
         <v>100000</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" hidden="1" spans="1:11">
       <c r="A13" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C13" s="6">
         <v>100000</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" hidden="1" spans="1:11">
       <c r="A14" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C14" s="6">
         <v>100000</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" hidden="1" spans="1:11">
       <c r="A15" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C15" s="6">
         <v>100000</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="H15" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>229</v>
+      </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" hidden="1" spans="1:11">
       <c r="A16" s="5" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C16" s="6">
         <v>100000</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="H16" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>229</v>
+      </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" hidden="1" spans="1:11">
       <c r="A17" s="5" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C17" s="6">
         <v>100000</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" hidden="1" spans="1:11">
       <c r="A18" s="5" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C18" s="6">
         <v>100000</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" hidden="1" spans="1:11">
       <c r="A19" s="5" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C19" s="6">
         <v>100000</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" hidden="1" spans="1:11">
       <c r="A20" s="5" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C20" s="6">
         <v>100000</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" hidden="1" spans="1:11">
       <c r="A21" s="8" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C21" s="9">
         <v>100000</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" hidden="1" spans="1:11">
       <c r="A22" s="8" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C22" s="9">
         <v>100000</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -6093,24 +6120,24 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" hidden="1" spans="1:11">
       <c r="A23" s="8" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C23" s="9">
         <v>100000</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -6118,21 +6145,21 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" hidden="1" spans="1:11">
       <c r="A24" s="10" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C24" s="11">
         <v>100000</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -6141,21 +6168,21 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" hidden="1" spans="1:11">
       <c r="A25" s="10" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C25" s="11">
         <v>100000</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -6164,18 +6191,18 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" hidden="1" spans="1:11">
       <c r="A26" s="12" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C26" s="4">
         <v>10000</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>209</v>
@@ -6183,22 +6210,24 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+      <c r="I26" s="2" t="s">
+        <v>229</v>
+      </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" hidden="1" spans="1:11">
       <c r="A27" s="12" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C27" s="13">
         <v>605501.57</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>209</v>
@@ -6206,22 +6235,24 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
+      <c r="I27" s="2" t="s">
+        <v>213</v>
+      </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" hidden="1" spans="1:11">
       <c r="A28" s="12" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C28" s="4">
         <v>200000.56</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>209</v>
@@ -6229,22 +6260,24 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
+      <c r="I28" s="2" t="s">
+        <v>213</v>
+      </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" hidden="1" spans="1:11">
       <c r="A29" s="14" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C29" s="16">
         <v>200000.56</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>209</v>
@@ -6252,17 +6285,34 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
+      <c r="I29" s="2" t="s">
+        <v>213</v>
+      </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="30" hidden="1"/>
+    <row r="31" hidden="1"/>
+    <row r="32" hidden="1" spans="1:11">
       <c r="A32" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H29" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H32" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="2627CR710"/>
+        <filter val="2627CR701"/>
+        <filter val="2627CR702"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters blank="1">
+        <filter val="NPA"/>
+        <filter val="Stn"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/MU/MU user manual infoneo (2).xlsx
+++ b/MU/MU user manual infoneo (2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600" activeTab="1"/>
+    <workbookView windowWidth="24000" windowHeight="9600" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Flow" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="BP - CG fee Calculatons" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet2!$A$1:$H$32</definedName>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="287">
   <si>
     <t>Category</t>
   </si>
@@ -1815,6 +1816,126 @@
   </si>
   <si>
     <t>MUDSBBJ20262027C</t>
+  </si>
+  <si>
+    <t>Access</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Outout</t>
+  </si>
+  <si>
+    <t>base period</t>
+  </si>
+  <si>
+    <t>Claim</t>
+  </si>
+  <si>
+    <t>MLI Cre</t>
+  </si>
+  <si>
+    <t>Upload
+Send for app</t>
+  </si>
+  <si>
+    <t>Cp1</t>
+  </si>
+  <si>
+    <t>MLI app</t>
+  </si>
+  <si>
+    <t>App 
+Reject</t>
+  </si>
+  <si>
+    <t>App</t>
+  </si>
+  <si>
+    <t>NCGTC</t>
+  </si>
+  <si>
+    <t>Reject</t>
+  </si>
+  <si>
+    <t>MLI cre</t>
+  </si>
+  <si>
+    <t>Can reupload</t>
+  </si>
+  <si>
+    <t>cp2</t>
+  </si>
+  <si>
+    <t>claim 1</t>
+  </si>
+  <si>
+    <t>NCGTC cre</t>
+  </si>
+  <si>
+    <t>App 
+Reject
+Return</t>
+  </si>
+  <si>
+    <t>NCGTC app</t>
+  </si>
+  <si>
+    <t>1 MLI Can not reupload</t>
+  </si>
+  <si>
+    <t>Return</t>
+  </si>
+  <si>
+    <t>MLI Can reupload
+Redirect to MLI</t>
+  </si>
+  <si>
+    <t>App 
+Reject
+Return
+Onhold</t>
+  </si>
+  <si>
+    <t>Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Redirected To NCGTC cre
+</t>
+  </si>
+  <si>
+    <t>For claim settlement</t>
+  </si>
+  <si>
+    <t>main main</t>
+  </si>
+  <si>
+    <t>Cp2</t>
+  </si>
+  <si>
+    <t>case 1</t>
+  </si>
+  <si>
+    <t>1st upload claim then Update CG</t>
+  </si>
+  <si>
+    <t>case 2</t>
+  </si>
+  <si>
+    <t>1st upload Update CG then claim</t>
+  </si>
+  <si>
+    <t>case 3</t>
+  </si>
+  <si>
+    <t>1st upload claim then Settle then upload , Update CG</t>
+  </si>
+  <si>
+    <t>case 4</t>
+  </si>
+  <si>
+    <t>1st Update CG , then claim , settle , next CP upload CG for same loan ac</t>
   </si>
 </sst>
 </file>
@@ -2082,13 +2203,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2723,9 +2844,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2737,21 +2867,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2791,20 +2921,20 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="180" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -3459,947 +3589,947 @@
   <dimension ref="A1:Z71"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7142857142857" style="45" customWidth="1"/>
+    <col min="1" max="1" width="22.7142857142857" style="48" customWidth="1"/>
     <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="49.8571428571429" style="40" customWidth="1"/>
+    <col min="3" max="3" width="49.8571428571429" style="43" customWidth="1"/>
     <col min="4" max="4" width="46.8571428571429" customWidth="1"/>
     <col min="5" max="5" width="57.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:26">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+      <c r="W1" s="51"/>
+      <c r="X1" s="51"/>
+      <c r="Y1" s="51"/>
+      <c r="Z1" s="51"/>
     </row>
     <row r="2" ht="135" spans="1:26">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="E2" s="53" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="75" spans="1:26">
-      <c r="A3" s="52"/>
-      <c r="B3" s="20" t="s">
+      <c r="A3" s="55"/>
+      <c r="B3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="20"/>
+      <c r="E3" s="23"/>
     </row>
     <row r="4" ht="75" spans="1:26">
-      <c r="A4" s="52"/>
-      <c r="B4" s="20" t="s">
+      <c r="A4" s="55"/>
+      <c r="B4" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="20"/>
+      <c r="E4" s="23"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="53"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
+      <c r="A5" s="56"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
     </row>
     <row r="6" ht="75" spans="1:26">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="53" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:26">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="20"/>
+      <c r="E7" s="23"/>
     </row>
     <row r="8" ht="56" customHeight="1" spans="1:26">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
     </row>
     <row r="9" ht="60" spans="1:26">
-      <c r="A9" s="52"/>
-      <c r="B9" s="20" t="s">
+      <c r="A9" s="55"/>
+      <c r="B9" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
     </row>
     <row r="10" ht="60" spans="1:26">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="20"/>
+      <c r="E10" s="23"/>
     </row>
     <row r="11" customFormat="1" ht="60" spans="1:26">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="20"/>
+      <c r="E11" s="23"/>
     </row>
     <row r="12" customFormat="1" ht="45" spans="1:26">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="51" t="s">
+      <c r="C12" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
     </row>
     <row r="13" customFormat="1" ht="60" spans="1:26">
-      <c r="A13" s="52"/>
-      <c r="B13" s="20" t="s">
+      <c r="A13" s="55"/>
+      <c r="B13" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
     </row>
     <row r="14" customFormat="1" ht="60" spans="1:26">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="20"/>
+      <c r="E14" s="23"/>
     </row>
     <row r="15" ht="60" spans="1:26">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="51" t="s">
+      <c r="D15" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="20"/>
+      <c r="E15" s="23"/>
     </row>
     <row r="16" ht="45" spans="1:26">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
     </row>
     <row r="17" ht="60" spans="1:5">
-      <c r="A17" s="52"/>
-      <c r="B17" s="20" t="s">
+      <c r="A17" s="55"/>
+      <c r="B17" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
     </row>
     <row r="18" customFormat="1" ht="60" spans="1:5">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
     </row>
     <row r="19" ht="60" spans="1:5">
-      <c r="A19" s="52" t="s">
+      <c r="A19" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="51" t="s">
+      <c r="D19" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="20"/>
+      <c r="E19" s="23"/>
     </row>
     <row r="20" ht="45" spans="1:5">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="51" t="s">
+      <c r="C20" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
     </row>
     <row r="21" ht="60" spans="1:5">
-      <c r="A21" s="52"/>
-      <c r="B21" s="20" t="s">
+      <c r="A21" s="55"/>
+      <c r="B21" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="51" t="s">
+      <c r="C21" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
     </row>
     <row r="22" ht="90" spans="1:5">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="51" t="s">
+      <c r="C22" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
     </row>
     <row r="23" ht="65" customHeight="1" spans="1:5">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="56" t="s">
+      <c r="D23" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="23" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" ht="65" customHeight="1" spans="1:5">
-      <c r="A24" s="52" t="s">
+      <c r="A24" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="50" t="s">
+      <c r="C24" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="56" t="s">
+      <c r="D24" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="20"/>
-    </row>
-    <row r="25" s="42" customFormat="1" ht="23.25" spans="1:5">
-      <c r="A25" s="57" t="s">
+      <c r="E24" s="23"/>
+    </row>
+    <row r="25" s="45" customFormat="1" ht="23.25" spans="1:5">
+      <c r="A25" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="59"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="62"/>
     </row>
     <row r="26" ht="90" spans="1:5">
-      <c r="A26" s="60" t="s">
+      <c r="A26" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="62" t="s">
+      <c r="C26" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="62" t="s">
+      <c r="D26" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="61"/>
+      <c r="E26" s="64"/>
     </row>
     <row r="27" ht="45" spans="1:5">
-      <c r="A27" s="60"/>
-      <c r="B27" s="20" t="s">
+      <c r="A27" s="63"/>
+      <c r="B27" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="51" t="s">
+      <c r="C27" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
     </row>
     <row r="28" ht="60" spans="1:5">
-      <c r="A28" s="63"/>
-      <c r="B28" s="20" t="s">
+      <c r="A28" s="66"/>
+      <c r="B28" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="51" t="s">
+      <c r="C28" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
     </row>
     <row r="29" ht="75" spans="1:5">
-      <c r="A29" s="52" t="s">
+      <c r="A29" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="51" t="s">
+      <c r="C29" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="64" t="s">
+      <c r="D29" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="20"/>
+      <c r="E29" s="23"/>
     </row>
     <row r="30" ht="45" spans="1:5">
-      <c r="A30" s="52" t="s">
+      <c r="A30" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="50" t="s">
+      <c r="C30" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
     </row>
     <row r="31" ht="55" customHeight="1" spans="1:5">
-      <c r="A31" s="52" t="s">
+      <c r="A31" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="50" t="s">
+      <c r="C31" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
     </row>
     <row r="32" ht="45" spans="1:5">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="50" t="s">
+      <c r="C32" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="51"/>
-      <c r="E32" s="20"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="23"/>
     </row>
     <row r="33" ht="45" spans="1:5">
-      <c r="A33" s="18"/>
-      <c r="B33" s="20" t="s">
+      <c r="A33" s="21"/>
+      <c r="B33" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="50" t="s">
+      <c r="C33" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="51"/>
-      <c r="E33" s="20"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="23"/>
     </row>
     <row r="34" ht="45" spans="1:5">
-      <c r="A34" s="18"/>
-      <c r="B34" s="20" t="s">
+      <c r="A34" s="21"/>
+      <c r="B34" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="51" t="s">
+      <c r="C34" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="51"/>
-      <c r="E34" s="20"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="23"/>
     </row>
     <row r="35" ht="75" spans="1:5">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="B35" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="51" t="s">
+      <c r="C35" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="51" t="s">
+      <c r="D35" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="E35" s="20"/>
+      <c r="E35" s="23"/>
     </row>
     <row r="36" ht="75" spans="1:5">
-      <c r="A36" s="18"/>
-      <c r="B36" s="20" t="s">
+      <c r="A36" s="21"/>
+      <c r="B36" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="51" t="s">
+      <c r="C36" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
     </row>
     <row r="37" ht="45" spans="1:5">
-      <c r="A37" s="18"/>
-      <c r="B37" s="20" t="s">
+      <c r="A37" s="21"/>
+      <c r="B37" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="51" t="s">
+      <c r="C37" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
     </row>
     <row r="38" ht="60" spans="1:5">
-      <c r="A38" s="65" t="s">
+      <c r="A38" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="51" t="s">
+      <c r="C38" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="51"/>
-      <c r="E38" s="20" t="s">
+      <c r="D38" s="54"/>
+      <c r="E38" s="23" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="39" ht="60" spans="1:5">
-      <c r="A39" s="60"/>
-      <c r="B39" s="20" t="s">
+      <c r="A39" s="63"/>
+      <c r="B39" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="51" t="s">
+      <c r="C39" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="51"/>
-      <c r="E39" s="20"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="23"/>
     </row>
     <row r="40" ht="90" spans="1:5">
-      <c r="A40" s="65" t="s">
+      <c r="A40" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="51" t="s">
+      <c r="C40" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="51" t="s">
+      <c r="D40" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="E40" s="20"/>
+      <c r="E40" s="23"/>
     </row>
     <row r="41" ht="75" spans="1:5">
-      <c r="A41" s="60"/>
-      <c r="B41" s="20" t="s">
+      <c r="A41" s="63"/>
+      <c r="B41" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="51" t="s">
+      <c r="C41" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
     </row>
     <row r="42" ht="45" spans="1:5">
-      <c r="A42" s="63"/>
-      <c r="B42" s="20" t="s">
+      <c r="A42" s="66"/>
+      <c r="B42" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="51" t="s">
+      <c r="C42" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
     </row>
     <row r="43" ht="75" spans="1:5">
-      <c r="A43" s="52" t="s">
+      <c r="A43" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="51" t="s">
+      <c r="C43" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D43" s="64" t="s">
+      <c r="D43" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="E43" s="20"/>
-    </row>
-    <row r="44" s="43" customFormat="1" ht="45" spans="1:5">
-      <c r="A44" s="49" t="s">
+      <c r="E43" s="23"/>
+    </row>
+    <row r="44" s="46" customFormat="1" ht="45" spans="1:5">
+      <c r="A44" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="66" t="s">
+      <c r="C44" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="E44" s="17"/>
+      <c r="E44" s="20"/>
     </row>
     <row r="45" ht="75" spans="1:5">
-      <c r="A45" s="18" t="s">
+      <c r="A45" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="20" t="s">
+      <c r="B45" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="51" t="s">
+      <c r="C45" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="51" t="s">
+      <c r="D45" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="E45" s="20"/>
+      <c r="E45" s="23"/>
     </row>
     <row r="46" ht="75" spans="1:5">
-      <c r="A46" s="18"/>
-      <c r="B46" s="20" t="s">
+      <c r="A46" s="21"/>
+      <c r="B46" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="51" t="s">
+      <c r="C46" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
     </row>
     <row r="47" ht="45" spans="1:5">
-      <c r="A47" s="18"/>
-      <c r="B47" s="20" t="s">
+      <c r="A47" s="21"/>
+      <c r="B47" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="51" t="s">
+      <c r="C47" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
     </row>
     <row r="48" ht="60" spans="1:5">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="51" t="s">
+      <c r="C48" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="D48" s="51"/>
-      <c r="E48" s="20" t="s">
+      <c r="D48" s="54"/>
+      <c r="E48" s="23" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="49" ht="60" spans="1:5">
-      <c r="A49" s="18"/>
-      <c r="B49" s="20" t="s">
+      <c r="A49" s="21"/>
+      <c r="B49" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="51" t="s">
+      <c r="C49" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="D49" s="51"/>
-      <c r="E49" s="20"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="23"/>
     </row>
     <row r="50" ht="90" spans="1:5">
-      <c r="A50" s="65" t="s">
+      <c r="A50" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="B50" s="20" t="s">
+      <c r="B50" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="51" t="s">
+      <c r="C50" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="D50" s="51" t="s">
+      <c r="D50" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="E50" s="20"/>
+      <c r="E50" s="23"/>
     </row>
     <row r="51" ht="75" spans="1:5">
-      <c r="A51" s="60"/>
-      <c r="B51" s="20" t="s">
+      <c r="A51" s="63"/>
+      <c r="B51" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C51" s="51" t="s">
+      <c r="C51" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="23"/>
     </row>
     <row r="52" ht="45" spans="1:5">
-      <c r="A52" s="63"/>
-      <c r="B52" s="20" t="s">
+      <c r="A52" s="66"/>
+      <c r="B52" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="51" t="s">
+      <c r="C52" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
     </row>
     <row r="53" ht="75" spans="1:5">
-      <c r="A53" s="52" t="s">
+      <c r="A53" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="B53" s="20" t="s">
+      <c r="B53" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C53" s="51" t="s">
+      <c r="C53" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D53" s="64" t="s">
+      <c r="D53" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="E53" s="20"/>
-    </row>
-    <row r="54" s="43" customFormat="1" ht="45" spans="1:5">
-      <c r="A54" s="49" t="s">
+      <c r="E53" s="23"/>
+    </row>
+    <row r="54" s="46" customFormat="1" ht="45" spans="1:5">
+      <c r="A54" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="17" t="s">
+      <c r="B54" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C54" s="66" t="s">
+      <c r="C54" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="D54" s="17" t="s">
+      <c r="D54" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="E54" s="17"/>
+      <c r="E54" s="20"/>
     </row>
     <row r="56" ht="75" spans="1:5">
-      <c r="A56" s="18" t="s">
+      <c r="A56" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="20" t="s">
+      <c r="B56" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C56" s="51" t="s">
+      <c r="C56" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="D56" s="51" t="s">
+      <c r="D56" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="E56" s="20"/>
+      <c r="E56" s="23"/>
     </row>
     <row r="57" ht="75" spans="1:5">
-      <c r="A57" s="18"/>
-      <c r="B57" s="20" t="s">
+      <c r="A57" s="21"/>
+      <c r="B57" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C57" s="51" t="s">
+      <c r="C57" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="23"/>
     </row>
     <row r="58" ht="45" spans="1:5">
-      <c r="A58" s="18"/>
-      <c r="B58" s="20" t="s">
+      <c r="A58" s="21"/>
+      <c r="B58" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="51" t="s">
+      <c r="C58" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="23"/>
     </row>
     <row r="59" ht="60" spans="1:5">
-      <c r="A59" s="18" t="s">
+      <c r="A59" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B59" s="20" t="s">
+      <c r="B59" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="51" t="s">
+      <c r="C59" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="D59" s="51"/>
-      <c r="E59" s="20" t="s">
+      <c r="D59" s="54"/>
+      <c r="E59" s="23" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="60" ht="60" spans="1:5">
-      <c r="A60" s="18"/>
-      <c r="B60" s="20" t="s">
+      <c r="A60" s="21"/>
+      <c r="B60" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="51" t="s">
+      <c r="C60" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="51"/>
-      <c r="E60" s="20"/>
-    </row>
-    <row r="61" s="44" customFormat="1" ht="90" spans="1:5">
-      <c r="A61" s="67" t="s">
+      <c r="D60" s="54"/>
+      <c r="E60" s="23"/>
+    </row>
+    <row r="61" s="47" customFormat="1" ht="90" spans="1:5">
+      <c r="A61" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="B61" s="68" t="s">
+      <c r="B61" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="69" t="s">
+      <c r="C61" s="72" t="s">
         <v>82</v>
       </c>
-      <c r="D61" s="69" t="s">
+      <c r="D61" s="72" t="s">
         <v>92</v>
       </c>
-      <c r="E61" s="68"/>
-    </row>
-    <row r="62" s="44" customFormat="1" ht="75" spans="1:5">
-      <c r="A62" s="70"/>
-      <c r="B62" s="68" t="s">
+      <c r="E61" s="71"/>
+    </row>
+    <row r="62" s="47" customFormat="1" ht="75" spans="1:5">
+      <c r="A62" s="73"/>
+      <c r="B62" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="C62" s="69" t="s">
+      <c r="C62" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="D62" s="68"/>
-      <c r="E62" s="68"/>
-    </row>
-    <row r="63" s="44" customFormat="1" ht="45" spans="1:5">
-      <c r="A63" s="71"/>
-      <c r="B63" s="68" t="s">
+      <c r="D62" s="71"/>
+      <c r="E62" s="71"/>
+    </row>
+    <row r="63" s="47" customFormat="1" ht="45" spans="1:5">
+      <c r="A63" s="74"/>
+      <c r="B63" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="69" t="s">
+      <c r="C63" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="D63" s="68"/>
-      <c r="E63" s="68"/>
+      <c r="D63" s="71"/>
+      <c r="E63" s="71"/>
     </row>
     <row r="64" ht="75" spans="1:5">
-      <c r="A64" s="52" t="s">
+      <c r="A64" s="55" t="s">
         <v>98</v>
       </c>
-      <c r="B64" s="20" t="s">
+      <c r="B64" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C64" s="51" t="s">
+      <c r="C64" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D64" s="64" t="s">
+      <c r="D64" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="E64" s="20"/>
-    </row>
-    <row r="65" s="43" customFormat="1" ht="45" spans="1:5">
-      <c r="A65" s="49" t="s">
+      <c r="E64" s="23"/>
+    </row>
+    <row r="65" s="46" customFormat="1" ht="45" spans="1:5">
+      <c r="A65" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="B65" s="17" t="s">
+      <c r="B65" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C65" s="66" t="s">
+      <c r="C65" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="D65" s="17" t="s">
+      <c r="D65" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="E65" s="17"/>
-    </row>
-    <row r="66" s="42" customFormat="1" ht="23.25" spans="1:5">
-      <c r="A66" s="72" t="s">
+      <c r="E65" s="20"/>
+    </row>
+    <row r="66" s="45" customFormat="1" ht="23.25" spans="1:5">
+      <c r="A66" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="B66" s="72"/>
-      <c r="C66" s="72"/>
-      <c r="D66" s="72"/>
-      <c r="E66" s="72"/>
+      <c r="B66" s="75"/>
+      <c r="C66" s="75"/>
+      <c r="D66" s="75"/>
+      <c r="E66" s="75"/>
     </row>
     <row r="67" ht="90" spans="1:5">
-      <c r="A67" s="60" t="s">
+      <c r="A67" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="B67" s="61" t="s">
+      <c r="B67" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="C67" s="62" t="s">
+      <c r="C67" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="D67" s="62" t="s">
+      <c r="D67" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="E67" s="61"/>
+      <c r="E67" s="64"/>
     </row>
     <row r="68" ht="45" spans="1:5">
-      <c r="A68" s="60"/>
-      <c r="B68" s="20" t="s">
+      <c r="A68" s="63"/>
+      <c r="B68" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="51" t="s">
+      <c r="C68" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
+      <c r="D68" s="23"/>
+      <c r="E68" s="23"/>
     </row>
     <row r="69" ht="60" spans="1:5">
-      <c r="A69" s="63"/>
-      <c r="B69" s="20" t="s">
+      <c r="A69" s="66"/>
+      <c r="B69" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C69" s="51" t="s">
+      <c r="C69" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
+      <c r="D69" s="23"/>
+      <c r="E69" s="23"/>
     </row>
     <row r="70" ht="75" spans="1:5">
-      <c r="A70" s="52" t="s">
+      <c r="A70" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="20" t="s">
+      <c r="B70" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="51" t="s">
+      <c r="C70" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D70" s="64" t="s">
+      <c r="D70" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="E70" s="20"/>
+      <c r="E70" s="23"/>
     </row>
     <row r="71" ht="45" spans="1:5">
-      <c r="A71" s="52" t="s">
+      <c r="A71" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="20" t="s">
+      <c r="B71" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C71" s="50" t="s">
+      <c r="C71" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
+      <c r="D71" s="23"/>
+      <c r="E71" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4434,83 +4564,86 @@
   <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="42" style="35" customWidth="1"/>
-    <col min="2" max="2" width="42.8571428571429" style="20" customWidth="1"/>
-    <col min="3" max="4" width="9.14285714285714" style="20"/>
+    <col min="1" max="1" width="42" style="38" customWidth="1"/>
+    <col min="2" max="2" width="42.8571428571429" style="23" customWidth="1"/>
+    <col min="3" max="4" width="9.14285714285714" style="23"/>
     <col min="5" max="5" width="43.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="12.4095238095238" customWidth="1"/>
     <col min="7" max="7" width="10.5714285714286"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:17">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:17">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="37">
-        <v>33000000</v>
-      </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
+      <c r="B3" s="40">
+        <v>1000000</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
       <c r="E3" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:17">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="37">
-        <v>2</v>
-      </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
+      <c r="B4" s="40">
+        <v>1</v>
+      </c>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
       <c r="E4" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="5" ht="33" customHeight="1" spans="1:17">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="37">
-        <v>1200001</v>
-      </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
+      <c r="B5" s="40">
+        <v>1000</v>
+      </c>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
       <c r="E5" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:17">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
+      <c r="B6" s="40">
+        <v>0</v>
+      </c>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
       <c r="E6" t="s">
         <v>114</v>
       </c>
-      <c r="N6" s="39">
+      <c r="N6" s="42">
         <v>15000</v>
       </c>
       <c r="P6">
@@ -4518,15 +4651,15 @@
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:17">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="37">
+      <c r="B7" s="40">
         <f>B5-B6</f>
-        <v>1200001</v>
-      </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
+        <v>1000</v>
+      </c>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
       <c r="E7" t="s">
         <v>116</v>
       </c>
@@ -4541,19 +4674,19 @@
       </c>
     </row>
     <row r="8" ht="71" customHeight="1" spans="1:17">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="40">
         <f>3%*B7</f>
-        <v>36000.03</v>
-      </c>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="N8" s="39">
+      <c r="N8" s="42">
         <v>20453</v>
       </c>
       <c r="P8">
@@ -4561,15 +4694,15 @@
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:17">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="40">
         <f>B7-B8</f>
-        <v>1164000.97</v>
-      </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
+        <v>970</v>
+      </c>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
       <c r="E9" t="s">
         <v>120</v>
       </c>
@@ -4581,19 +4714,22 @@
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:17">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="40">
         <f>15%*B3</f>
-        <v>4950000</v>
-      </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
+        <v>150000</v>
+      </c>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
       <c r="E10" t="s">
         <v>122</v>
       </c>
-      <c r="K10" s="41">
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="K10" s="44">
         <v>38697.18</v>
       </c>
       <c r="N10">
@@ -4604,19 +4740,22 @@
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:17">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="40">
         <f>75%*B9</f>
-        <v>873000.7275</v>
-      </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
+        <v>727.5</v>
+      </c>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
       <c r="E11" t="s">
         <v>124</v>
       </c>
-      <c r="K11" s="41">
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="K11" s="44">
         <v>47062.7</v>
       </c>
       <c r="N11">
@@ -4627,37 +4766,40 @@
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:17">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="40">
         <f>B11</f>
-        <v>873000.7275</v>
-      </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
+        <v>727.5</v>
+      </c>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="F12">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:17">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
       <c r="E13" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="14" ht="33" customHeight="1" spans="1:17">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="40">
         <f>B12-B13</f>
-        <v>873000.7275</v>
-      </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
+        <v>727.5</v>
+      </c>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -4698,199 +4840,199 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-    </row>
-    <row r="2" s="29" customFormat="1" spans="1:14">
-      <c r="A2" s="30" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+    </row>
+    <row r="2" s="32" customFormat="1" spans="1:14">
+      <c r="A2" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="N2" s="29">
+      <c r="N2" s="32">
         <v>832.88</v>
       </c>
     </row>
-    <row r="3" s="29" customFormat="1" spans="1:14">
-      <c r="A3" s="31">
+    <row r="3" s="32" customFormat="1" spans="1:14">
+      <c r="A3" s="34">
         <v>46174</v>
       </c>
-      <c r="B3" s="31">
+      <c r="B3" s="34">
         <v>46477</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="35">
         <f>B3-A3+1</f>
         <v>304</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="36">
         <f>1%*E3*C3/365</f>
         <v>832.876712328767</v>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="35">
         <v>100000</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="35">
         <f>D3*18%</f>
         <v>149.917808219178</v>
       </c>
-      <c r="G3" s="32">
+      <c r="G3" s="35">
         <f>D3+F3</f>
         <v>982.794520547945</v>
       </c>
     </row>
-    <row r="4" s="29" customFormat="1"/>
+    <row r="4" s="32" customFormat="1"/>
     <row r="7" spans="1:14">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="33" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="31">
+      <c r="A9" s="34">
         <v>46072</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="34">
         <v>46112</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="35">
         <f>B9-A9+1</f>
         <v>41</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="36">
         <f>0.25%*E9*C9/365</f>
         <v>28.0821917808219</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="35">
         <v>100000</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="35">
         <f>D9*18%</f>
         <v>5.05479452054795</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="35">
         <f>D9+F9</f>
         <v>33.1369863013699</v>
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="F14" s="30" t="s">
+      <c r="F14" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="H14" s="30" t="s">
+      <c r="H14" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="I14" s="30" t="s">
+      <c r="I14" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="J14" s="30" t="s">
+      <c r="J14" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="K14" s="30" t="s">
+      <c r="K14" s="33" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="35">
         <v>10000</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="34">
         <v>46082</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="34">
         <v>46477</v>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="35">
         <f>DATEDIF(C15,D15,"d")+1</f>
         <v>396</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="37">
         <v>0.01</v>
       </c>
-      <c r="G15" s="32">
+      <c r="G15" s="35">
         <f>IF(K15="Closed",0,B15*F15*(E15/365))</f>
         <v>108.493150684932</v>
       </c>
-      <c r="H15" s="32">
+      <c r="H15" s="35">
         <f>G15*9%</f>
         <v>9.76438356164384</v>
       </c>
-      <c r="I15" s="32">
+      <c r="I15" s="35">
         <f>18%*G15</f>
         <v>19.5287671232877</v>
       </c>
-      <c r="J15" s="32">
+      <c r="J15" s="35">
         <f>G15+H15+I15</f>
         <v>137.786301369863</v>
       </c>
-      <c r="K15" s="32" t="s">
+      <c r="K15" s="35" t="s">
         <v>150</v>
       </c>
     </row>
@@ -4926,559 +5068,559 @@
       </c>
     </row>
     <row r="2" spans="3:10">
-      <c r="C2" s="17"/>
-      <c r="D2" s="17" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="21" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="3" spans="3:10">
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21" t="s">
+      <c r="G3" s="24"/>
+      <c r="H3" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="J3" s="18"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" spans="3:10">
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="25">
         <v>46386</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="I4" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="J4" s="18"/>
+      <c r="J4" s="21"/>
     </row>
     <row r="5" spans="3:10">
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="25">
         <v>46477</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="J5" s="18"/>
+      <c r="J5" s="21"/>
     </row>
     <row r="6" spans="3:10">
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="25">
         <v>46568</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="I6" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="J6" s="18"/>
+      <c r="J6" s="21"/>
     </row>
     <row r="7" spans="3:10">
-      <c r="C7" s="23"/>
-      <c r="I7" s="23"/>
+      <c r="C7" s="26"/>
+      <c r="I7" s="26"/>
     </row>
     <row r="8" spans="3:10">
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="27">
         <v>46843</v>
       </c>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="J8" s="23" t="s">
+      <c r="J8" s="26" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="9" spans="3:10">
-      <c r="C9" s="23"/>
-      <c r="F9" s="25" t="s">
+      <c r="C9" s="26"/>
+      <c r="F9" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="29">
         <v>46843</v>
       </c>
-      <c r="I9" s="27" t="s">
+      <c r="I9" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="J9" s="27" t="s">
+      <c r="J9" s="30" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="10" spans="3:10">
-      <c r="C10" s="23"/>
-      <c r="F10" s="25" t="s">
+      <c r="C10" s="26"/>
+      <c r="F10" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26">
+      <c r="G10" s="29"/>
+      <c r="H10" s="29">
         <v>46844</v>
       </c>
-      <c r="I10" s="27" t="s">
+      <c r="I10" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="J10" s="27" t="s">
+      <c r="J10" s="30" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="11" spans="3:10">
-      <c r="C11" s="23"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="23"/>
+      <c r="C11" s="26"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="26"/>
     </row>
     <row r="12" spans="3:10">
-      <c r="C12" s="23"/>
-      <c r="I12" s="23"/>
+      <c r="C12" s="26"/>
+      <c r="I12" s="26"/>
     </row>
     <row r="13" spans="3:10">
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="G13" s="24" t="s">
+      <c r="G13" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="27">
         <v>47208</v>
       </c>
-      <c r="I13" s="19" t="s">
+      <c r="I13" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="J13" s="23" t="s">
+      <c r="J13" s="26" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="14" spans="3:10">
-      <c r="C14" s="23"/>
-      <c r="F14" s="25" t="s">
+      <c r="C14" s="26"/>
+      <c r="F14" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="29">
         <v>47208</v>
       </c>
-      <c r="I14" s="27" t="s">
+      <c r="I14" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="J14" s="27" t="s">
+      <c r="J14" s="30" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="15" spans="3:10">
-      <c r="C15" s="23"/>
-      <c r="F15" s="25" t="s">
+      <c r="C15" s="26"/>
+      <c r="F15" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26">
+      <c r="G15" s="29"/>
+      <c r="H15" s="29">
         <v>47209</v>
       </c>
-      <c r="I15" s="27" t="s">
+      <c r="I15" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="J15" s="27" t="s">
+      <c r="J15" s="30" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="16" spans="3:10">
-      <c r="C16" s="23"/>
-      <c r="I16" s="23"/>
+      <c r="C16" s="26"/>
+      <c r="I16" s="26"/>
     </row>
     <row r="17" spans="3:10">
-      <c r="C17" s="23"/>
-      <c r="I17" s="23"/>
+      <c r="C17" s="26"/>
+      <c r="I17" s="26"/>
     </row>
     <row r="18" spans="3:10">
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="27">
         <v>47573</v>
       </c>
-      <c r="I18" s="19" t="s">
+      <c r="I18" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="J18" s="23" t="s">
+      <c r="J18" s="26" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="23"/>
-      <c r="F19" s="25" t="s">
+      <c r="C19" s="26"/>
+      <c r="F19" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="G19" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="29">
         <v>47573</v>
       </c>
-      <c r="I19" s="27" t="s">
+      <c r="I19" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="J19" s="27" t="s">
+      <c r="J19" s="30" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="20" spans="3:10">
-      <c r="C20" s="23"/>
-      <c r="F20" s="25" t="s">
+      <c r="C20" s="26"/>
+      <c r="F20" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26">
+      <c r="G20" s="29"/>
+      <c r="H20" s="29">
         <v>47574</v>
       </c>
-      <c r="I20" s="27" t="s">
+      <c r="I20" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="J20" s="27" t="s">
+      <c r="J20" s="30" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="23"/>
-      <c r="I21" s="23"/>
+      <c r="C21" s="26"/>
+      <c r="I21" s="26"/>
     </row>
     <row r="22" spans="3:10">
-      <c r="C22" s="23"/>
-      <c r="I22" s="23"/>
+      <c r="C22" s="26"/>
+      <c r="I22" s="26"/>
     </row>
     <row r="23" spans="3:10">
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="G23" s="24" t="s">
+      <c r="G23" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="H23" s="24">
+      <c r="H23" s="27">
         <v>47938</v>
       </c>
-      <c r="I23" s="19" t="s">
+      <c r="I23" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="J23" s="23" t="s">
+      <c r="J23" s="26" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="24" spans="3:10">
-      <c r="F24" s="25" t="s">
+      <c r="F24" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="G24" s="26" t="s">
+      <c r="G24" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="29">
         <v>47938</v>
       </c>
-      <c r="I24" s="27" t="s">
+      <c r="I24" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="J24" s="27" t="s">
+      <c r="J24" s="30" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="25" spans="3:10">
-      <c r="F25" s="25" t="s">
+      <c r="F25" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26">
+      <c r="G25" s="29"/>
+      <c r="H25" s="29">
         <v>47939</v>
       </c>
-      <c r="I25" s="27" t="s">
+      <c r="I25" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="J25" s="27" t="s">
+      <c r="J25" s="30" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="26" spans="3:10">
-      <c r="I26" s="23"/>
+      <c r="I26" s="26"/>
     </row>
     <row r="27" spans="3:10">
-      <c r="I27" s="23"/>
+      <c r="I27" s="26"/>
     </row>
     <row r="28" spans="3:10">
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="G28" s="24" t="s">
+      <c r="G28" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="H28" s="24">
+      <c r="H28" s="27">
         <v>48304</v>
       </c>
-      <c r="I28" s="19" t="s">
+      <c r="I28" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="J28" s="23" t="s">
+      <c r="J28" s="26" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="29" spans="3:10">
-      <c r="F29" s="25" t="s">
+      <c r="F29" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="G29" s="26" t="s">
+      <c r="G29" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="H29" s="26">
+      <c r="H29" s="29">
         <v>48304</v>
       </c>
-      <c r="I29" s="27" t="s">
+      <c r="I29" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="J29" s="27" t="s">
+      <c r="J29" s="30" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="30" spans="3:10">
-      <c r="F30" s="25" t="s">
+      <c r="F30" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26">
+      <c r="G30" s="29"/>
+      <c r="H30" s="29">
         <v>48305</v>
       </c>
-      <c r="I30" s="27" t="s">
+      <c r="I30" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="J30" s="27" t="s">
+      <c r="J30" s="30" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="31" spans="3:10">
-      <c r="I31" s="23"/>
+      <c r="I31" s="26"/>
     </row>
     <row r="32" spans="3:10">
-      <c r="I32" s="23"/>
+      <c r="I32" s="26"/>
     </row>
     <row r="33" spans="3:10">
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="D33" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="F33" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="G33" s="24" t="s">
+      <c r="G33" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="H33" s="24">
+      <c r="H33" s="27">
         <v>48669</v>
       </c>
-      <c r="I33" s="19" t="s">
+      <c r="I33" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="J33" s="23" t="s">
+      <c r="J33" s="26" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="34" spans="3:10">
-      <c r="F34" s="25" t="s">
+      <c r="F34" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="G34" s="26" t="s">
+      <c r="G34" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="H34" s="26">
+      <c r="H34" s="29">
         <v>48669</v>
       </c>
-      <c r="I34" s="27" t="s">
+      <c r="I34" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="J34" s="27" t="s">
+      <c r="J34" s="30" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="35" spans="3:10">
-      <c r="F35" s="25" t="s">
+      <c r="F35" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26">
+      <c r="G35" s="29"/>
+      <c r="H35" s="29">
         <v>48670</v>
       </c>
-      <c r="I35" s="27" t="s">
+      <c r="I35" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="J35" s="27" t="s">
+      <c r="J35" s="30" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="36" spans="3:10">
-      <c r="I36" s="23"/>
+      <c r="I36" s="26"/>
     </row>
     <row r="37" spans="3:10">
-      <c r="I37" s="23"/>
+      <c r="I37" s="26"/>
     </row>
     <row r="38" spans="3:10">
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="D38" s="20" t="s">
+      <c r="D38" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="F38" s="20" t="s">
+      <c r="F38" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="G38" s="24" t="s">
+      <c r="G38" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="H38" s="24">
+      <c r="H38" s="27">
         <v>49034</v>
       </c>
-      <c r="I38" s="19" t="s">
+      <c r="I38" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="J38" s="23" t="s">
+      <c r="J38" s="26" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="39" spans="3:10">
-      <c r="F39" s="25"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="27"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5491,831 +5633,1082 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.1428571428571" customWidth="1"/>
     <col min="2" max="2" width="15.2857142857143" customWidth="1"/>
-    <col min="3" max="3" width="14.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="17.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="11.7142857142857" customWidth="1"/>
     <col min="6" max="6" width="13.5714285714286" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="14.4285714285714" customWidth="1"/>
+    <col min="7" max="7" width="15.5714285714286" customWidth="1"/>
+    <col min="8" max="8" width="16.1428571428571" customWidth="1"/>
     <col min="9" max="9" width="15.8571428571429" customWidth="1"/>
     <col min="10" max="10" width="10.7142857142857" customWidth="1"/>
-    <col min="11" max="11" width="13.4285714285714" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="5" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="7">
         <v>100000</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="7">
         <v>100000</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-    </row>
-    <row r="4" hidden="1" spans="1:11">
-      <c r="A4" s="5" t="s">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="9">
         <v>100000</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" hidden="1" spans="1:11">
-      <c r="A5" s="5" t="s">
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="9">
         <v>100000</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" hidden="1" spans="1:11">
-      <c r="A6" s="5" t="s">
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="9">
         <v>100000</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" hidden="1" spans="1:11">
-      <c r="A7" s="5" t="s">
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="9">
         <v>100000</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" hidden="1" spans="1:11">
-      <c r="A8" s="5" t="s">
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="9">
         <v>100000</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" hidden="1" spans="1:11">
-      <c r="A9" s="5" t="s">
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="9">
         <v>100000</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" hidden="1" spans="1:11">
-      <c r="A10" s="5" t="s">
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="9">
         <v>100000</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="9">
         <v>100000</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" hidden="1" spans="1:11">
-      <c r="A12" s="5" t="s">
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="9">
         <v>100000</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" hidden="1" spans="1:11">
-      <c r="A13" s="5" t="s">
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="9">
         <v>100000</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" hidden="1" spans="1:11">
-      <c r="A14" s="5" t="s">
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="9">
         <v>100000</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" hidden="1" spans="1:11">
-      <c r="A15" s="5" t="s">
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="9">
         <v>100000</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" hidden="1" spans="1:11">
-      <c r="A16" s="5" t="s">
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="9">
         <v>100000</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" hidden="1" spans="1:11">
-      <c r="A17" s="5" t="s">
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="9">
         <v>100000</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" hidden="1" spans="1:11">
-      <c r="A18" s="5" t="s">
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="9">
         <v>100000</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" hidden="1" spans="1:11">
-      <c r="A19" s="5" t="s">
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="9">
         <v>100000</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" hidden="1" spans="1:11">
-      <c r="A20" s="5" t="s">
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="9">
         <v>100000</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" hidden="1" spans="1:11">
-      <c r="A21" s="8" t="s">
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="12">
         <v>100000</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-    </row>
-    <row r="22" hidden="1" spans="1:11">
-      <c r="A22" s="8" t="s">
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="12">
         <v>100000</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" hidden="1" spans="1:11">
-      <c r="A23" s="8" t="s">
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="12">
         <v>100000</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" hidden="1" spans="1:11">
-      <c r="A24" s="10" t="s">
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="14">
         <v>100000</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" hidden="1" spans="1:11">
-      <c r="A25" s="10" t="s">
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="14">
         <v>100000</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" hidden="1" spans="1:11">
-      <c r="A26" s="12" t="s">
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="7">
         <v>10000</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2" t="s">
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" hidden="1" spans="1:11">
-      <c r="A27" s="12" t="s">
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="16">
         <v>605501.57</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2" t="s">
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" hidden="1" spans="1:11">
-      <c r="A28" s="12" t="s">
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="7">
         <v>200000.56</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2" t="s">
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29" hidden="1" spans="1:11">
-      <c r="A29" s="14" t="s">
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="19">
         <v>200000.56</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2" t="s">
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" hidden="1"/>
-    <row r="31" hidden="1"/>
-    <row r="32" hidden="1" spans="1:11">
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
         <v>249</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H32" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="2627CR710"/>
-        <filter val="2627CR701"/>
-        <filter val="2627CR702"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters blank="1">
-        <filter val="NPA"/>
-        <filter val="Stn"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:L25"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="14.4666666666667" customWidth="1"/>
+    <col min="8" max="8" width="10.9809523809524" customWidth="1"/>
+    <col min="9" max="9" width="60.7809523809524" customWidth="1"/>
+    <col min="10" max="10" width="11.8761904761905" customWidth="1"/>
+    <col min="12" max="12" width="31.4285714285714" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12">
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" ht="30" spans="2:12">
+      <c r="B2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" ht="30" spans="2:12">
+      <c r="B3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+      <c r="D3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" ht="30" spans="2:12">
+      <c r="H4" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="5" ht="45" spans="2:12">
+      <c r="B5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C5">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>266</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" ht="45" spans="2:12">
+      <c r="H6" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" ht="45" spans="2:12">
+      <c r="H7" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" ht="60" spans="2:12">
+      <c r="H8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="9" ht="60" spans="2:12">
+      <c r="H9" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10" ht="60" spans="2:12">
+      <c r="H10" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" ht="30" spans="2:12">
+      <c r="H11" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="12" ht="30" spans="2:12">
+      <c r="H12" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="17" spans="8:9">
+      <c r="H17" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="19" spans="8:9">
+      <c r="H19" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="20" spans="8:9">
+      <c r="H20" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="21" spans="8:9">
+      <c r="H21" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="22" spans="8:9">
+      <c r="H22" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="25" spans="8:9">
+      <c r="H25" t="s">
+        <v>213</v>
+      </c>
+      <c r="I25" t="s">
+        <v>266</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="L11:L12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/MU/MU user manual infoneo (2).xlsx
+++ b/MU/MU user manual infoneo (2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600" activeTab="5"/>
+    <workbookView windowWidth="24000" windowHeight="9600" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Flow" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
     <sheet name="Sheet4" sheetId="9" r:id="rId6"/>
+    <sheet name="Sheet3" sheetId="10" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet2!$A$1:$H$32</definedName>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="295">
   <si>
     <t>Category</t>
   </si>
@@ -1434,7 +1435,7 @@
     <t>Maximum Payout(Rs.)</t>
   </si>
   <si>
-    <t>15% of crystlized sanction amount</t>
+    <t>15% of crystlized original sanction amount</t>
   </si>
   <si>
     <t>Amount of Eligible Interim claim(Rs.)</t>
@@ -1936,6 +1937,30 @@
   </si>
   <si>
     <t>1st Update CG , then claim , settle , next CP upload CG for same loan ac</t>
+  </si>
+  <si>
+    <t>Sanct</t>
+  </si>
+  <si>
+    <t>10 Record</t>
+  </si>
+  <si>
+    <t>5L</t>
+  </si>
+  <si>
+    <t>6L</t>
+  </si>
+  <si>
+    <t>cryz</t>
+  </si>
+  <si>
+    <t>21L</t>
+  </si>
+  <si>
+    <t>Max payout on claim</t>
+  </si>
+  <si>
+    <t>22L</t>
   </si>
 </sst>
 </file>
@@ -2844,8 +2869,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
@@ -2906,9 +2937,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2929,9 +2957,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2983,9 +3008,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3638,898 +3660,898 @@
       <c r="A2" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="75" spans="1:26">
-      <c r="A3" s="55"/>
-      <c r="B3" s="23" t="s">
+      <c r="A3" s="54"/>
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="3"/>
     </row>
     <row r="4" ht="75" spans="1:26">
-      <c r="A4" s="55"/>
-      <c r="B4" s="23" t="s">
+      <c r="A4" s="54"/>
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="56"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
+      <c r="A5" s="55"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
     </row>
     <row r="6" ht="75" spans="1:26">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:26">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D7" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="3"/>
     </row>
     <row r="8" ht="56" customHeight="1" spans="1:26">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" ht="60" spans="1:26">
-      <c r="A9" s="55"/>
-      <c r="B9" s="23" t="s">
+      <c r="A9" s="54"/>
+      <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" ht="60" spans="1:26">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="23"/>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" customFormat="1" ht="60" spans="1:26">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="53" t="s">
+      <c r="D11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="23"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" customFormat="1" ht="45" spans="1:26">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" customFormat="1" ht="60" spans="1:26">
-      <c r="A13" s="55"/>
-      <c r="B13" s="23" t="s">
+      <c r="A13" s="54"/>
+      <c r="B13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="54" t="s">
+      <c r="C13" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" customFormat="1" ht="60" spans="1:26">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="23"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" ht="60" spans="1:26">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="54" t="s">
+      <c r="D15" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="23"/>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" ht="45" spans="1:26">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" ht="60" spans="1:5">
-      <c r="A17" s="55"/>
-      <c r="B17" s="23" t="s">
+      <c r="A17" s="54"/>
+      <c r="B17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="54" t="s">
+      <c r="C17" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" customFormat="1" ht="60" spans="1:5">
-      <c r="A18" s="55" t="s">
+      <c r="A18" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="53" t="s">
+      <c r="C18" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" ht="60" spans="1:5">
-      <c r="A19" s="55" t="s">
+      <c r="A19" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="53" t="s">
+      <c r="C19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="54" t="s">
+      <c r="D19" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="23"/>
+      <c r="E19" s="3"/>
     </row>
     <row r="20" ht="45" spans="1:5">
-      <c r="A20" s="55" t="s">
+      <c r="A20" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" ht="60" spans="1:5">
-      <c r="A21" s="55"/>
-      <c r="B21" s="23" t="s">
+      <c r="A21" s="54"/>
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="54" t="s">
+      <c r="C21" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" ht="90" spans="1:5">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="54" t="s">
+      <c r="C22" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" ht="65" customHeight="1" spans="1:5">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="53" t="s">
+      <c r="C23" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="59" t="s">
+      <c r="D23" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E23" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" ht="65" customHeight="1" spans="1:5">
-      <c r="A24" s="55" t="s">
+      <c r="A24" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="53" t="s">
+      <c r="C24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="59" t="s">
+      <c r="D24" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="23"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" s="45" customFormat="1" ht="23.25" spans="1:5">
-      <c r="A25" s="60" t="s">
+      <c r="A25" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="61"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="62"/>
+      <c r="B25" s="60"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="61"/>
     </row>
     <row r="26" ht="90" spans="1:5">
-      <c r="A26" s="63" t="s">
+      <c r="A26" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="64" t="s">
+      <c r="B26" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="65" t="s">
+      <c r="C26" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="65" t="s">
+      <c r="D26" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="64"/>
+      <c r="E26" s="63"/>
     </row>
     <row r="27" ht="45" spans="1:5">
-      <c r="A27" s="63"/>
-      <c r="B27" s="23" t="s">
+      <c r="A27" s="62"/>
+      <c r="B27" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="54" t="s">
+      <c r="C27" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
     </row>
     <row r="28" ht="60" spans="1:5">
-      <c r="A28" s="66"/>
-      <c r="B28" s="23" t="s">
+      <c r="A28" s="65"/>
+      <c r="B28" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="54" t="s">
+      <c r="C28" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
     </row>
     <row r="29" ht="75" spans="1:5">
-      <c r="A29" s="55" t="s">
+      <c r="A29" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="54" t="s">
+      <c r="C29" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="67" t="s">
+      <c r="D29" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="23"/>
+      <c r="E29" s="3"/>
     </row>
     <row r="30" ht="45" spans="1:5">
-      <c r="A30" s="55" t="s">
+      <c r="A30" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="53" t="s">
+      <c r="C30" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
     </row>
     <row r="31" ht="55" customHeight="1" spans="1:5">
-      <c r="A31" s="55" t="s">
+      <c r="A31" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="53" t="s">
+      <c r="C31" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
     </row>
     <row r="32" ht="45" spans="1:5">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="53" t="s">
+      <c r="C32" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="54"/>
-      <c r="E32" s="23"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" ht="45" spans="1:5">
-      <c r="A33" s="21"/>
-      <c r="B33" s="23" t="s">
+      <c r="A33" s="23"/>
+      <c r="B33" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="53" t="s">
+      <c r="C33" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="54"/>
-      <c r="E33" s="23"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="3"/>
     </row>
     <row r="34" ht="45" spans="1:5">
-      <c r="A34" s="21"/>
-      <c r="B34" s="23" t="s">
+      <c r="A34" s="23"/>
+      <c r="B34" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="54" t="s">
+      <c r="C34" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="54"/>
-      <c r="E34" s="23"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="3"/>
     </row>
     <row r="35" ht="75" spans="1:5">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="23" t="s">
+      <c r="B35" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="54" t="s">
+      <c r="C35" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="54" t="s">
+      <c r="D35" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="E35" s="23"/>
+      <c r="E35" s="3"/>
     </row>
     <row r="36" ht="75" spans="1:5">
-      <c r="A36" s="21"/>
-      <c r="B36" s="23" t="s">
+      <c r="A36" s="23"/>
+      <c r="B36" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="54" t="s">
+      <c r="C36" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
     </row>
     <row r="37" ht="45" spans="1:5">
-      <c r="A37" s="21"/>
-      <c r="B37" s="23" t="s">
+      <c r="A37" s="23"/>
+      <c r="B37" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="54" t="s">
+      <c r="C37" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
     </row>
     <row r="38" ht="60" spans="1:5">
-      <c r="A38" s="68" t="s">
+      <c r="A38" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="54" t="s">
+      <c r="C38" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="54"/>
-      <c r="E38" s="23" t="s">
+      <c r="D38" s="53"/>
+      <c r="E38" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="39" ht="60" spans="1:5">
-      <c r="A39" s="63"/>
-      <c r="B39" s="23" t="s">
+      <c r="A39" s="62"/>
+      <c r="B39" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="54" t="s">
+      <c r="C39" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="54"/>
-      <c r="E39" s="23"/>
+      <c r="D39" s="53"/>
+      <c r="E39" s="3"/>
     </row>
     <row r="40" ht="90" spans="1:5">
-      <c r="A40" s="68" t="s">
+      <c r="A40" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="23" t="s">
+      <c r="B40" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="54" t="s">
+      <c r="C40" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="54" t="s">
+      <c r="D40" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="E40" s="23"/>
+      <c r="E40" s="3"/>
     </row>
     <row r="41" ht="75" spans="1:5">
-      <c r="A41" s="63"/>
-      <c r="B41" s="23" t="s">
+      <c r="A41" s="62"/>
+      <c r="B41" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="54" t="s">
+      <c r="C41" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
     </row>
     <row r="42" ht="45" spans="1:5">
-      <c r="A42" s="66"/>
-      <c r="B42" s="23" t="s">
+      <c r="A42" s="65"/>
+      <c r="B42" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="54" t="s">
+      <c r="C42" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
     </row>
     <row r="43" ht="75" spans="1:5">
-      <c r="A43" s="55" t="s">
+      <c r="A43" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="54" t="s">
+      <c r="C43" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="D43" s="67" t="s">
+      <c r="D43" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="E43" s="23"/>
+      <c r="E43" s="3"/>
     </row>
     <row r="44" s="46" customFormat="1" ht="45" spans="1:5">
       <c r="A44" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="20" t="s">
+      <c r="B44" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="69" t="s">
+      <c r="C44" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="D44" s="20" t="s">
+      <c r="D44" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="E44" s="20"/>
+      <c r="E44" s="22"/>
     </row>
     <row r="45" ht="75" spans="1:5">
-      <c r="A45" s="21" t="s">
+      <c r="A45" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="54" t="s">
+      <c r="C45" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="54" t="s">
+      <c r="D45" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="E45" s="23"/>
+      <c r="E45" s="3"/>
     </row>
     <row r="46" ht="75" spans="1:5">
-      <c r="A46" s="21"/>
-      <c r="B46" s="23" t="s">
+      <c r="A46" s="23"/>
+      <c r="B46" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="54" t="s">
+      <c r="C46" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="23"/>
-      <c r="E46" s="23"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
     </row>
     <row r="47" ht="45" spans="1:5">
-      <c r="A47" s="21"/>
-      <c r="B47" s="23" t="s">
+      <c r="A47" s="23"/>
+      <c r="B47" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="54" t="s">
+      <c r="C47" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
     </row>
     <row r="48" ht="60" spans="1:5">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="54" t="s">
+      <c r="C48" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="D48" s="54"/>
-      <c r="E48" s="23" t="s">
+      <c r="D48" s="53"/>
+      <c r="E48" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="49" ht="60" spans="1:5">
-      <c r="A49" s="21"/>
-      <c r="B49" s="23" t="s">
+      <c r="A49" s="23"/>
+      <c r="B49" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="54" t="s">
+      <c r="C49" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="D49" s="54"/>
-      <c r="E49" s="23"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="3"/>
     </row>
     <row r="50" ht="90" spans="1:5">
-      <c r="A50" s="68" t="s">
+      <c r="A50" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="B50" s="23" t="s">
+      <c r="B50" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="54" t="s">
+      <c r="C50" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="D50" s="54" t="s">
+      <c r="D50" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="E50" s="23"/>
+      <c r="E50" s="3"/>
     </row>
     <row r="51" ht="75" spans="1:5">
-      <c r="A51" s="63"/>
-      <c r="B51" s="23" t="s">
+      <c r="A51" s="62"/>
+      <c r="B51" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C51" s="54" t="s">
+      <c r="C51" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
     </row>
     <row r="52" ht="45" spans="1:5">
-      <c r="A52" s="66"/>
-      <c r="B52" s="23" t="s">
+      <c r="A52" s="65"/>
+      <c r="B52" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="54" t="s">
+      <c r="C52" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
     </row>
     <row r="53" ht="75" spans="1:5">
-      <c r="A53" s="55" t="s">
+      <c r="A53" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="B53" s="23" t="s">
+      <c r="B53" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C53" s="54" t="s">
+      <c r="C53" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="D53" s="67" t="s">
+      <c r="D53" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="E53" s="23"/>
+      <c r="E53" s="3"/>
     </row>
     <row r="54" s="46" customFormat="1" ht="45" spans="1:5">
       <c r="A54" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="20" t="s">
+      <c r="B54" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C54" s="69" t="s">
+      <c r="C54" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="D54" s="20" t="s">
+      <c r="D54" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="E54" s="20"/>
+      <c r="E54" s="22"/>
     </row>
     <row r="56" ht="75" spans="1:5">
-      <c r="A56" s="21" t="s">
+      <c r="A56" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="23" t="s">
+      <c r="B56" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C56" s="54" t="s">
+      <c r="C56" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="D56" s="54" t="s">
+      <c r="D56" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="E56" s="23"/>
+      <c r="E56" s="3"/>
     </row>
     <row r="57" ht="75" spans="1:5">
-      <c r="A57" s="21"/>
-      <c r="B57" s="23" t="s">
+      <c r="A57" s="23"/>
+      <c r="B57" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C57" s="54" t="s">
+      <c r="C57" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="D57" s="23"/>
-      <c r="E57" s="23"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
     </row>
     <row r="58" ht="45" spans="1:5">
-      <c r="A58" s="21"/>
-      <c r="B58" s="23" t="s">
+      <c r="A58" s="23"/>
+      <c r="B58" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="54" t="s">
+      <c r="C58" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
     </row>
     <row r="59" ht="60" spans="1:5">
-      <c r="A59" s="21" t="s">
+      <c r="A59" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B59" s="23" t="s">
+      <c r="B59" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="54" t="s">
+      <c r="C59" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="D59" s="54"/>
-      <c r="E59" s="23" t="s">
+      <c r="D59" s="53"/>
+      <c r="E59" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="60" ht="60" spans="1:5">
-      <c r="A60" s="21"/>
-      <c r="B60" s="23" t="s">
+      <c r="A60" s="23"/>
+      <c r="B60" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="54" t="s">
+      <c r="C60" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="54"/>
-      <c r="E60" s="23"/>
+      <c r="D60" s="53"/>
+      <c r="E60" s="3"/>
     </row>
     <row r="61" s="47" customFormat="1" ht="90" spans="1:5">
-      <c r="A61" s="70" t="s">
+      <c r="A61" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="B61" s="71" t="s">
+      <c r="B61" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="72" t="s">
+      <c r="C61" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="D61" s="72" t="s">
+      <c r="D61" s="71" t="s">
         <v>92</v>
       </c>
-      <c r="E61" s="71"/>
+      <c r="E61" s="70"/>
     </row>
     <row r="62" s="47" customFormat="1" ht="75" spans="1:5">
-      <c r="A62" s="73"/>
-      <c r="B62" s="71" t="s">
+      <c r="A62" s="72"/>
+      <c r="B62" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="C62" s="72" t="s">
+      <c r="C62" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="D62" s="71"/>
-      <c r="E62" s="71"/>
+      <c r="D62" s="70"/>
+      <c r="E62" s="70"/>
     </row>
     <row r="63" s="47" customFormat="1" ht="45" spans="1:5">
-      <c r="A63" s="74"/>
-      <c r="B63" s="71" t="s">
+      <c r="A63" s="73"/>
+      <c r="B63" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="72" t="s">
+      <c r="C63" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="D63" s="71"/>
-      <c r="E63" s="71"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
     </row>
     <row r="64" ht="75" spans="1:5">
-      <c r="A64" s="55" t="s">
+      <c r="A64" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="B64" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C64" s="54" t="s">
+      <c r="C64" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="D64" s="67" t="s">
+      <c r="D64" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="E64" s="23"/>
+      <c r="E64" s="3"/>
     </row>
     <row r="65" s="46" customFormat="1" ht="45" spans="1:5">
       <c r="A65" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C65" s="69" t="s">
+      <c r="C65" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="D65" s="20" t="s">
+      <c r="D65" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="E65" s="20"/>
+      <c r="E65" s="22"/>
     </row>
     <row r="66" s="45" customFormat="1" ht="23.25" spans="1:5">
-      <c r="A66" s="75" t="s">
+      <c r="A66" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="B66" s="75"/>
-      <c r="C66" s="75"/>
-      <c r="D66" s="75"/>
-      <c r="E66" s="75"/>
+      <c r="B66" s="74"/>
+      <c r="C66" s="74"/>
+      <c r="D66" s="74"/>
+      <c r="E66" s="74"/>
     </row>
     <row r="67" ht="90" spans="1:5">
-      <c r="A67" s="63" t="s">
+      <c r="A67" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="B67" s="64" t="s">
+      <c r="B67" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="C67" s="65" t="s">
+      <c r="C67" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="D67" s="65" t="s">
+      <c r="D67" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="E67" s="64"/>
+      <c r="E67" s="63"/>
     </row>
     <row r="68" ht="45" spans="1:5">
-      <c r="A68" s="63"/>
-      <c r="B68" s="23" t="s">
+      <c r="A68" s="62"/>
+      <c r="B68" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="54" t="s">
+      <c r="C68" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="D68" s="23"/>
-      <c r="E68" s="23"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
     </row>
     <row r="69" ht="60" spans="1:5">
-      <c r="A69" s="66"/>
-      <c r="B69" s="23" t="s">
+      <c r="A69" s="65"/>
+      <c r="B69" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C69" s="54" t="s">
+      <c r="C69" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
     </row>
     <row r="70" ht="75" spans="1:5">
-      <c r="A70" s="55" t="s">
+      <c r="A70" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="23" t="s">
+      <c r="B70" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="54" t="s">
+      <c r="C70" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="D70" s="67" t="s">
+      <c r="D70" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="E70" s="23"/>
+      <c r="E70" s="3"/>
     </row>
     <row r="71" ht="45" spans="1:5">
-      <c r="A71" s="55" t="s">
+      <c r="A71" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="23" t="s">
+      <c r="B71" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C71" s="53" t="s">
+      <c r="C71" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D71" s="23"/>
-      <c r="E71" s="23"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4565,8 +4587,8 @@
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" style="38" customWidth="1"/>
-    <col min="2" max="2" width="42.8571428571429" style="23" customWidth="1"/>
-    <col min="3" max="4" width="9.14285714285714" style="23"/>
+    <col min="2" max="2" width="42.8571428571429" style="3" customWidth="1"/>
+    <col min="3" max="4" width="9.14285714285714" style="3"/>
     <col min="5" max="5" width="43.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="12.4095238095238" customWidth="1"/>
     <col min="7" max="7" width="10.5714285714286"/>
@@ -4840,15 +4862,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" s="32" customFormat="1" spans="1:14">
       <c r="A2" s="33" t="s">
@@ -4905,11 +4927,11 @@
     </row>
     <row r="4" s="32" customFormat="1"/>
     <row r="7" spans="1:14">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="33" t="s">
@@ -5068,559 +5090,559 @@
       </c>
     </row>
     <row r="2" spans="3:10">
-      <c r="C2" s="20"/>
-      <c r="D2" s="20" t="s">
+      <c r="C2" s="22"/>
+      <c r="D2" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="23" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="3" spans="3:10">
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24" t="s">
+      <c r="G3" s="25"/>
+      <c r="H3" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="23"/>
     </row>
     <row r="4" spans="3:10">
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="26">
         <v>46386</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" spans="3:10">
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="26">
         <v>46477</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="23"/>
     </row>
     <row r="6" spans="3:10">
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="26">
         <v>46568</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="J6" s="21"/>
+      <c r="J6" s="23"/>
     </row>
     <row r="7" spans="3:10">
-      <c r="C7" s="26"/>
-      <c r="I7" s="26"/>
+      <c r="C7" s="27"/>
+      <c r="I7" s="27"/>
     </row>
     <row r="8" spans="3:10">
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G8" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="28">
         <v>46843</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="I8" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="J8" s="26" t="s">
+      <c r="J8" s="27" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="9" spans="3:10">
-      <c r="C9" s="26"/>
-      <c r="F9" s="28" t="s">
+      <c r="C9" s="27"/>
+      <c r="F9" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="30">
         <v>46843</v>
       </c>
-      <c r="I9" s="30" t="s">
+      <c r="I9" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J9" s="30" t="s">
+      <c r="J9" s="31" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="10" spans="3:10">
-      <c r="C10" s="26"/>
-      <c r="F10" s="28" t="s">
+      <c r="C10" s="27"/>
+      <c r="F10" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29">
+      <c r="G10" s="30"/>
+      <c r="H10" s="30">
         <v>46844</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="I10" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J10" s="30" t="s">
+      <c r="J10" s="31" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="11" spans="3:10">
-      <c r="C11" s="26"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="26"/>
+      <c r="C11" s="27"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="27"/>
     </row>
     <row r="12" spans="3:10">
-      <c r="C12" s="26"/>
-      <c r="I12" s="26"/>
+      <c r="C12" s="27"/>
+      <c r="I12" s="27"/>
     </row>
     <row r="13" spans="3:10">
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="G13" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="28">
         <v>47208</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="J13" s="26" t="s">
+      <c r="J13" s="27" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="14" spans="3:10">
-      <c r="C14" s="26"/>
-      <c r="F14" s="28" t="s">
+      <c r="C14" s="27"/>
+      <c r="F14" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="G14" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="30">
         <v>47208</v>
       </c>
-      <c r="I14" s="30" t="s">
+      <c r="I14" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J14" s="30" t="s">
+      <c r="J14" s="31" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="15" spans="3:10">
-      <c r="C15" s="26"/>
-      <c r="F15" s="28" t="s">
+      <c r="C15" s="27"/>
+      <c r="F15" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29">
+      <c r="G15" s="30"/>
+      <c r="H15" s="30">
         <v>47209</v>
       </c>
-      <c r="I15" s="30" t="s">
+      <c r="I15" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J15" s="30" t="s">
+      <c r="J15" s="31" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="16" spans="3:10">
-      <c r="C16" s="26"/>
-      <c r="I16" s="26"/>
+      <c r="C16" s="27"/>
+      <c r="I16" s="27"/>
     </row>
     <row r="17" spans="3:10">
-      <c r="C17" s="26"/>
-      <c r="I17" s="26"/>
+      <c r="C17" s="27"/>
+      <c r="I17" s="27"/>
     </row>
     <row r="18" spans="3:10">
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="F18" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G18" s="27" t="s">
+      <c r="G18" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="28">
         <v>47573</v>
       </c>
-      <c r="I18" s="22" t="s">
+      <c r="I18" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="J18" s="26" t="s">
+      <c r="J18" s="27" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="26"/>
-      <c r="F19" s="28" t="s">
+      <c r="C19" s="27"/>
+      <c r="F19" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="G19" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="H19" s="29">
+      <c r="H19" s="30">
         <v>47573</v>
       </c>
-      <c r="I19" s="30" t="s">
+      <c r="I19" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J19" s="30" t="s">
+      <c r="J19" s="31" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="20" spans="3:10">
-      <c r="C20" s="26"/>
-      <c r="F20" s="28" t="s">
+      <c r="C20" s="27"/>
+      <c r="F20" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29">
+      <c r="G20" s="30"/>
+      <c r="H20" s="30">
         <v>47574</v>
       </c>
-      <c r="I20" s="30" t="s">
+      <c r="I20" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J20" s="30" t="s">
+      <c r="J20" s="31" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="26"/>
-      <c r="I21" s="26"/>
+      <c r="C21" s="27"/>
+      <c r="I21" s="27"/>
     </row>
     <row r="22" spans="3:10">
-      <c r="C22" s="26"/>
-      <c r="I22" s="26"/>
+      <c r="C22" s="27"/>
+      <c r="I22" s="27"/>
     </row>
     <row r="23" spans="3:10">
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="D23" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E23" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G23" s="27" t="s">
+      <c r="G23" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="H23" s="27">
+      <c r="H23" s="28">
         <v>47938</v>
       </c>
-      <c r="I23" s="22" t="s">
+      <c r="I23" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="J23" s="26" t="s">
+      <c r="J23" s="27" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="24" spans="3:10">
-      <c r="F24" s="28" t="s">
+      <c r="F24" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="G24" s="29" t="s">
+      <c r="G24" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="30">
         <v>47938</v>
       </c>
-      <c r="I24" s="30" t="s">
+      <c r="I24" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J24" s="30" t="s">
+      <c r="J24" s="31" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="25" spans="3:10">
-      <c r="F25" s="28" t="s">
+      <c r="F25" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29">
+      <c r="G25" s="30"/>
+      <c r="H25" s="30">
         <v>47939</v>
       </c>
-      <c r="I25" s="30" t="s">
+      <c r="I25" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J25" s="30" t="s">
+      <c r="J25" s="31" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="26" spans="3:10">
-      <c r="I26" s="26"/>
+      <c r="I26" s="27"/>
     </row>
     <row r="27" spans="3:10">
-      <c r="I27" s="26"/>
+      <c r="I27" s="27"/>
     </row>
     <row r="28" spans="3:10">
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F28" s="23" t="s">
+      <c r="F28" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G28" s="27" t="s">
+      <c r="G28" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="H28" s="27">
+      <c r="H28" s="28">
         <v>48304</v>
       </c>
-      <c r="I28" s="22" t="s">
+      <c r="I28" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="J28" s="26" t="s">
+      <c r="J28" s="27" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="29" spans="3:10">
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="G29" s="29" t="s">
+      <c r="G29" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="H29" s="29">
+      <c r="H29" s="30">
         <v>48304</v>
       </c>
-      <c r="I29" s="30" t="s">
+      <c r="I29" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J29" s="30" t="s">
+      <c r="J29" s="31" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="30" spans="3:10">
-      <c r="F30" s="28" t="s">
+      <c r="F30" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29">
+      <c r="G30" s="30"/>
+      <c r="H30" s="30">
         <v>48305</v>
       </c>
-      <c r="I30" s="30" t="s">
+      <c r="I30" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J30" s="30" t="s">
+      <c r="J30" s="31" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="31" spans="3:10">
-      <c r="I31" s="26"/>
+      <c r="I31" s="27"/>
     </row>
     <row r="32" spans="3:10">
-      <c r="I32" s="26"/>
+      <c r="I32" s="27"/>
     </row>
     <row r="33" spans="3:10">
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="E33" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F33" s="23" t="s">
+      <c r="F33" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G33" s="27" t="s">
+      <c r="G33" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="H33" s="27">
+      <c r="H33" s="28">
         <v>48669</v>
       </c>
-      <c r="I33" s="22" t="s">
+      <c r="I33" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="J33" s="26" t="s">
+      <c r="J33" s="27" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="34" spans="3:10">
-      <c r="F34" s="28" t="s">
+      <c r="F34" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="G34" s="29" t="s">
+      <c r="G34" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="H34" s="29">
+      <c r="H34" s="30">
         <v>48669</v>
       </c>
-      <c r="I34" s="30" t="s">
+      <c r="I34" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J34" s="30" t="s">
+      <c r="J34" s="31" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="35" spans="3:10">
-      <c r="F35" s="28" t="s">
+      <c r="F35" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29">
+      <c r="G35" s="30"/>
+      <c r="H35" s="30">
         <v>48670</v>
       </c>
-      <c r="I35" s="30" t="s">
+      <c r="I35" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J35" s="30" t="s">
+      <c r="J35" s="31" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="36" spans="3:10">
-      <c r="I36" s="26"/>
+      <c r="I36" s="27"/>
     </row>
     <row r="37" spans="3:10">
-      <c r="I37" s="26"/>
+      <c r="I37" s="27"/>
     </row>
     <row r="38" spans="3:10">
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="D38" s="23" t="s">
+      <c r="D38" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="E38" s="23" t="s">
+      <c r="E38" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F38" s="23" t="s">
+      <c r="F38" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="G38" s="27" t="s">
+      <c r="G38" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="H38" s="27">
+      <c r="H38" s="28">
         <v>49034</v>
       </c>
-      <c r="I38" s="22" t="s">
+      <c r="I38" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="J38" s="26" t="s">
+      <c r="J38" s="27" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="39" spans="3:10">
-      <c r="F39" s="28"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="30"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5651,787 +5673,787 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="7" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="9">
         <v>100000</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="7"/>
+      <c r="G2" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="9">
         <v>100000</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5" t="s">
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="11">
         <v>100000</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="11">
         <v>100000</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="11">
         <v>100000</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="11">
         <v>100000</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="11">
         <v>100000</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="11">
         <v>100000</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="11">
         <v>100000</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="11">
         <v>100000</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="11">
         <v>100000</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="11">
         <v>100000</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="11">
         <v>100000</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="11">
         <v>100000</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="11">
         <v>100000</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="11">
         <v>100000</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="11">
         <v>100000</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="11">
         <v>100000</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="11">
         <v>100000</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="14">
         <v>100000</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="14">
         <v>100000</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="14">
         <v>100000</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="16">
         <v>100000</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="16">
         <v>100000</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="9">
         <v>10000</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5" t="s">
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="18">
         <v>605501.57</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5" t="s">
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="9">
         <v>200000.56</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5" t="s">
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C29" s="19">
+      <c r="C29" s="21">
         <v>200000.56</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5" t="s">
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
@@ -6461,19 +6483,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12">
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="L1" s="1"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" ht="30" spans="2:12">
       <c r="B2" t="s">
@@ -6485,15 +6507,15 @@
       <c r="G2" t="s">
         <v>254</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
     </row>
     <row r="3" ht="30" spans="2:12">
       <c r="B3" t="s">
@@ -6505,34 +6527,34 @@
       <c r="D3" t="s">
         <v>213</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="L3" s="1"/>
+      <c r="L3" s="3"/>
     </row>
     <row r="4" ht="30" spans="2:12">
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="3" t="s">
         <v>264</v>
       </c>
     </row>
@@ -6546,118 +6568,118 @@
       <c r="D5" t="s">
         <v>266</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1" t="s">
+      <c r="K5" s="3"/>
+      <c r="L5" s="3" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="6" ht="45" spans="2:12">
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1" t="s">
+      <c r="K6" s="3"/>
+      <c r="L6" s="3" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="7" ht="45" spans="2:12">
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="2" t="s">
+      <c r="K7" s="3"/>
+      <c r="L7" s="4" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="8" ht="60" spans="2:12">
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
+      <c r="K8" s="3"/>
+      <c r="L8" s="3" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="9" ht="60" spans="2:12">
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1" t="s">
+      <c r="K9" s="3"/>
+      <c r="L9" s="3" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="10" ht="60" spans="2:12">
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="2" t="s">
+      <c r="K10" s="3"/>
+      <c r="L10" s="4" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="11" ht="30" spans="2:12">
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="3" t="s">
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="5" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="12" ht="30" spans="2:12">
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="5"/>
     </row>
     <row r="17" spans="8:9">
       <c r="H17" t="s">
@@ -6665,34 +6687,34 @@
       </c>
     </row>
     <row r="19" spans="8:9">
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="3" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="20" spans="8:9">
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" s="3" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="21" spans="8:9">
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="3" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="22" spans="8:9">
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="3" t="s">
         <v>286</v>
       </c>
     </row>
@@ -6711,4 +6733,96 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="6"/>
+  <cols>
+    <col min="3" max="3" width="12.4285714285714" customWidth="1"/>
+    <col min="7" max="7" width="24.2857142857143" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="D1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="B2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="B3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="B4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="B5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" t="s">
+        <v>288</v>
+      </c>
+      <c r="D5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8" t="s">
+        <v>257</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/MU/MU user manual infoneo (2).xlsx
+++ b/MU/MU user manual infoneo (2).xlsx
@@ -4,19 +4,21 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600" activeTab="1"/>
+    <workbookView windowWidth="24000" windowHeight="9600" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Flow" sheetId="1" r:id="rId1"/>
-    <sheet name="Certificate calcualtions" sheetId="4" r:id="rId2"/>
-    <sheet name="BP - CG fee Calculatons" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
-    <sheet name="Sheet4" sheetId="9" r:id="rId6"/>
-    <sheet name="Sheet3" sheetId="10" r:id="rId7"/>
+    <sheet name="Claim Management  - normal " sheetId="4" r:id="rId2"/>
+    <sheet name="Claim Management  - SHG" sheetId="11" r:id="rId3"/>
+    <sheet name="Claim Management  - SHG (2)" sheetId="12" r:id="rId4"/>
+    <sheet name="BP - CG fee Calculatons" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet4" sheetId="9" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="10" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet2!$A$1:$H$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Sheet2!$A$1:$H$32</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="303">
   <si>
     <t>Category</t>
   </si>
@@ -1377,6 +1379,15 @@
     </r>
   </si>
   <si>
+    <t>Claim 1</t>
+  </si>
+  <si>
+    <t>Claim 2</t>
+  </si>
+  <si>
+    <t>Final claim</t>
+  </si>
+  <si>
     <t>Portfolio</t>
   </si>
   <si>
@@ -1456,6 +1467,31 @@
     <t>Eligible Claim Payout (Rs)</t>
   </si>
   <si>
+    <t>MUDMudr20262027SHG</t>
+  </si>
+  <si>
+    <t>if(@AmountOfEligibleInterimClaim&gt;@MaximumCappedInterimClaim)
+begin
+set @ActualInterimClaim=@MaximumCappedInterimClaim
+set @AmountOfEligibleInterimClaim=@MaximumCappedInterimClaim
+end</t>
+  </si>
+  <si>
+    <t>sanction</t>
+  </si>
+  <si>
+    <t>EligibleNPAOutstandingAmount</t>
+  </si>
+  <si>
+    <t>2nd loss</t>
+  </si>
+  <si>
+    <t>AmountOfEligibleInterimClaim</t>
+  </si>
+  <si>
+    <t>MaximumCappedInterimClaim</t>
+  </si>
+  <si>
     <t>Base period for normal portfolio</t>
   </si>
   <si>
@@ -1711,13 +1747,7 @@
     <t>NPA</t>
   </si>
   <si>
-    <t>Claim 1</t>
-  </si>
-  <si>
     <t>2627CR704</t>
-  </si>
-  <si>
-    <t>Claim 2</t>
   </si>
   <si>
     <t>Claim 3</t>
@@ -2252,13 +2282,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2461,7 +2491,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -2507,6 +2537,56 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -2580,19 +2660,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2745,7 +2812,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2757,34 +2824,34 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2869,7 +2936,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2967,11 +3034,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
@@ -2979,31 +3070,73 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3027,52 +3160,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3611,53 +3741,53 @@
   <dimension ref="A1:Z71"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7142857142857" style="48" customWidth="1"/>
+    <col min="1" max="1" width="22.7142857142857" style="69" customWidth="1"/>
     <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="49.8571428571429" style="43" customWidth="1"/>
+    <col min="3" max="3" width="49.8571428571429" style="70" customWidth="1"/>
     <col min="4" max="4" width="46.8571428571429" customWidth="1"/>
     <col min="5" max="5" width="57.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:26">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
     </row>
     <row r="2" ht="135" spans="1:26">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="74" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -3666,7 +3796,7 @@
       <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="75" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="4" t="s">
@@ -3674,20 +3804,20 @@
       </c>
     </row>
     <row r="3" ht="75" spans="1:26">
-      <c r="A3" s="54"/>
+      <c r="A3" s="76"/>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="75" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" ht="75" spans="1:26">
-      <c r="A4" s="54"/>
+      <c r="A4" s="76"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -3700,14 +3830,14 @@
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="55"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
+      <c r="A5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
     </row>
     <row r="6" ht="75" spans="1:26">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="76" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -3716,7 +3846,7 @@
       <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="58" t="s">
+      <c r="D6" s="80" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -3724,7 +3854,7 @@
       </c>
     </row>
     <row r="7" ht="75" spans="1:26">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="76" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -3733,37 +3863,37 @@
       <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="D7" s="75" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8" ht="56" customHeight="1" spans="1:26">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="76" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="53" t="s">
+      <c r="C8" s="75" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
     <row r="9" ht="60" spans="1:26">
-      <c r="A9" s="54"/>
+      <c r="A9" s="76"/>
       <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="75" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
     <row r="10" ht="60" spans="1:26">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="76" t="s">
         <v>26</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -3772,13 +3902,13 @@
       <c r="C10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="58" t="s">
+      <c r="D10" s="80" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3"/>
     </row>
     <row r="11" customFormat="1" ht="60" spans="1:26">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="76" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -3793,31 +3923,31 @@
       <c r="E11" s="3"/>
     </row>
     <row r="12" customFormat="1" ht="45" spans="1:26">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="76" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="75" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
     <row r="13" customFormat="1" ht="60" spans="1:26">
-      <c r="A13" s="54"/>
+      <c r="A13" s="76"/>
       <c r="B13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="75" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
     <row r="14" customFormat="1" ht="60" spans="1:26">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="76" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -3832,7 +3962,7 @@
       <c r="E14" s="3"/>
     </row>
     <row r="15" ht="60" spans="1:26">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -3841,37 +3971,37 @@
       <c r="C15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="53" t="s">
+      <c r="D15" s="75" t="s">
         <v>37</v>
       </c>
       <c r="E15" s="3"/>
     </row>
     <row r="16" ht="45" spans="1:26">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="76" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="53" t="s">
+      <c r="C16" s="75" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
     <row r="17" ht="60" spans="1:5">
-      <c r="A17" s="54"/>
+      <c r="A17" s="76"/>
       <c r="B17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="75" t="s">
         <v>25</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
     <row r="18" customFormat="1" ht="60" spans="1:5">
-      <c r="A18" s="54" t="s">
+      <c r="A18" s="76" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -3884,7 +4014,7 @@
       <c r="E18" s="3"/>
     </row>
     <row r="19" ht="60" spans="1:5">
-      <c r="A19" s="54" t="s">
+      <c r="A19" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -3893,50 +4023,50 @@
       <c r="C19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="53" t="s">
+      <c r="D19" s="75" t="s">
         <v>42</v>
       </c>
       <c r="E19" s="3"/>
     </row>
     <row r="20" ht="45" spans="1:5">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="76" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="53" t="s">
+      <c r="C20" s="75" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
     <row r="21" ht="60" spans="1:5">
-      <c r="A21" s="54"/>
+      <c r="A21" s="76"/>
       <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="53" t="s">
+      <c r="C21" s="75" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
     <row r="22" ht="90" spans="1:5">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="76" t="s">
         <v>43</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="53" t="s">
+      <c r="C22" s="75" t="s">
         <v>45</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
     <row r="23" ht="65" customHeight="1" spans="1:5">
-      <c r="A23" s="54" t="s">
+      <c r="A23" s="76" t="s">
         <v>46</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -3945,7 +4075,7 @@
       <c r="C23" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="58" t="s">
+      <c r="D23" s="80" t="s">
         <v>49</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -3953,7 +4083,7 @@
       </c>
     </row>
     <row r="24" ht="65" customHeight="1" spans="1:5">
-      <c r="A24" s="54" t="s">
+      <c r="A24" s="76" t="s">
         <v>51</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -3962,74 +4092,74 @@
       <c r="C24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="58" t="s">
+      <c r="D24" s="80" t="s">
         <v>49</v>
       </c>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" s="45" customFormat="1" ht="23.25" spans="1:5">
-      <c r="A25" s="59" t="s">
+    <row r="25" s="66" customFormat="1" ht="23.25" spans="1:5">
+      <c r="A25" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="60"/>
-      <c r="C25" s="60"/>
-      <c r="D25" s="60"/>
-      <c r="E25" s="61"/>
+      <c r="B25" s="82"/>
+      <c r="C25" s="82"/>
+      <c r="D25" s="82"/>
+      <c r="E25" s="83"/>
     </row>
     <row r="26" ht="90" spans="1:5">
-      <c r="A26" s="62" t="s">
+      <c r="A26" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="63" t="s">
+      <c r="B26" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="64" t="s">
+      <c r="C26" s="85" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="64" t="s">
+      <c r="D26" s="85" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="63"/>
+      <c r="E26" s="60"/>
     </row>
     <row r="27" ht="45" spans="1:5">
-      <c r="A27" s="62"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="53" t="s">
+      <c r="C27" s="75" t="s">
         <v>58</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
     <row r="28" ht="60" spans="1:5">
-      <c r="A28" s="65"/>
+      <c r="A28" s="86"/>
       <c r="B28" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="53" t="s">
+      <c r="C28" s="75" t="s">
         <v>59</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
     <row r="29" ht="75" spans="1:5">
-      <c r="A29" s="54" t="s">
+      <c r="A29" s="76" t="s">
         <v>60</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="53" t="s">
+      <c r="C29" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="66" t="s">
+      <c r="D29" s="87" t="s">
         <v>62</v>
       </c>
       <c r="E29" s="3"/>
     </row>
     <row r="30" ht="45" spans="1:5">
-      <c r="A30" s="54" t="s">
+      <c r="A30" s="76" t="s">
         <v>63</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -4042,7 +4172,7 @@
       <c r="E30" s="3"/>
     </row>
     <row r="31" ht="55" customHeight="1" spans="1:5">
-      <c r="A31" s="54" t="s">
+      <c r="A31" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -4064,7 +4194,7 @@
       <c r="C32" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="53"/>
+      <c r="D32" s="75"/>
       <c r="E32" s="3"/>
     </row>
     <row r="33" ht="45" spans="1:5">
@@ -4075,7 +4205,7 @@
       <c r="C33" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="53"/>
+      <c r="D33" s="75"/>
       <c r="E33" s="3"/>
     </row>
     <row r="34" ht="45" spans="1:5">
@@ -4083,10 +4213,10 @@
       <c r="B34" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="53" t="s">
+      <c r="C34" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="53"/>
+      <c r="D34" s="75"/>
       <c r="E34" s="3"/>
     </row>
     <row r="35" ht="75" spans="1:5">
@@ -4096,10 +4226,10 @@
       <c r="B35" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="53" t="s">
+      <c r="C35" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="53" t="s">
+      <c r="D35" s="75" t="s">
         <v>73</v>
       </c>
       <c r="E35" s="3"/>
@@ -4109,7 +4239,7 @@
       <c r="B36" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="53" t="s">
+      <c r="C36" s="75" t="s">
         <v>75</v>
       </c>
       <c r="D36" s="3"/>
@@ -4120,98 +4250,98 @@
       <c r="B37" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="53" t="s">
+      <c r="C37" s="75" t="s">
         <v>76</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
     <row r="38" ht="60" spans="1:5">
-      <c r="A38" s="67" t="s">
+      <c r="A38" s="88" t="s">
         <v>77</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="53" t="s">
+      <c r="C38" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="53"/>
+      <c r="D38" s="75"/>
       <c r="E38" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="39" ht="60" spans="1:5">
-      <c r="A39" s="62"/>
+      <c r="A39" s="84"/>
       <c r="B39" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="53" t="s">
+      <c r="C39" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="53"/>
+      <c r="D39" s="75"/>
       <c r="E39" s="3"/>
     </row>
     <row r="40" ht="90" spans="1:5">
-      <c r="A40" s="67" t="s">
+      <c r="A40" s="88" t="s">
         <v>81</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="53" t="s">
+      <c r="C40" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="53" t="s">
+      <c r="D40" s="75" t="s">
         <v>83</v>
       </c>
       <c r="E40" s="3"/>
     </row>
     <row r="41" ht="75" spans="1:5">
-      <c r="A41" s="62"/>
+      <c r="A41" s="84"/>
       <c r="B41" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="53" t="s">
+      <c r="C41" s="75" t="s">
         <v>75</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
     <row r="42" ht="45" spans="1:5">
-      <c r="A42" s="65"/>
+      <c r="A42" s="86"/>
       <c r="B42" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="53" t="s">
+      <c r="C42" s="75" t="s">
         <v>76</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
     </row>
     <row r="43" ht="75" spans="1:5">
-      <c r="A43" s="54" t="s">
+      <c r="A43" s="76" t="s">
         <v>84</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="53" t="s">
+      <c r="C43" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="D43" s="66" t="s">
+      <c r="D43" s="87" t="s">
         <v>85</v>
       </c>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" s="46" customFormat="1" ht="45" spans="1:5">
-      <c r="A44" s="52" t="s">
+    <row r="44" s="67" customFormat="1" ht="45" spans="1:5">
+      <c r="A44" s="74" t="s">
         <v>86</v>
       </c>
       <c r="B44" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="68" t="s">
+      <c r="C44" s="89" t="s">
         <v>87</v>
       </c>
       <c r="D44" s="22" t="s">
@@ -4226,10 +4356,10 @@
       <c r="B45" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="53" t="s">
+      <c r="C45" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="53" t="s">
+      <c r="D45" s="75" t="s">
         <v>90</v>
       </c>
       <c r="E45" s="3"/>
@@ -4239,7 +4369,7 @@
       <c r="B46" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="53" t="s">
+      <c r="C46" s="75" t="s">
         <v>75</v>
       </c>
       <c r="D46" s="3"/>
@@ -4250,7 +4380,7 @@
       <c r="B47" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="53" t="s">
+      <c r="C47" s="75" t="s">
         <v>76</v>
       </c>
       <c r="D47" s="3"/>
@@ -4263,10 +4393,10 @@
       <c r="B48" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="53" t="s">
+      <c r="C48" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="D48" s="53"/>
+      <c r="D48" s="75"/>
       <c r="E48" s="3" t="s">
         <v>79</v>
       </c>
@@ -4276,72 +4406,72 @@
       <c r="B49" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="53" t="s">
+      <c r="C49" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="D49" s="53"/>
+      <c r="D49" s="75"/>
       <c r="E49" s="3"/>
     </row>
     <row r="50" ht="90" spans="1:5">
-      <c r="A50" s="67" t="s">
+      <c r="A50" s="88" t="s">
         <v>91</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="53" t="s">
+      <c r="C50" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="D50" s="53" t="s">
+      <c r="D50" s="75" t="s">
         <v>92</v>
       </c>
       <c r="E50" s="3"/>
     </row>
     <row r="51" ht="75" spans="1:5">
-      <c r="A51" s="62"/>
+      <c r="A51" s="84"/>
       <c r="B51" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C51" s="53" t="s">
+      <c r="C51" s="75" t="s">
         <v>75</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
     </row>
     <row r="52" ht="45" spans="1:5">
-      <c r="A52" s="65"/>
+      <c r="A52" s="86"/>
       <c r="B52" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="53" t="s">
+      <c r="C52" s="75" t="s">
         <v>76</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
     </row>
     <row r="53" ht="75" spans="1:5">
-      <c r="A53" s="54" t="s">
+      <c r="A53" s="76" t="s">
         <v>93</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C53" s="53" t="s">
+      <c r="C53" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="D53" s="66" t="s">
+      <c r="D53" s="87" t="s">
         <v>85</v>
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" s="46" customFormat="1" ht="45" spans="1:5">
-      <c r="A54" s="52" t="s">
+    <row r="54" s="67" customFormat="1" ht="45" spans="1:5">
+      <c r="A54" s="74" t="s">
         <v>94</v>
       </c>
       <c r="B54" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C54" s="68" t="s">
+      <c r="C54" s="89" t="s">
         <v>95</v>
       </c>
       <c r="D54" s="22" t="s">
@@ -4356,10 +4486,10 @@
       <c r="B56" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C56" s="53" t="s">
+      <c r="C56" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="D56" s="53" t="s">
+      <c r="D56" s="75" t="s">
         <v>97</v>
       </c>
       <c r="E56" s="3"/>
@@ -4369,7 +4499,7 @@
       <c r="B57" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C57" s="53" t="s">
+      <c r="C57" s="75" t="s">
         <v>75</v>
       </c>
       <c r="D57" s="3"/>
@@ -4380,7 +4510,7 @@
       <c r="B58" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="53" t="s">
+      <c r="C58" s="75" t="s">
         <v>76</v>
       </c>
       <c r="D58" s="3"/>
@@ -4393,10 +4523,10 @@
       <c r="B59" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="53" t="s">
+      <c r="C59" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="D59" s="53"/>
+      <c r="D59" s="75"/>
       <c r="E59" s="3" t="s">
         <v>79</v>
       </c>
@@ -4406,72 +4536,72 @@
       <c r="B60" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="53" t="s">
+      <c r="C60" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="53"/>
+      <c r="D60" s="75"/>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" s="47" customFormat="1" ht="90" spans="1:5">
-      <c r="A61" s="69" t="s">
+    <row r="61" s="68" customFormat="1" ht="90" spans="1:5">
+      <c r="A61" s="90" t="s">
         <v>91</v>
       </c>
-      <c r="B61" s="70" t="s">
+      <c r="B61" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="71" t="s">
+      <c r="C61" s="92" t="s">
         <v>82</v>
       </c>
-      <c r="D61" s="71" t="s">
+      <c r="D61" s="92" t="s">
         <v>92</v>
       </c>
-      <c r="E61" s="70"/>
-    </row>
-    <row r="62" s="47" customFormat="1" ht="75" spans="1:5">
-      <c r="A62" s="72"/>
-      <c r="B62" s="70" t="s">
+      <c r="E61" s="91"/>
+    </row>
+    <row r="62" s="68" customFormat="1" ht="75" spans="1:5">
+      <c r="A62" s="93"/>
+      <c r="B62" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="C62" s="71" t="s">
+      <c r="C62" s="92" t="s">
         <v>75</v>
       </c>
-      <c r="D62" s="70"/>
-      <c r="E62" s="70"/>
-    </row>
-    <row r="63" s="47" customFormat="1" ht="45" spans="1:5">
-      <c r="A63" s="73"/>
-      <c r="B63" s="70" t="s">
+      <c r="D62" s="91"/>
+      <c r="E62" s="91"/>
+    </row>
+    <row r="63" s="68" customFormat="1" ht="45" spans="1:5">
+      <c r="A63" s="94"/>
+      <c r="B63" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="71" t="s">
+      <c r="C63" s="92" t="s">
         <v>76</v>
       </c>
-      <c r="D63" s="70"/>
-      <c r="E63" s="70"/>
+      <c r="D63" s="91"/>
+      <c r="E63" s="91"/>
     </row>
     <row r="64" ht="75" spans="1:5">
-      <c r="A64" s="54" t="s">
+      <c r="A64" s="76" t="s">
         <v>98</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C64" s="53" t="s">
+      <c r="C64" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="D64" s="66" t="s">
+      <c r="D64" s="87" t="s">
         <v>85</v>
       </c>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" s="46" customFormat="1" ht="45" spans="1:5">
-      <c r="A65" s="52" t="s">
+    <row r="65" s="67" customFormat="1" ht="45" spans="1:5">
+      <c r="A65" s="74" t="s">
         <v>94</v>
       </c>
       <c r="B65" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C65" s="68" t="s">
+      <c r="C65" s="89" t="s">
         <v>95</v>
       </c>
       <c r="D65" s="22" t="s">
@@ -4479,69 +4609,69 @@
       </c>
       <c r="E65" s="22"/>
     </row>
-    <row r="66" s="45" customFormat="1" ht="23.25" spans="1:5">
-      <c r="A66" s="74" t="s">
+    <row r="66" s="66" customFormat="1" ht="23.25" spans="1:5">
+      <c r="A66" s="95" t="s">
         <v>99</v>
       </c>
-      <c r="B66" s="74"/>
-      <c r="C66" s="74"/>
-      <c r="D66" s="74"/>
-      <c r="E66" s="74"/>
+      <c r="B66" s="95"/>
+      <c r="C66" s="95"/>
+      <c r="D66" s="95"/>
+      <c r="E66" s="95"/>
     </row>
     <row r="67" ht="90" spans="1:5">
-      <c r="A67" s="62" t="s">
+      <c r="A67" s="84" t="s">
         <v>100</v>
       </c>
-      <c r="B67" s="63" t="s">
+      <c r="B67" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="C67" s="64" t="s">
+      <c r="C67" s="85" t="s">
         <v>55</v>
       </c>
-      <c r="D67" s="64" t="s">
+      <c r="D67" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="E67" s="63"/>
+      <c r="E67" s="60"/>
     </row>
     <row r="68" ht="45" spans="1:5">
-      <c r="A68" s="62"/>
+      <c r="A68" s="84"/>
       <c r="B68" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="53" t="s">
+      <c r="C68" s="75" t="s">
         <v>58</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
     </row>
     <row r="69" ht="60" spans="1:5">
-      <c r="A69" s="65"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C69" s="53" t="s">
+      <c r="C69" s="75" t="s">
         <v>59</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
     </row>
     <row r="70" ht="75" spans="1:5">
-      <c r="A70" s="54" t="s">
+      <c r="A70" s="76" t="s">
         <v>60</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="53" t="s">
+      <c r="C70" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="D70" s="66" t="s">
+      <c r="D70" s="87" t="s">
         <v>102</v>
       </c>
       <c r="E70" s="3"/>
     </row>
     <row r="71" ht="45" spans="1:5">
-      <c r="A71" s="54" t="s">
+      <c r="A71" s="76" t="s">
         <v>63</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -4583,262 +4713,283 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="42" style="38" customWidth="1"/>
     <col min="2" max="2" width="42.8571428571429" style="3" customWidth="1"/>
-    <col min="3" max="4" width="9.14285714285714" style="3"/>
-    <col min="5" max="5" width="43.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="12.4095238095238" customWidth="1"/>
-    <col min="7" max="7" width="10.5714285714286"/>
+    <col min="3" max="3" width="16.2380952380952" style="3" customWidth="1"/>
+    <col min="4" max="4" width="13.3714285714286" style="3" customWidth="1"/>
+    <col min="5" max="5" width="22.7238095238095" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:5">
+      <c r="B1" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="C1" s="41"/>
+      <c r="D1" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:17">
-      <c r="A2" s="39" t="s">
+      <c r="E1" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="40" t="s">
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:5">
+      <c r="A2" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-    </row>
-    <row r="3" ht="64" customHeight="1" spans="1:17">
-      <c r="A3" s="39" t="s">
+      <c r="B2" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="40">
-        <v>1000000</v>
-      </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" t="s">
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:5">
+      <c r="A3" s="42" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="4" ht="29" customHeight="1" spans="1:17">
-      <c r="A4" s="39" t="s">
+      <c r="B3" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="40">
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+    </row>
+    <row r="4" ht="64" customHeight="1" spans="1:5">
+      <c r="A4" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="47">
+        <v>3115502.69</v>
+      </c>
+      <c r="D4" s="47">
+        <v>3015502.69</v>
+      </c>
+      <c r="E4" s="48">
+        <v>2715502.69</v>
+      </c>
+    </row>
+    <row r="5" ht="29" customHeight="1" spans="1:5">
+      <c r="A5" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="47">
         <v>1</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" ht="33" customHeight="1" spans="1:17">
-      <c r="A5" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5" s="40">
-        <v>1000</v>
-      </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1" spans="1:17">
-      <c r="A6" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="B6" s="40">
+      <c r="D5" s="47">
+        <f>C5</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="48">
+        <f>D5</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="33" customHeight="1" spans="1:5">
+      <c r="A6" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="47">
+        <v>115000</v>
+      </c>
+      <c r="D6" s="47">
+        <v>215000</v>
+      </c>
+      <c r="E6" s="47">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1" spans="1:5">
+      <c r="A7" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="47">
+        <v>14200</v>
+      </c>
+      <c r="D7" s="47">
+        <v>27000</v>
+      </c>
+      <c r="E7" s="47">
         <v>0</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" t="s">
-        <v>114</v>
-      </c>
-      <c r="N6" s="42">
-        <v>15000</v>
-      </c>
-      <c r="P6">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:17">
-      <c r="A7" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" s="40">
-        <f>B5-B6</f>
-        <v>1000</v>
-      </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" t="s">
-        <v>116</v>
-      </c>
-      <c r="N7">
-        <v>17112</v>
-      </c>
-      <c r="P7">
-        <v>1280</v>
-      </c>
-      <c r="Q7">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="8" ht="71" customHeight="1" spans="1:17">
-      <c r="A8" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="B8" s="40">
-        <f>3%*B7</f>
-        <v>30</v>
-      </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="43" t="s">
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:5">
+      <c r="A8" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="N8" s="42">
-        <v>20453</v>
-      </c>
-      <c r="P8">
-        <v>8760</v>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1" spans="1:17">
-      <c r="A9" s="41" t="s">
+      <c r="B8" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="40">
-        <f>B7-B8</f>
-        <v>970</v>
-      </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" t="s">
+      <c r="C8" s="47">
+        <f>C6-C7</f>
+        <v>100800</v>
+      </c>
+      <c r="D8" s="47">
+        <f>D6-D7</f>
+        <v>188000</v>
+      </c>
+      <c r="E8" s="47">
+        <f>E6-E7</f>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="9" ht="71" customHeight="1" spans="1:5">
+      <c r="A9" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="N9">
-        <v>21067</v>
-      </c>
-      <c r="P9">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1" spans="1:17">
-      <c r="A10" s="41" t="s">
+      <c r="B9" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="40">
-        <f>15%*B3</f>
-        <v>150000</v>
-      </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" t="s">
+      <c r="C9" s="47">
+        <f>3%*C8</f>
+        <v>3024</v>
+      </c>
+      <c r="D9" s="47">
+        <f>3%*D8</f>
+        <v>5640</v>
+      </c>
+      <c r="E9" s="47">
+        <f>3%*E8</f>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="1:5">
+      <c r="A10" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-      <c r="K10" s="44">
-        <v>38697.18</v>
-      </c>
-      <c r="N10">
-        <v>80250</v>
-      </c>
-      <c r="P10">
-        <v>23458</v>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1" spans="1:17">
-      <c r="A11" s="41" t="s">
+      <c r="B10" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="40">
-        <f>75%*B9</f>
-        <v>727.5</v>
-      </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" t="s">
+      <c r="C10" s="47">
+        <f>C8-C9</f>
+        <v>97776</v>
+      </c>
+      <c r="D10" s="47">
+        <f>D8-D9</f>
+        <v>182360</v>
+      </c>
+      <c r="E10" s="47">
+        <f>E8-E9</f>
+        <v>194000</v>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" spans="1:5">
+      <c r="A11" s="49" t="s">
         <v>124</v>
       </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-      <c r="K11" s="44">
-        <v>47062.7</v>
-      </c>
-      <c r="N11">
-        <v>15000</v>
-      </c>
-      <c r="P11">
-        <v>7100</v>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1" spans="1:17">
-      <c r="A12" s="41" t="s">
+      <c r="B11" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="B12" s="40">
-        <f>B11</f>
-        <v>727.5</v>
-      </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="F12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" ht="38" customHeight="1" spans="1:17">
-      <c r="A13" s="41" t="s">
+      <c r="C11" s="64">
+        <f>15%*C4</f>
+        <v>467325.4035</v>
+      </c>
+      <c r="D11" s="64">
+        <f>15%*D4</f>
+        <v>452325.4035</v>
+      </c>
+      <c r="E11" s="64">
+        <f>15%*E4</f>
+        <v>407325.4035</v>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1" spans="1:5">
+      <c r="A12" s="49" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" t="s">
+      <c r="B12" s="46" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="14" ht="33" customHeight="1" spans="1:17">
-      <c r="A14" s="41" t="s">
+      <c r="C12" s="47">
+        <f>75%*C10</f>
+        <v>73332</v>
+      </c>
+      <c r="D12" s="47">
+        <f>75%*D10</f>
+        <v>136770</v>
+      </c>
+      <c r="E12" s="47">
+        <f>75%*E10</f>
+        <v>145500</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" spans="1:5">
+      <c r="A13" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="40">
-        <f>B12-B13</f>
-        <v>727.5</v>
-      </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="47">
+        <f>C12</f>
+        <v>73332</v>
+      </c>
+      <c r="D13" s="47">
+        <f>D12</f>
+        <v>136770</v>
+      </c>
+      <c r="E13" s="47">
+        <f>E12</f>
+        <v>145500</v>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1" spans="1:5">
+      <c r="A14" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47">
+        <f>C15</f>
+        <v>73332</v>
+      </c>
+      <c r="E14" s="47">
+        <f>D15+C15</f>
+        <v>136770</v>
+      </c>
+    </row>
+    <row r="15" ht="33" customHeight="1" spans="1:5">
+      <c r="A15" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="46"/>
+      <c r="C15" s="65">
+        <f>C13-C14</f>
+        <v>73332</v>
+      </c>
+      <c r="D15" s="65">
+        <f>D13-D14</f>
+        <v>63438</v>
+      </c>
+      <c r="E15" s="65">
+        <f>E13-E14</f>
+        <v>8730</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
+  <mergeCells count="3">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4846,6 +4997,522 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="42" style="38" customWidth="1"/>
+    <col min="2" max="2" width="40" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.4952380952381" style="39" customWidth="1"/>
+    <col min="4" max="4" width="23.3714285714286" style="40" customWidth="1"/>
+    <col min="5" max="5" width="24.8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="B1" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:15">
+      <c r="A2" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="45"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:15">
+      <c r="A3" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45"/>
+    </row>
+    <row r="4" ht="64" customHeight="1" spans="1:15">
+      <c r="A4" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="47">
+        <v>5500001</v>
+      </c>
+      <c r="D4" s="48">
+        <v>3000000</v>
+      </c>
+      <c r="E4" s="48">
+        <v>9200001</v>
+      </c>
+    </row>
+    <row r="5" ht="29" customHeight="1" spans="1:15">
+      <c r="A5" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="47">
+        <v>1</v>
+      </c>
+      <c r="D5" s="48">
+        <f>C5</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="48">
+        <f>D5</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="33" customHeight="1" spans="1:15">
+      <c r="A6" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="47">
+        <v>1100500</v>
+      </c>
+      <c r="D6" s="48">
+        <v>1100000</v>
+      </c>
+      <c r="E6" s="48">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1" spans="1:15">
+      <c r="A7" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="47">
+        <v>3800</v>
+      </c>
+      <c r="D7" s="48">
+        <v>1200</v>
+      </c>
+      <c r="E7" s="48">
+        <v>20800</v>
+      </c>
+      <c r="L7" s="50">
+        <v>15000</v>
+      </c>
+      <c r="N7">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:15">
+      <c r="A8" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="47">
+        <f>C6-C7</f>
+        <v>1096700</v>
+      </c>
+      <c r="D8" s="48">
+        <f>D6-D7</f>
+        <v>1098800</v>
+      </c>
+      <c r="E8" s="48">
+        <f>E6-E7</f>
+        <v>1779200</v>
+      </c>
+      <c r="L8">
+        <v>17112</v>
+      </c>
+      <c r="N8">
+        <v>1280</v>
+      </c>
+      <c r="O8">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" spans="1:15">
+      <c r="A9" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="46"/>
+      <c r="C9" s="51">
+        <f>75%*C8</f>
+        <v>822525</v>
+      </c>
+      <c r="D9" s="51">
+        <f>75%*D8</f>
+        <v>824100</v>
+      </c>
+      <c r="E9" s="51">
+        <f>75%*E8</f>
+        <v>1334400</v>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1" spans="1:15">
+      <c r="A10" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" s="47">
+        <v>0</v>
+      </c>
+      <c r="D10" s="48">
+        <f>C11</f>
+        <v>822525</v>
+      </c>
+      <c r="E10" s="48">
+        <f>D11+C11</f>
+        <v>824100</v>
+      </c>
+    </row>
+    <row r="11" ht="33" customHeight="1" spans="1:15">
+      <c r="A11" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="46"/>
+      <c r="C11" s="47">
+        <f>C9-C10</f>
+        <v>822525</v>
+      </c>
+      <c r="D11" s="52">
+        <f>D9-D10</f>
+        <v>1575</v>
+      </c>
+      <c r="E11" s="41">
+        <f>E9-E10</f>
+        <v>510300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="59"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="61"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O19"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="42" style="38" customWidth="1"/>
+    <col min="2" max="2" width="40" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.4952380952381" style="39" customWidth="1"/>
+    <col min="4" max="4" width="23.3714285714286" style="40" customWidth="1"/>
+    <col min="5" max="5" width="24.8" customWidth="1"/>
+    <col min="9" max="9" width="20.647619047619" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="B1" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:15">
+      <c r="A2" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="45"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:15">
+      <c r="A3" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45"/>
+    </row>
+    <row r="4" ht="64" customHeight="1" spans="1:15">
+      <c r="A4" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="47">
+        <v>5500001</v>
+      </c>
+      <c r="D4" s="48">
+        <v>3000000</v>
+      </c>
+      <c r="E4" s="48">
+        <v>9200001</v>
+      </c>
+    </row>
+    <row r="5" ht="29" customHeight="1" spans="1:15">
+      <c r="A5" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="47">
+        <v>1</v>
+      </c>
+      <c r="D5" s="48">
+        <f>C5</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="48">
+        <f>D5</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="33" customHeight="1" spans="1:15">
+      <c r="A6" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="47">
+        <v>1100500</v>
+      </c>
+      <c r="D6" s="48">
+        <v>1100000</v>
+      </c>
+      <c r="E6" s="48">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1" spans="1:15">
+      <c r="A7" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="47">
+        <v>3800</v>
+      </c>
+      <c r="D7" s="48">
+        <v>1200</v>
+      </c>
+      <c r="E7" s="48">
+        <v>20800</v>
+      </c>
+      <c r="L7" s="50">
+        <v>15000</v>
+      </c>
+      <c r="N7">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:15">
+      <c r="A8" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="47">
+        <f>C6-C7</f>
+        <v>1096700</v>
+      </c>
+      <c r="D8" s="48">
+        <f>D6-D7</f>
+        <v>1098800</v>
+      </c>
+      <c r="E8" s="48">
+        <f>E6-E7</f>
+        <v>1779200</v>
+      </c>
+      <c r="L8">
+        <v>17112</v>
+      </c>
+      <c r="N8">
+        <v>1280</v>
+      </c>
+      <c r="O8">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" spans="1:15">
+      <c r="A9" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="46"/>
+      <c r="C9" s="51">
+        <f>75%*C8</f>
+        <v>822525</v>
+      </c>
+      <c r="D9" s="51">
+        <f>75%*D8</f>
+        <v>824100</v>
+      </c>
+      <c r="E9" s="51">
+        <f>75%*E8</f>
+        <v>1334400</v>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1" spans="1:15">
+      <c r="A10" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" s="47">
+        <v>0</v>
+      </c>
+      <c r="D10" s="48">
+        <f>C11</f>
+        <v>822525</v>
+      </c>
+      <c r="E10" s="48">
+        <f>D11+C11</f>
+        <v>824100</v>
+      </c>
+    </row>
+    <row r="11" ht="125" customHeight="1" spans="1:15">
+      <c r="A11" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="46"/>
+      <c r="C11" s="47">
+        <f>C9-C10</f>
+        <v>822525</v>
+      </c>
+      <c r="D11" s="52">
+        <f>D9-D10</f>
+        <v>1575</v>
+      </c>
+      <c r="E11" s="41">
+        <f>E9-E10</f>
+        <v>510300</v>
+      </c>
+      <c r="I11" s="53" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="54" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="55"/>
+      <c r="C12" s="56">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" s="29"/>
+      <c r="C13" s="58">
+        <v>2680800</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="B14" s="29"/>
+      <c r="C14" s="58">
+        <f>C13</f>
+        <v>2680800</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" s="29"/>
+      <c r="C15" s="58">
+        <f>75%*C14</f>
+        <v>2010600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="58">
+        <f>15%*C12</f>
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="57"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="58" t="b">
+        <f>IF(C15&gt;C16,C16=C15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="B18" s="29"/>
+      <c r="C18" s="58">
+        <f>15%*C14</f>
+        <v>402120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="57"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="58"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N15"/>
@@ -4863,7 +5530,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="24" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -4874,25 +5541,25 @@
     </row>
     <row r="2" s="32" customFormat="1" spans="1:14">
       <c r="A2" s="33" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="N2" s="32">
         <v>832.88</v>
@@ -4928,32 +5595,32 @@
     <row r="4" s="32" customFormat="1"/>
     <row r="7" spans="1:14">
       <c r="A7" s="24" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B7" s="24"/>
       <c r="C7" s="24"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="33" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4985,42 +5652,42 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="33" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="K14" s="33" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="35" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B15" s="35">
         <v>10000</v>
@@ -5055,7 +5722,7 @@
         <v>137.786301369863</v>
       </c>
       <c r="K15" s="35" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -5068,7 +5735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C1:J39"/>
@@ -5086,124 +5753,124 @@
   <sheetData>
     <row r="1" spans="3:10">
       <c r="C1" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="3:10">
       <c r="C2" s="22"/>
       <c r="D2" s="22" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="J2" s="23" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="3:10">
       <c r="C3" s="24" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G3" s="25"/>
       <c r="H3" s="25" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J3" s="23"/>
     </row>
     <row r="4" spans="3:10">
       <c r="C4" s="24" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H4" s="26">
         <v>46386</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J4" s="23"/>
     </row>
     <row r="5" spans="3:10">
       <c r="C5" s="24" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H5" s="26">
         <v>46477</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J5" s="23"/>
     </row>
     <row r="6" spans="3:10">
       <c r="C6" s="24" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H6" s="26">
         <v>46568</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J6" s="23"/>
     </row>
@@ -5213,62 +5880,62 @@
     </row>
     <row r="8" spans="3:10">
       <c r="C8" s="24" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H8" s="28">
         <v>46843</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J8" s="27" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="3:10">
       <c r="C9" s="27"/>
       <c r="F9" s="29" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="H9" s="30">
         <v>46843</v>
       </c>
       <c r="I9" s="31" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="3:10">
       <c r="C10" s="27"/>
       <c r="F10" s="29" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G10" s="30"/>
       <c r="H10" s="30">
         <v>46844</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="3:10">
@@ -5285,62 +5952,62 @@
     </row>
     <row r="13" spans="3:10">
       <c r="C13" s="24" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H13" s="28">
         <v>47208</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="3:10">
       <c r="C14" s="27"/>
       <c r="F14" s="29" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="H14" s="30">
         <v>47208</v>
       </c>
       <c r="I14" s="31" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J14" s="31" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="3:10">
       <c r="C15" s="27"/>
       <c r="F15" s="29" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G15" s="30"/>
       <c r="H15" s="30">
         <v>47209</v>
       </c>
       <c r="I15" s="31" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J15" s="31" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="3:10">
@@ -5353,62 +6020,62 @@
     </row>
     <row r="18" spans="3:10">
       <c r="C18" s="24" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H18" s="28">
         <v>47573</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J18" s="27" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="3:10">
       <c r="C19" s="27"/>
       <c r="F19" s="29" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G19" s="30" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="H19" s="30">
         <v>47573</v>
       </c>
       <c r="I19" s="31" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J19" s="31" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="3:10">
       <c r="C20" s="27"/>
       <c r="F20" s="29" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G20" s="30"/>
       <c r="H20" s="30">
         <v>47574</v>
       </c>
       <c r="I20" s="31" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J20" s="31" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="3:10">
@@ -5421,60 +6088,60 @@
     </row>
     <row r="23" spans="3:10">
       <c r="C23" s="24" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G23" s="28" t="s">
         <v>185</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G23" s="28" t="s">
-        <v>175</v>
       </c>
       <c r="H23" s="28">
         <v>47938</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="3:10">
       <c r="F24" s="29" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G24" s="30" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="H24" s="30">
         <v>47938</v>
       </c>
       <c r="I24" s="31" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J24" s="31" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="3:10">
       <c r="F25" s="29" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G25" s="30"/>
       <c r="H25" s="30">
         <v>47939</v>
       </c>
       <c r="I25" s="31" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J25" s="31" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="3:10">
@@ -5485,60 +6152,60 @@
     </row>
     <row r="28" spans="3:10">
       <c r="C28" s="24" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H28" s="28">
         <v>48304</v>
       </c>
       <c r="I28" s="24" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J28" s="27" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="3:10">
       <c r="F29" s="29" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="H29" s="30">
         <v>48304</v>
       </c>
       <c r="I29" s="31" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J29" s="31" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="3:10">
       <c r="F30" s="29" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G30" s="30"/>
       <c r="H30" s="30">
         <v>48305</v>
       </c>
       <c r="I30" s="31" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J30" s="31" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="3:10">
@@ -5549,60 +6216,60 @@
     </row>
     <row r="33" spans="3:10">
       <c r="C33" s="24" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G33" s="28" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H33" s="28">
         <v>48669</v>
       </c>
       <c r="I33" s="24" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J33" s="27" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="34" spans="3:10">
       <c r="F34" s="29" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G34" s="30" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="H34" s="30">
         <v>48669</v>
       </c>
       <c r="I34" s="31" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J34" s="31" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="3:10">
       <c r="F35" s="29" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G35" s="30"/>
       <c r="H35" s="30">
         <v>48670</v>
       </c>
       <c r="I35" s="31" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J35" s="31" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="3:10">
@@ -5613,28 +6280,28 @@
     </row>
     <row r="38" spans="3:10">
       <c r="C38" s="24" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="G38" s="28" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="H38" s="28">
         <v>49034</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J38" s="27" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="3:10">
@@ -5653,7 +6320,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K32"/>
@@ -5674,58 +6341,58 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="6" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="8" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="C2" s="9">
         <v>100000</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
@@ -5734,23 +6401,23 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="8" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C3" s="9">
         <v>100000</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -5759,28 +6426,28 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="10" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C4" s="11">
         <v>100000</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>214</v>
+        <v>103</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
@@ -5788,87 +6455,87 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C5" s="11">
         <v>100000</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>214</v>
+        <v>103</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>216</v>
+        <v>104</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="10" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C6" s="11">
         <v>100000</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>216</v>
+        <v>104</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="10" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C7" s="11">
         <v>100000</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
@@ -5877,25 +6544,25 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C8" s="11">
         <v>100000</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -5904,25 +6571,25 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="10" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C9" s="11">
         <v>100000</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -5931,25 +6598,25 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="10" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C10" s="11">
         <v>100000</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -5958,28 +6625,28 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="10" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C11" s="11">
         <v>100000</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
@@ -5987,25 +6654,25 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="10" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C12" s="11">
         <v>100000</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -6014,25 +6681,25 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="10" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C13" s="11">
         <v>100000</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
@@ -6041,25 +6708,25 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="10" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C14" s="11">
         <v>100000</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
@@ -6068,28 +6735,28 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="10" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C15" s="11">
         <v>100000</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
@@ -6097,28 +6764,28 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="10" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C16" s="11">
         <v>100000</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
@@ -6126,25 +6793,25 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="10" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C17" s="11">
         <v>100000</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -6153,25 +6820,25 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="10" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C18" s="11">
         <v>100000</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -6180,25 +6847,25 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="10" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C19" s="11">
         <v>100000</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -6207,25 +6874,25 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="10" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C20" s="11">
         <v>100000</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -6234,25 +6901,25 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="13" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C21" s="14">
         <v>100000</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -6261,22 +6928,22 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="13" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C22" s="14">
         <v>100000</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
@@ -6286,22 +6953,22 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="13" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C23" s="14">
         <v>100000</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
@@ -6311,19 +6978,19 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="15" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C24" s="16">
         <v>100000</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -6334,19 +7001,19 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="15" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C25" s="16">
         <v>100000</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
@@ -6357,107 +7024,107 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="17" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C26" s="9">
         <v>10000</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="17" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C27" s="18">
         <v>605501.57</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="17" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C28" s="9">
         <v>200000.56</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="19" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C29" s="21">
         <v>200000.56</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -6469,7 +7136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:L25"/>
@@ -6487,31 +7154,31 @@
         <v>1</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="L1" s="3"/>
     </row>
     <row r="2" ht="30" spans="2:12">
       <c r="B2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="G2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -6519,163 +7186,163 @@
     </row>
     <row r="3" ht="30" spans="2:12">
       <c r="B3" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C3">
         <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="30" spans="2:12">
       <c r="H4" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" ht="45" spans="2:12">
       <c r="B5" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C5">
         <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="I5" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" ht="45" spans="2:12">
       <c r="H6" s="3" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" ht="45" spans="2:12">
       <c r="H7" s="3" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="4" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" ht="60" spans="2:12">
       <c r="H8" s="3" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" ht="60" spans="2:12">
       <c r="H9" s="3" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" ht="60" spans="2:12">
       <c r="H10" s="3" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="4" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" ht="30" spans="2:12">
       <c r="H11" s="3" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="5" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" ht="30" spans="2:12">
       <c r="H12" s="3" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -6683,47 +7350,47 @@
     </row>
     <row r="17" spans="8:9">
       <c r="H17" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" spans="8:9">
       <c r="H19" s="3" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="8:9">
       <c r="H20" s="3" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="8:9">
       <c r="H21" s="3" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="8:9">
       <c r="H22" s="3" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="8:9">
       <c r="H25" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="I25" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -6735,90 +7402,106 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="12.4285714285714" customWidth="1"/>
     <col min="7" max="7" width="24.2857142857143" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="D1" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="B2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C2" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D2" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="E2" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="B3" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C3" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D3" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="B4" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C4" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D4" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C5" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D5" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="F6" s="2">
         <v>0.15</v>
       </c>
       <c r="G6" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>294</v>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="G15" s="1">
+        <f>15%*3000000</f>
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="17" spans="7:9">
+      <c r="G17" s="1">
+        <f>75%*2700000</f>
+        <v>2025000</v>
+      </c>
+      <c r="I17" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
